--- a/ONON.xlsx
+++ b/ONON.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{785726AD-1731-4FE3-A1EE-2F9AABBDD52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F02E5AE-7E7C-4B42-B511-C4954981D781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{3D17FBD5-4686-4900-BBF2-80842DD395C0}"/>
   </bookViews>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="317">
   <si>
     <t>On Holding</t>
   </si>
@@ -1037,6 +1037,18 @@
   </si>
   <si>
     <t>FY25</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -1056,13 +1068,19 @@
     <numFmt numFmtId="173" formatCode="\F\Y#,##0"/>
     <numFmt numFmtId="174" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1425,19 +1443,19 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1457,43 +1475,43 @@
     <xf numFmtId="9" fontId="0" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="5" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="5" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="6" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1509,102 +1527,106 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="12" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="8" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="13" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="9" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="173" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="173" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2078,8 +2100,8 @@
       <c r="G2" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="95">
-        <v>41.04</v>
+      <c r="H2" s="89">
+        <v>36.42</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -2088,10 +2110,7 @@
       </c>
       <c r="H3" s="66">
         <f>+H2*H10</f>
-        <v>34.884</v>
-      </c>
-      <c r="I3" s="96" t="s">
-        <v>308</v>
+        <v>30.957000000000001</v>
       </c>
       <c r="K3" s="68"/>
     </row>
@@ -2105,7 +2124,9 @@
       <c r="H4" s="66">
         <v>296.87335300000001</v>
       </c>
-      <c r="I4" s="67"/>
+      <c r="I4" s="114" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B5" s="65" t="s">
@@ -2116,10 +2137,7 @@
       </c>
       <c r="H5" s="66">
         <f>+H3*H4</f>
-        <v>10356.130046052</v>
-      </c>
-      <c r="I5" s="96" t="s">
-        <v>308</v>
+        <v>9190.3083888210003</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -2127,10 +2145,10 @@
         <v>5</v>
       </c>
       <c r="H6" s="66">
-        <v>1019.9</v>
-      </c>
-      <c r="I6" s="96" t="s">
-        <v>308</v>
+        <v>1020.4</v>
+      </c>
+      <c r="I6" s="114" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -2144,8 +2162,11 @@
         <v>6</v>
       </c>
       <c r="H7" s="66">
-        <f>2.8+56.7</f>
-        <v>59.5</v>
+        <f>52.2+5.8</f>
+        <v>58</v>
+      </c>
+      <c r="I7" s="114" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -2160,7 +2181,7 @@
       </c>
       <c r="H8" s="66">
         <f>+H5-H6+H7</f>
-        <v>9395.730046052</v>
+        <v>8227.9083888210007</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -2252,7 +2273,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7A9B0E-FCCA-49E4-9A23-D8042125AB6F}">
-  <dimension ref="A1:AS97"/>
+  <dimension ref="A1:AW97"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="65" bestFit="1" customWidth="1"/>
@@ -2260,12 +2281,12 @@
     <col min="3" max="16384" width="9.140625" style="65"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A1" s="69" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.2">
       <c r="C2" s="67" t="s">
         <v>13</v>
       </c>
@@ -2302,29 +2323,41 @@
       <c r="N2" s="67" t="s">
         <v>308</v>
       </c>
-      <c r="P2" s="67" t="s">
+      <c r="O2" s="114" t="s">
+        <v>313</v>
+      </c>
+      <c r="P2" s="114" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q2" s="114" t="s">
+        <v>315</v>
+      </c>
+      <c r="R2" s="114" t="s">
+        <v>316</v>
+      </c>
+      <c r="T2" s="67" t="s">
         <v>129</v>
       </c>
-      <c r="Q2" s="67" t="s">
+      <c r="U2" s="67" t="s">
         <v>130</v>
       </c>
-      <c r="R2" s="67" t="s">
+      <c r="V2" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="S2" s="67" t="s">
+      <c r="W2" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="T2" s="67" t="s">
+      <c r="X2" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="U2" s="67" t="s">
+      <c r="Y2" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="V2" s="96" t="s">
+      <c r="Z2" s="90" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B3" s="65" t="s">
         <v>64</v>
       </c>
@@ -2338,7 +2371,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="66">
-        <f>+T3-SUM(C3:E3)</f>
+        <f>+X3-SUM(C3:E3)</f>
         <v>112.19999999999999</v>
       </c>
       <c r="G3" s="66">
@@ -2351,7 +2384,7 @@
         <v>165.8</v>
       </c>
       <c r="J3" s="66">
-        <f>+U3-SUM(G3:I3)</f>
+        <f>+Y3-SUM(G3:I3)</f>
         <v>147.39999999999992</v>
       </c>
       <c r="K3" s="66">
@@ -2364,38 +2397,40 @@
         <v>213.3</v>
       </c>
       <c r="N3" s="66">
-        <f>+V3-SUM(K3:M3)</f>
+        <f>+Z3-SUM(K3:M3)</f>
         <v>183</v>
       </c>
-      <c r="O3" s="66"/>
-      <c r="P3" s="66">
+      <c r="O3" s="66">
+        <v>207.1</v>
+      </c>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="66"/>
+      <c r="T3" s="66">
         <f>128.344+9.148</f>
         <v>137.49199999999999</v>
       </c>
-      <c r="Q3" s="66">
+      <c r="U3" s="66">
         <f>187.51+6.697</f>
         <v>194.20699999999999</v>
       </c>
-      <c r="R3" s="66">
+      <c r="V3" s="66">
         <f>260.4+12</f>
         <v>272.39999999999998</v>
       </c>
-      <c r="S3" s="66">
+      <c r="W3" s="66">
         <v>378.1</v>
       </c>
-      <c r="T3" s="66">
+      <c r="X3" s="66">
         <v>488.7</v>
       </c>
-      <c r="U3" s="66">
+      <c r="Y3" s="66">
         <v>577.79999999999995</v>
       </c>
-      <c r="V3" s="66">
+      <c r="Z3" s="66">
         <v>762.7</v>
       </c>
-      <c r="W3" s="66"/>
-      <c r="X3" s="66"/>
-      <c r="Y3" s="66"/>
-      <c r="Z3" s="66"/>
       <c r="AA3" s="66"/>
       <c r="AB3" s="66"/>
       <c r="AC3" s="66"/>
@@ -2415,8 +2450,12 @@
       <c r="AQ3" s="66"/>
       <c r="AR3" s="66"/>
       <c r="AS3" s="66"/>
-    </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT3" s="66"/>
+      <c r="AU3" s="66"/>
+      <c r="AV3" s="66"/>
+      <c r="AW3" s="66"/>
+    </row>
+    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B4" s="65" t="s">
         <v>65</v>
       </c>
@@ -2430,7 +2469,7 @@
         <v>294.89999999999998</v>
       </c>
       <c r="F4" s="66">
-        <f t="shared" ref="F4:F20" si="0">+T4-SUM(C4:E4)</f>
+        <f t="shared" ref="F4:F20" si="0">+X4-SUM(C4:E4)</f>
         <v>300.50000000000011</v>
       </c>
       <c r="G4" s="66">
@@ -2443,7 +2482,7 @@
         <v>395.5</v>
       </c>
       <c r="J4" s="66">
-        <f t="shared" ref="J4:J21" si="1">+U4-SUM(G4:I4)</f>
+        <f t="shared" ref="J4:J21" si="1">+Y4-SUM(G4:I4)</f>
         <v>385.20000000000005</v>
       </c>
       <c r="K4" s="66">
@@ -2456,35 +2495,37 @@
         <v>436.2</v>
       </c>
       <c r="N4" s="66">
-        <f t="shared" ref="N4:N11" si="2">+V4-SUM(K4:M4)</f>
+        <f t="shared" ref="N4:N11" si="2">+Z4-SUM(K4:M4)</f>
         <v>434.19999999999982</v>
       </c>
-      <c r="O4" s="66"/>
-      <c r="P4" s="66">
+      <c r="O4" s="66">
+        <v>450.7</v>
+      </c>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="66"/>
+      <c r="R4" s="66"/>
+      <c r="S4" s="66"/>
+      <c r="T4" s="66">
         <v>111.761</v>
       </c>
-      <c r="Q4" s="66">
+      <c r="U4" s="66">
         <v>208.089</v>
       </c>
-      <c r="R4" s="66">
+      <c r="V4" s="66">
         <v>409.5</v>
       </c>
-      <c r="S4" s="66">
+      <c r="W4" s="66">
         <v>763.8</v>
       </c>
-      <c r="T4" s="66">
+      <c r="X4" s="66">
         <v>1162.2</v>
       </c>
-      <c r="U4" s="66">
+      <c r="Y4" s="66">
         <v>1480.3</v>
       </c>
-      <c r="V4" s="66">
+      <c r="Z4" s="66">
         <v>1740.1</v>
       </c>
-      <c r="W4" s="66"/>
-      <c r="X4" s="66"/>
-      <c r="Y4" s="66"/>
-      <c r="Z4" s="66"/>
       <c r="AA4" s="66"/>
       <c r="AB4" s="66"/>
       <c r="AC4" s="66"/>
@@ -2504,8 +2545,12 @@
       <c r="AQ4" s="66"/>
       <c r="AR4" s="66"/>
       <c r="AS4" s="66"/>
-    </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT4" s="66"/>
+      <c r="AU4" s="66"/>
+      <c r="AV4" s="66"/>
+      <c r="AW4" s="66"/>
+    </row>
+    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B5" s="65" t="s">
         <v>26</v>
       </c>
@@ -2548,33 +2593,35 @@
         <f t="shared" si="2"/>
         <v>126.39999999999998</v>
       </c>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66">
+      <c r="O5" s="66">
+        <v>174</v>
+      </c>
+      <c r="P5" s="66"/>
+      <c r="Q5" s="66"/>
+      <c r="R5" s="66"/>
+      <c r="S5" s="66"/>
+      <c r="T5" s="66">
         <v>17.867000000000001</v>
       </c>
-      <c r="Q5" s="66">
+      <c r="U5" s="66">
         <v>22.998999999999999</v>
       </c>
-      <c r="R5" s="66">
+      <c r="V5" s="66">
         <f>42.7</f>
         <v>42.7</v>
       </c>
-      <c r="S5" s="66">
+      <c r="W5" s="66">
         <v>80.2</v>
       </c>
-      <c r="T5" s="66">
+      <c r="X5" s="66">
         <v>141.1</v>
       </c>
-      <c r="U5" s="66">
+      <c r="Y5" s="66">
         <v>260.2</v>
       </c>
-      <c r="V5" s="66">
+      <c r="Z5" s="66">
         <v>511.1</v>
       </c>
-      <c r="W5" s="66"/>
-      <c r="X5" s="66"/>
-      <c r="Y5" s="66"/>
-      <c r="Z5" s="66"/>
       <c r="AA5" s="66"/>
       <c r="AB5" s="66"/>
       <c r="AC5" s="66"/>
@@ -2594,8 +2641,12 @@
       <c r="AQ5" s="66"/>
       <c r="AR5" s="66"/>
       <c r="AS5" s="66"/>
-    </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT5" s="66"/>
+      <c r="AU5" s="66"/>
+      <c r="AV5" s="66"/>
+      <c r="AW5" s="66"/>
+    </row>
+    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B6" s="65" t="s">
         <v>27</v>
       </c>
@@ -2638,32 +2689,34 @@
         <f t="shared" si="2"/>
         <v>687.30000000000018</v>
       </c>
-      <c r="O6" s="66"/>
-      <c r="P6" s="66">
+      <c r="O6" s="66">
+        <v>763.7</v>
+      </c>
+      <c r="P6" s="66"/>
+      <c r="Q6" s="66"/>
+      <c r="R6" s="66"/>
+      <c r="S6" s="66"/>
+      <c r="T6" s="66">
         <v>255.61199999999999</v>
       </c>
-      <c r="Q6" s="66">
+      <c r="U6" s="66">
         <v>406.39</v>
       </c>
-      <c r="R6" s="66">
+      <c r="V6" s="66">
         <v>683.3</v>
       </c>
-      <c r="S6" s="66">
+      <c r="W6" s="66">
         <v>1167.5</v>
       </c>
-      <c r="T6" s="66">
+      <c r="X6" s="66">
         <v>1711.4</v>
       </c>
-      <c r="U6" s="66">
+      <c r="Y6" s="66">
         <v>2199.6</v>
       </c>
-      <c r="V6" s="66">
+      <c r="Z6" s="66">
         <v>2804.4</v>
       </c>
-      <c r="W6" s="66"/>
-      <c r="X6" s="66"/>
-      <c r="Y6" s="66"/>
-      <c r="Z6" s="66"/>
       <c r="AA6" s="66"/>
       <c r="AB6" s="66"/>
       <c r="AC6" s="66"/>
@@ -2683,8 +2736,12 @@
       <c r="AQ6" s="66"/>
       <c r="AR6" s="66"/>
       <c r="AS6" s="66"/>
-    </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT6" s="66"/>
+      <c r="AU6" s="66"/>
+      <c r="AV6" s="66"/>
+      <c r="AW6" s="66"/>
+    </row>
+    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B7" s="65" t="s">
         <v>28</v>
       </c>
@@ -2727,32 +2784,34 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="O7" s="66"/>
-      <c r="P7" s="66">
+      <c r="O7" s="66">
+        <v>55.3</v>
+      </c>
+      <c r="P7" s="66"/>
+      <c r="Q7" s="66"/>
+      <c r="R7" s="66"/>
+      <c r="S7" s="66"/>
+      <c r="T7" s="66">
         <v>9.57</v>
       </c>
-      <c r="Q7" s="66">
+      <c r="U7" s="66">
         <v>15.75</v>
       </c>
-      <c r="R7" s="66">
+      <c r="V7" s="66">
         <v>36.299999999999997</v>
       </c>
-      <c r="S7" s="66">
+      <c r="W7" s="66">
         <v>47.3</v>
       </c>
-      <c r="T7" s="66">
+      <c r="X7" s="66">
         <v>68.900000000000006</v>
       </c>
-      <c r="U7" s="66">
+      <c r="Y7" s="66">
         <v>101</v>
       </c>
-      <c r="V7" s="66">
+      <c r="Z7" s="66">
         <v>169.9</v>
       </c>
-      <c r="W7" s="66"/>
-      <c r="X7" s="66"/>
-      <c r="Y7" s="66"/>
-      <c r="Z7" s="66"/>
       <c r="AA7" s="66"/>
       <c r="AB7" s="66"/>
       <c r="AC7" s="66"/>
@@ -2772,8 +2831,12 @@
       <c r="AQ7" s="66"/>
       <c r="AR7" s="66"/>
       <c r="AS7" s="66"/>
-    </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT7" s="66"/>
+      <c r="AU7" s="66"/>
+      <c r="AV7" s="66"/>
+      <c r="AW7" s="66"/>
+    </row>
+    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B8" s="65" t="s">
         <v>29</v>
       </c>
@@ -2816,32 +2879,34 @@
         <f t="shared" si="2"/>
         <v>11.3</v>
       </c>
-      <c r="O8" s="66"/>
-      <c r="P8" s="66">
+      <c r="O8" s="66">
+        <v>12.9</v>
+      </c>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="66"/>
+      <c r="T8" s="66">
         <v>1.9379999999999999</v>
       </c>
-      <c r="Q8" s="66">
+      <c r="U8" s="66">
         <v>3.1549999999999998</v>
       </c>
-      <c r="R8" s="66">
+      <c r="V8" s="66">
         <v>5</v>
       </c>
-      <c r="S8" s="66">
+      <c r="W8" s="66">
         <v>7.4</v>
       </c>
-      <c r="T8" s="66">
+      <c r="X8" s="66">
         <v>11.8</v>
       </c>
-      <c r="U8" s="66">
+      <c r="Y8" s="66">
         <v>17.7</v>
       </c>
-      <c r="V8" s="66">
+      <c r="Z8" s="66">
         <v>39.6</v>
       </c>
-      <c r="W8" s="66"/>
-      <c r="X8" s="66"/>
-      <c r="Y8" s="66"/>
-      <c r="Z8" s="66"/>
       <c r="AA8" s="66"/>
       <c r="AB8" s="66"/>
       <c r="AC8" s="66"/>
@@ -2861,8 +2926,12 @@
       <c r="AQ8" s="66"/>
       <c r="AR8" s="66"/>
       <c r="AS8" s="66"/>
-    </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT8" s="66"/>
+      <c r="AU8" s="66"/>
+      <c r="AV8" s="66"/>
+      <c r="AW8" s="66"/>
+    </row>
+    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B9" s="65" t="s">
         <v>24</v>
       </c>
@@ -2905,32 +2974,34 @@
         <f t="shared" si="2"/>
         <v>383.09999999999991</v>
       </c>
-      <c r="O9" s="66"/>
-      <c r="P9" s="66">
+      <c r="O9" s="66">
+        <v>509.6</v>
+      </c>
+      <c r="P9" s="66"/>
+      <c r="Q9" s="66"/>
+      <c r="R9" s="66"/>
+      <c r="S9" s="66"/>
+      <c r="T9" s="66">
         <v>200.71600000000001</v>
       </c>
-      <c r="Q9" s="66">
+      <c r="U9" s="66">
         <v>264.81900000000002</v>
       </c>
-      <c r="R9" s="66">
+      <c r="V9" s="66">
         <v>448.8</v>
       </c>
-      <c r="S9" s="66">
+      <c r="W9" s="66">
         <v>777</v>
       </c>
-      <c r="T9" s="66">
+      <c r="X9" s="66">
         <v>1120.3</v>
       </c>
-      <c r="U9" s="66">
+      <c r="Y9" s="66">
         <v>1375.5</v>
       </c>
-      <c r="V9" s="66">
+      <c r="Z9" s="66">
         <v>1753.4</v>
       </c>
-      <c r="W9" s="66"/>
-      <c r="X9" s="66"/>
-      <c r="Y9" s="66"/>
-      <c r="Z9" s="66"/>
       <c r="AA9" s="66"/>
       <c r="AB9" s="66"/>
       <c r="AC9" s="66"/>
@@ -2950,8 +3021,12 @@
       <c r="AQ9" s="66"/>
       <c r="AR9" s="66"/>
       <c r="AS9" s="66"/>
-    </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT9" s="66"/>
+      <c r="AU9" s="66"/>
+      <c r="AV9" s="66"/>
+      <c r="AW9" s="66"/>
+    </row>
+    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B10" s="65" t="s">
         <v>25</v>
       </c>
@@ -2994,32 +3069,34 @@
         <f t="shared" si="2"/>
         <v>360.59999999999991</v>
       </c>
-      <c r="O10" s="66"/>
-      <c r="P10" s="66">
+      <c r="O10" s="66">
+        <v>322.3</v>
+      </c>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="66"/>
+      <c r="R10" s="66"/>
+      <c r="S10" s="66"/>
+      <c r="T10" s="66">
         <v>66.403999999999996</v>
       </c>
-      <c r="Q10" s="66">
+      <c r="U10" s="66">
         <v>160.476</v>
       </c>
-      <c r="R10" s="66">
+      <c r="V10" s="66">
         <v>275.8</v>
       </c>
-      <c r="S10" s="66">
+      <c r="W10" s="66">
         <v>445.1</v>
       </c>
-      <c r="T10" s="66">
+      <c r="X10" s="66">
         <v>671.8</v>
       </c>
-      <c r="U10" s="66">
+      <c r="Y10" s="66">
         <v>942.8</v>
       </c>
-      <c r="V10" s="66">
+      <c r="Z10" s="66">
         <v>1260.5</v>
       </c>
-      <c r="W10" s="66"/>
-      <c r="X10" s="66"/>
-      <c r="Y10" s="66"/>
-      <c r="Z10" s="66"/>
       <c r="AA10" s="66"/>
       <c r="AB10" s="66"/>
       <c r="AC10" s="66"/>
@@ -3035,8 +3112,12 @@
       <c r="AM10" s="66"/>
       <c r="AN10" s="66"/>
       <c r="AO10" s="66"/>
-    </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AP10" s="66"/>
+      <c r="AQ10" s="66"/>
+      <c r="AR10" s="66"/>
+      <c r="AS10" s="66"/>
+    </row>
+    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B11" s="64" t="s">
         <v>21</v>
       </c>
@@ -3075,36 +3156,38 @@
       <c r="M11" s="81">
         <v>794.4</v>
       </c>
-      <c r="N11" s="66">
+      <c r="N11" s="81">
         <f t="shared" si="2"/>
         <v>743.79999999999973</v>
       </c>
-      <c r="O11" s="66"/>
-      <c r="P11" s="81">
+      <c r="O11" s="81">
+        <v>831.9</v>
+      </c>
+      <c r="P11" s="66"/>
+      <c r="Q11" s="66"/>
+      <c r="R11" s="66"/>
+      <c r="S11" s="66"/>
+      <c r="T11" s="81">
         <v>267.12</v>
       </c>
-      <c r="Q11" s="81">
+      <c r="U11" s="81">
         <v>425.29</v>
       </c>
-      <c r="R11" s="81">
+      <c r="V11" s="81">
         <v>724.6</v>
       </c>
-      <c r="S11" s="81">
+      <c r="W11" s="81">
         <v>1222.0999999999999</v>
       </c>
-      <c r="T11" s="81">
+      <c r="X11" s="81">
         <v>1792.1</v>
       </c>
-      <c r="U11" s="81">
+      <c r="Y11" s="81">
         <v>2318.3000000000002</v>
       </c>
-      <c r="V11" s="81">
+      <c r="Z11" s="81">
         <v>3014</v>
       </c>
-      <c r="W11" s="66"/>
-      <c r="X11" s="66"/>
-      <c r="Y11" s="66"/>
-      <c r="Z11" s="66"/>
       <c r="AA11" s="66"/>
       <c r="AB11" s="66"/>
       <c r="AC11" s="66"/>
@@ -3120,8 +3203,12 @@
       <c r="AM11" s="66"/>
       <c r="AN11" s="66"/>
       <c r="AO11" s="66"/>
-    </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AP11" s="66"/>
+      <c r="AQ11" s="66"/>
+      <c r="AR11" s="66"/>
+      <c r="AS11" s="66"/>
+    </row>
+    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B12" s="65" t="s">
         <v>22</v>
       </c>
@@ -3161,35 +3248,37 @@
         <v>272.10000000000002</v>
       </c>
       <c r="N12" s="66">
-        <f>+V12-SUM(K12:M12)</f>
+        <f>+Z12-SUM(K12:M12)</f>
         <v>268.49999999999989</v>
       </c>
-      <c r="O12" s="66"/>
-      <c r="P12" s="66">
+      <c r="O12" s="66">
+        <v>297.60000000000002</v>
+      </c>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66"/>
+      <c r="R12" s="66"/>
+      <c r="S12" s="66"/>
+      <c r="T12" s="66">
         <v>124.003</v>
       </c>
-      <c r="Q12" s="66">
+      <c r="U12" s="66">
         <v>194.19</v>
       </c>
-      <c r="R12" s="66">
+      <c r="V12" s="66">
         <v>294.3</v>
       </c>
-      <c r="S12" s="66">
+      <c r="W12" s="66">
         <v>537.20000000000005</v>
       </c>
-      <c r="T12" s="66">
+      <c r="X12" s="66">
         <v>724.8</v>
       </c>
-      <c r="U12" s="66">
+      <c r="Y12" s="66">
         <v>912.6</v>
       </c>
-      <c r="V12" s="66">
+      <c r="Z12" s="66">
         <v>1120.3</v>
       </c>
-      <c r="W12" s="66"/>
-      <c r="X12" s="66"/>
-      <c r="Y12" s="66"/>
-      <c r="Z12" s="66"/>
       <c r="AA12" s="66"/>
       <c r="AB12" s="66"/>
       <c r="AC12" s="66"/>
@@ -3205,8 +3294,12 @@
       <c r="AM12" s="66"/>
       <c r="AN12" s="66"/>
       <c r="AO12" s="66"/>
-    </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AP12" s="66"/>
+      <c r="AQ12" s="66"/>
+      <c r="AR12" s="66"/>
+      <c r="AS12" s="66"/>
+    </row>
+    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B13" s="65" t="s">
         <v>23</v>
       </c>
@@ -3239,7 +3332,7 @@
         <v>385.29999999999995</v>
       </c>
       <c r="J13" s="66">
-        <f t="shared" ref="J13:N13" si="4">+J11-J12</f>
+        <f t="shared" ref="J13:O13" si="4">+J11-J12</f>
         <v>376.80000000000007</v>
       </c>
       <c r="K13" s="66">
@@ -3258,39 +3351,42 @@
         <f t="shared" si="4"/>
         <v>475.29999999999984</v>
       </c>
-      <c r="O13" s="66"/>
-      <c r="P13" s="66">
-        <f t="shared" ref="P13:T13" si="5">+P11-P12</f>
+      <c r="O13" s="66">
+        <f t="shared" si="4"/>
+        <v>534.29999999999995</v>
+      </c>
+      <c r="P13" s="66"/>
+      <c r="Q13" s="66"/>
+      <c r="R13" s="66"/>
+      <c r="S13" s="66"/>
+      <c r="T13" s="66">
+        <f t="shared" ref="T13:X13" si="5">+T11-T12</f>
         <v>143.11700000000002</v>
       </c>
-      <c r="Q13" s="66">
+      <c r="U13" s="66">
         <f t="shared" si="5"/>
         <v>231.10000000000002</v>
       </c>
-      <c r="R13" s="66">
+      <c r="V13" s="66">
         <f t="shared" si="5"/>
         <v>430.3</v>
       </c>
-      <c r="S13" s="66">
+      <c r="W13" s="66">
         <f t="shared" si="5"/>
         <v>684.89999999999986</v>
       </c>
-      <c r="T13" s="66">
+      <c r="X13" s="66">
         <f t="shared" si="5"/>
         <v>1067.3</v>
       </c>
-      <c r="U13" s="66">
-        <f>+U11-U12</f>
+      <c r="Y13" s="66">
+        <f>+Y11-Y12</f>
         <v>1405.7000000000003</v>
       </c>
-      <c r="V13" s="66">
-        <f>+V11-V12</f>
+      <c r="Z13" s="66">
+        <f>+Z11-Z12</f>
         <v>1893.7</v>
       </c>
-      <c r="W13" s="66"/>
-      <c r="X13" s="66"/>
-      <c r="Y13" s="66"/>
-      <c r="Z13" s="66"/>
       <c r="AA13" s="66"/>
       <c r="AB13" s="66"/>
       <c r="AC13" s="66"/>
@@ -3306,8 +3402,12 @@
       <c r="AM13" s="66"/>
       <c r="AN13" s="66"/>
       <c r="AO13" s="66"/>
-    </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AP13" s="66"/>
+      <c r="AQ13" s="66"/>
+      <c r="AR13" s="66"/>
+      <c r="AS13" s="66"/>
+    </row>
+    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B14" s="65" t="s">
         <v>30</v>
       </c>
@@ -3347,35 +3447,37 @@
         <v>397.5</v>
       </c>
       <c r="N14" s="66">
-        <f>+V14-SUM(K14:M14)</f>
+        <f>+Z14-SUM(K14:M14)</f>
         <v>392.89999999999986</v>
       </c>
-      <c r="O14" s="66"/>
-      <c r="P14" s="66">
+      <c r="O14" s="66">
+        <v>416.9</v>
+      </c>
+      <c r="P14" s="66"/>
+      <c r="Q14" s="66"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="66"/>
+      <c r="T14" s="66">
         <v>137.428</v>
       </c>
-      <c r="Q14" s="66">
+      <c r="U14" s="66">
         <v>248.19900000000001</v>
       </c>
-      <c r="R14" s="66">
+      <c r="V14" s="66">
         <v>571.4</v>
       </c>
-      <c r="S14" s="66">
+      <c r="W14" s="66">
         <v>599.79999999999995</v>
       </c>
-      <c r="T14" s="66">
+      <c r="X14" s="66">
         <v>887</v>
       </c>
-      <c r="U14" s="66">
+      <c r="Y14" s="66">
         <v>1194.2</v>
       </c>
-      <c r="V14" s="66">
+      <c r="Z14" s="66">
         <v>1516.6</v>
       </c>
-      <c r="W14" s="66"/>
-      <c r="X14" s="66"/>
-      <c r="Y14" s="66"/>
-      <c r="Z14" s="66"/>
       <c r="AA14" s="66"/>
       <c r="AB14" s="66"/>
       <c r="AC14" s="66"/>
@@ -3391,8 +3493,12 @@
       <c r="AM14" s="66"/>
       <c r="AN14" s="66"/>
       <c r="AO14" s="66"/>
-    </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AP14" s="66"/>
+      <c r="AQ14" s="66"/>
+      <c r="AR14" s="66"/>
+      <c r="AS14" s="66"/>
+    </row>
+    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B15" s="65" t="s">
         <v>31</v>
       </c>
@@ -3425,7 +3531,7 @@
         <v>72.599999999999966</v>
       </c>
       <c r="J15" s="66">
-        <f t="shared" ref="J15:N15" si="7">+J13-J14</f>
+        <f t="shared" ref="J15:O15" si="7">+J13-J14</f>
         <v>53.000000000000114</v>
       </c>
       <c r="K15" s="66">
@@ -3444,39 +3550,42 @@
         <f t="shared" si="7"/>
         <v>82.399999999999977</v>
       </c>
-      <c r="O15" s="66"/>
-      <c r="P15" s="66">
-        <f t="shared" ref="P15:R15" si="8">+P13-P14</f>
+      <c r="O15" s="66">
+        <f t="shared" si="7"/>
+        <v>117.39999999999998</v>
+      </c>
+      <c r="P15" s="66"/>
+      <c r="Q15" s="66"/>
+      <c r="R15" s="66"/>
+      <c r="S15" s="66"/>
+      <c r="T15" s="66">
+        <f t="shared" ref="T15:V15" si="8">+T13-T14</f>
         <v>5.6890000000000214</v>
       </c>
-      <c r="Q15" s="66">
+      <c r="U15" s="66">
         <f t="shared" si="8"/>
         <v>-17.09899999999999</v>
       </c>
-      <c r="R15" s="66">
+      <c r="V15" s="66">
         <f t="shared" si="8"/>
         <v>-141.09999999999997</v>
       </c>
-      <c r="S15" s="66">
-        <f>+S13-S14</f>
+      <c r="W15" s="66">
+        <f>+W13-W14</f>
         <v>85.099999999999909</v>
       </c>
-      <c r="T15" s="66">
-        <f>+T13-T14</f>
+      <c r="X15" s="66">
+        <f>+X13-X14</f>
         <v>180.29999999999995</v>
       </c>
-      <c r="U15" s="66">
-        <f>+U13-U14</f>
+      <c r="Y15" s="66">
+        <f>+Y13-Y14</f>
         <v>211.50000000000023</v>
       </c>
-      <c r="V15" s="66">
-        <f>+V13-V14</f>
+      <c r="Z15" s="66">
+        <f>+Z13-Z14</f>
         <v>377.10000000000014</v>
       </c>
-      <c r="W15" s="66"/>
-      <c r="X15" s="66"/>
-      <c r="Y15" s="66"/>
-      <c r="Z15" s="66"/>
       <c r="AA15" s="66"/>
       <c r="AB15" s="66"/>
       <c r="AC15" s="66"/>
@@ -3492,8 +3601,12 @@
       <c r="AM15" s="66"/>
       <c r="AN15" s="66"/>
       <c r="AO15" s="66"/>
-    </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AP15" s="66"/>
+      <c r="AQ15" s="66"/>
+      <c r="AR15" s="66"/>
+      <c r="AS15" s="66"/>
+    </row>
+    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B16" s="65" t="s">
         <v>32</v>
       </c>
@@ -3533,35 +3646,37 @@
         <v>8.1</v>
       </c>
       <c r="N16" s="66">
-        <f>+V16-SUM(K16:M16)</f>
+        <f>+Z16-SUM(K16:M16)</f>
         <v>8</v>
       </c>
-      <c r="O16" s="66"/>
-      <c r="P16" s="66">
+      <c r="O16" s="66">
+        <v>7</v>
+      </c>
+      <c r="P16" s="66"/>
+      <c r="Q16" s="66"/>
+      <c r="R16" s="66"/>
+      <c r="S16" s="66"/>
+      <c r="T16" s="66">
         <v>4.7E-2</v>
       </c>
-      <c r="Q16" s="66">
+      <c r="U16" s="66">
         <v>2.7E-2</v>
       </c>
-      <c r="R16" s="66">
+      <c r="V16" s="66">
         <v>0</v>
       </c>
-      <c r="S16" s="66">
+      <c r="W16" s="66">
         <v>5.7</v>
       </c>
-      <c r="T16" s="66">
+      <c r="X16" s="66">
         <v>11.5</v>
       </c>
-      <c r="U16" s="66">
+      <c r="Y16" s="66">
         <v>23.5</v>
       </c>
-      <c r="V16" s="66">
+      <c r="Z16" s="66">
         <v>30.9</v>
       </c>
-      <c r="W16" s="66"/>
-      <c r="X16" s="66"/>
-      <c r="Y16" s="66"/>
-      <c r="Z16" s="66"/>
       <c r="AA16" s="66"/>
       <c r="AB16" s="66"/>
       <c r="AC16" s="66"/>
@@ -3577,8 +3692,12 @@
       <c r="AM16" s="66"/>
       <c r="AN16" s="66"/>
       <c r="AO16" s="66"/>
-    </row>
-    <row r="17" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP16" s="66"/>
+      <c r="AQ16" s="66"/>
+      <c r="AR16" s="66"/>
+      <c r="AS16" s="66"/>
+    </row>
+    <row r="17" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B17" s="65" t="s">
         <v>33</v>
       </c>
@@ -3618,35 +3737,37 @@
         <v>8.1</v>
       </c>
       <c r="N17" s="66">
-        <f>+V17-SUM(K17:M17)</f>
+        <f>+Z17-SUM(K17:M17)</f>
         <v>7.8999999999999986</v>
       </c>
-      <c r="O17" s="66"/>
-      <c r="P17" s="66">
+      <c r="O17" s="66">
+        <v>8</v>
+      </c>
+      <c r="P17" s="66"/>
+      <c r="Q17" s="66"/>
+      <c r="R17" s="66"/>
+      <c r="S17" s="66"/>
+      <c r="T17" s="66">
         <v>0.69699999999999995</v>
       </c>
-      <c r="Q17" s="66">
+      <c r="U17" s="66">
         <v>0.93</v>
       </c>
-      <c r="R17" s="66">
+      <c r="V17" s="66">
         <v>3.6</v>
       </c>
-      <c r="S17" s="66">
+      <c r="W17" s="66">
         <v>6.4</v>
       </c>
-      <c r="T17" s="66">
+      <c r="X17" s="66">
         <v>11.3</v>
       </c>
-      <c r="U17" s="66">
+      <c r="Y17" s="66">
         <v>23.1</v>
       </c>
-      <c r="V17" s="66">
+      <c r="Z17" s="66">
         <v>29.6</v>
       </c>
-      <c r="W17" s="66"/>
-      <c r="X17" s="66"/>
-      <c r="Y17" s="66"/>
-      <c r="Z17" s="66"/>
       <c r="AA17" s="66"/>
       <c r="AB17" s="66"/>
       <c r="AC17" s="66"/>
@@ -3662,8 +3783,12 @@
       <c r="AM17" s="66"/>
       <c r="AN17" s="66"/>
       <c r="AO17" s="66"/>
-    </row>
-    <row r="18" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP17" s="66"/>
+      <c r="AQ17" s="66"/>
+      <c r="AR17" s="66"/>
+      <c r="AS17" s="66"/>
+    </row>
+    <row r="18" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B18" s="65" t="s">
         <v>34</v>
       </c>
@@ -3703,35 +3828,37 @@
         <v>6.1</v>
       </c>
       <c r="N18" s="66">
-        <f>+V18-SUM(K18:M18)</f>
+        <f>+Z18-SUM(K18:M18)</f>
         <v>-333.7</v>
       </c>
-      <c r="O18" s="66"/>
-      <c r="P18" s="66">
+      <c r="O18" s="115">
+        <v>0.3</v>
+      </c>
+      <c r="P18" s="66"/>
+      <c r="Q18" s="66"/>
+      <c r="R18" s="66"/>
+      <c r="S18" s="66"/>
+      <c r="T18" s="66">
         <v>-1.893</v>
       </c>
-      <c r="Q18" s="66">
+      <c r="U18" s="66">
         <v>-6.4340000000000002</v>
       </c>
-      <c r="R18" s="66">
+      <c r="V18" s="66">
         <v>-14.9</v>
       </c>
-      <c r="S18" s="66">
+      <c r="W18" s="66">
         <v>-6.5</v>
       </c>
-      <c r="T18" s="66">
+      <c r="X18" s="66">
         <v>-111.4</v>
       </c>
-      <c r="U18" s="66">
+      <c r="Y18" s="66">
         <v>67.7</v>
       </c>
-      <c r="V18" s="66">
+      <c r="Z18" s="66">
         <v>-173.2</v>
       </c>
-      <c r="W18" s="66"/>
-      <c r="X18" s="66"/>
-      <c r="Y18" s="66"/>
-      <c r="Z18" s="66"/>
       <c r="AA18" s="66"/>
       <c r="AB18" s="66"/>
       <c r="AC18" s="66"/>
@@ -3747,8 +3874,12 @@
       <c r="AM18" s="66"/>
       <c r="AN18" s="66"/>
       <c r="AO18" s="66"/>
-    </row>
-    <row r="19" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP18" s="66"/>
+      <c r="AQ18" s="66"/>
+      <c r="AR18" s="66"/>
+      <c r="AS18" s="66"/>
+    </row>
+    <row r="19" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B19" s="65" t="s">
         <v>35</v>
       </c>
@@ -3781,7 +3912,7 @@
         <v>29.499999999999964</v>
       </c>
       <c r="J19" s="66">
-        <f t="shared" ref="J19:N19" si="10">+J15+J16-J17-J18</f>
+        <f t="shared" ref="J19:O19" si="10">+J15+J16-J17-J18</f>
         <v>-43.899999999999892</v>
       </c>
       <c r="K19" s="66">
@@ -3800,39 +3931,42 @@
         <f t="shared" si="10"/>
         <v>416.19999999999993</v>
       </c>
-      <c r="O19" s="66"/>
-      <c r="P19" s="66">
-        <f t="shared" ref="P19:S19" si="11">+P15+P16-P17+P18</f>
+      <c r="O19" s="66">
+        <f t="shared" si="10"/>
+        <v>116.09999999999998</v>
+      </c>
+      <c r="P19" s="66"/>
+      <c r="Q19" s="66"/>
+      <c r="R19" s="66"/>
+      <c r="S19" s="66"/>
+      <c r="T19" s="66">
+        <f t="shared" ref="T19:W19" si="11">+T15+T16-T17+T18</f>
         <v>3.1460000000000212</v>
       </c>
-      <c r="Q19" s="66">
+      <c r="U19" s="66">
         <f t="shared" si="11"/>
         <v>-24.435999999999989</v>
       </c>
-      <c r="R19" s="66">
+      <c r="V19" s="66">
         <f t="shared" si="11"/>
         <v>-159.59999999999997</v>
       </c>
-      <c r="S19" s="66">
+      <c r="W19" s="66">
         <f t="shared" si="11"/>
         <v>77.899999999999906</v>
       </c>
-      <c r="T19" s="66">
-        <f>+T15+T16-T17+T18</f>
+      <c r="X19" s="66">
+        <f>+X15+X16-X17+X18</f>
         <v>69.099999999999937</v>
       </c>
-      <c r="U19" s="66">
-        <f>+U15+U16-U17+U18</f>
+      <c r="Y19" s="66">
+        <f>+Y15+Y16-Y17+Y18</f>
         <v>279.60000000000025</v>
       </c>
-      <c r="V19" s="66">
-        <f>+V15+V16-V17+V18</f>
+      <c r="Z19" s="66">
+        <f>+Z15+Z16-Z17+Z18</f>
         <v>205.2000000000001</v>
       </c>
-      <c r="W19" s="66"/>
-      <c r="X19" s="66"/>
-      <c r="Y19" s="66"/>
-      <c r="Z19" s="66"/>
       <c r="AA19" s="66"/>
       <c r="AB19" s="66"/>
       <c r="AC19" s="66"/>
@@ -3848,8 +3982,12 @@
       <c r="AM19" s="66"/>
       <c r="AN19" s="66"/>
       <c r="AO19" s="66"/>
-    </row>
-    <row r="20" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP19" s="66"/>
+      <c r="AQ19" s="66"/>
+      <c r="AR19" s="66"/>
+      <c r="AS19" s="66"/>
+    </row>
+    <row r="20" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B20" s="65" t="s">
         <v>58</v>
       </c>
@@ -3889,35 +4027,37 @@
         <v>-0.3</v>
       </c>
       <c r="N20" s="66">
-        <f>+V20-SUM(K20:M20)</f>
+        <f>+Z20-SUM(K20:M20)</f>
         <v>1.0000000000000002</v>
       </c>
-      <c r="O20" s="66"/>
-      <c r="P20" s="66">
+      <c r="O20" s="66">
+        <v>12.8</v>
+      </c>
+      <c r="P20" s="66"/>
+      <c r="Q20" s="66"/>
+      <c r="R20" s="66"/>
+      <c r="S20" s="66"/>
+      <c r="T20" s="66">
         <v>4.62</v>
       </c>
-      <c r="Q20" s="66">
+      <c r="U20" s="66">
         <v>3.0830000000000002</v>
       </c>
-      <c r="R20" s="66">
+      <c r="V20" s="66">
         <v>10.6</v>
       </c>
-      <c r="S20" s="66">
+      <c r="W20" s="66">
         <v>20.2</v>
       </c>
-      <c r="T20" s="66">
+      <c r="X20" s="66">
         <v>-10.5</v>
       </c>
-      <c r="U20" s="66">
+      <c r="Y20" s="66">
         <v>37.4</v>
       </c>
-      <c r="V20" s="66">
+      <c r="Z20" s="66">
         <v>1.5</v>
       </c>
-      <c r="W20" s="66"/>
-      <c r="X20" s="66"/>
-      <c r="Y20" s="66"/>
-      <c r="Z20" s="66"/>
       <c r="AA20" s="66"/>
       <c r="AB20" s="66"/>
       <c r="AC20" s="66"/>
@@ -3933,8 +4073,12 @@
       <c r="AM20" s="66"/>
       <c r="AN20" s="66"/>
       <c r="AO20" s="66"/>
-    </row>
-    <row r="21" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP20" s="66"/>
+      <c r="AQ20" s="66"/>
+      <c r="AR20" s="66"/>
+      <c r="AS20" s="66"/>
+    </row>
+    <row r="21" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B21" s="65" t="s">
         <v>36</v>
       </c>
@@ -3986,39 +4130,42 @@
         <f>+N19-N20</f>
         <v>415.19999999999993</v>
       </c>
-      <c r="O21" s="66"/>
-      <c r="P21" s="66">
-        <f t="shared" ref="P21:S21" si="13">+P19-P20</f>
+      <c r="O21" s="66">
+        <f>+O19-O20</f>
+        <v>103.29999999999998</v>
+      </c>
+      <c r="P21" s="66"/>
+      <c r="Q21" s="66"/>
+      <c r="R21" s="66"/>
+      <c r="S21" s="66"/>
+      <c r="T21" s="66">
+        <f t="shared" ref="T21:W21" si="13">+T19-T20</f>
         <v>-1.4739999999999789</v>
       </c>
-      <c r="Q21" s="66">
+      <c r="U21" s="66">
         <f t="shared" si="13"/>
         <v>-27.518999999999991</v>
       </c>
-      <c r="R21" s="66">
+      <c r="V21" s="66">
         <f t="shared" si="13"/>
         <v>-170.19999999999996</v>
       </c>
-      <c r="S21" s="66">
+      <c r="W21" s="66">
         <f t="shared" si="13"/>
         <v>57.699999999999903</v>
       </c>
-      <c r="T21" s="66">
-        <f>+T19-T20</f>
+      <c r="X21" s="66">
+        <f>+X19-X20</f>
         <v>79.599999999999937</v>
       </c>
-      <c r="U21" s="66">
-        <f>+U19-U20</f>
+      <c r="Y21" s="66">
+        <f>+Y19-Y20</f>
         <v>242.20000000000024</v>
       </c>
-      <c r="V21" s="66">
-        <f>+V19-V20</f>
+      <c r="Z21" s="66">
+        <f>+Z19-Z20</f>
         <v>203.7000000000001</v>
       </c>
-      <c r="W21" s="66"/>
-      <c r="X21" s="66"/>
-      <c r="Y21" s="66"/>
-      <c r="Z21" s="66"/>
       <c r="AA21" s="66"/>
       <c r="AB21" s="66"/>
       <c r="AC21" s="66"/>
@@ -4034,12 +4181,12 @@
       <c r="AM21" s="66"/>
       <c r="AN21" s="66"/>
       <c r="AO21" s="66"/>
-    </row>
-    <row r="22" spans="2:41" x14ac:dyDescent="0.2">
-      <c r="O22" s="66"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
+      <c r="AP21" s="66"/>
+      <c r="AQ21" s="66"/>
+      <c r="AR21" s="66"/>
+      <c r="AS21" s="66"/>
+    </row>
+    <row r="22" spans="2:45" x14ac:dyDescent="0.2">
       <c r="S22" s="66"/>
       <c r="T22" s="66"/>
       <c r="U22" s="66"/>
@@ -4063,8 +4210,12 @@
       <c r="AM22" s="66"/>
       <c r="AN22" s="66"/>
       <c r="AO22" s="66"/>
-    </row>
-    <row r="23" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP22" s="66"/>
+      <c r="AQ22" s="66"/>
+      <c r="AR22" s="66"/>
+      <c r="AS22" s="66"/>
+    </row>
+    <row r="23" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B23" s="65" t="s">
         <v>37</v>
       </c>
@@ -4097,7 +4248,7 @@
         <v>0.10547035930930765</v>
       </c>
       <c r="J23" s="82">
-        <f t="shared" ref="J23:N23" si="15">+J21/J24</f>
+        <f t="shared" ref="J23:O23" si="15">+J21/J24</f>
         <v>0.30865931272619346</v>
       </c>
       <c r="K23" s="82">
@@ -4116,37 +4267,40 @@
         <f t="shared" si="15"/>
         <v>1.4004671691335091</v>
       </c>
-      <c r="O23" s="66"/>
-      <c r="P23" s="83" t="s">
+      <c r="O23" s="82">
+        <f t="shared" si="15"/>
+        <v>0.34795982514469725</v>
+      </c>
+      <c r="P23" s="82"/>
+      <c r="Q23" s="82"/>
+      <c r="R23" s="82"/>
+      <c r="S23" s="66"/>
+      <c r="T23" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="Q23" s="83" t="s">
+      <c r="U23" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="R23" s="84">
-        <f t="shared" ref="R23:T23" si="16">+R21/R24</f>
+      <c r="V23" s="84">
+        <f t="shared" ref="V23:X23" si="16">+V21/V24</f>
         <v>-0.6442791449096904</v>
       </c>
-      <c r="S23" s="84">
+      <c r="W23" s="84">
         <f t="shared" si="16"/>
         <v>0.20446745803841362</v>
       </c>
-      <c r="T23" s="84">
+      <c r="X23" s="84">
         <f t="shared" si="16"/>
         <v>0.27951160025110511</v>
       </c>
-      <c r="U23" s="84">
-        <f>+U21/U24</f>
+      <c r="Y23" s="84">
+        <f>+Y21/Y24</f>
         <v>0.83621124767655408</v>
       </c>
-      <c r="V23" s="84">
-        <f>+V21/V24</f>
+      <c r="Z23" s="84">
+        <f>+Z21/Z24</f>
         <v>0.68615117504331924</v>
       </c>
-      <c r="W23" s="66"/>
-      <c r="X23" s="66"/>
-      <c r="Y23" s="66"/>
-      <c r="Z23" s="66"/>
       <c r="AA23" s="66"/>
       <c r="AB23" s="66"/>
       <c r="AC23" s="66"/>
@@ -4162,8 +4316,12 @@
       <c r="AM23" s="66"/>
       <c r="AN23" s="66"/>
       <c r="AO23" s="66"/>
-    </row>
-    <row r="24" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP23" s="66"/>
+      <c r="AQ23" s="66"/>
+      <c r="AR23" s="66"/>
+      <c r="AS23" s="66"/>
+    </row>
+    <row r="24" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B24" s="65" t="s">
         <v>3</v>
       </c>
@@ -4177,7 +4335,7 @@
         <v>284.12787700000001</v>
       </c>
       <c r="F24" s="66">
-        <f>+T24</f>
+        <f>+X24</f>
         <v>284.78245600000002</v>
       </c>
       <c r="G24" s="66">
@@ -4190,7 +4348,7 @@
         <v>288.23263900000001</v>
       </c>
       <c r="J24" s="66">
-        <f>+U24</f>
+        <f>+Y24</f>
         <v>289.63972999999999</v>
       </c>
       <c r="K24" s="66">
@@ -4205,32 +4363,34 @@
       <c r="N24" s="66">
         <v>296.47249799999997</v>
       </c>
-      <c r="O24" s="66"/>
-      <c r="P24" s="83" t="s">
+      <c r="O24" s="66">
+        <v>296.87335300000001</v>
+      </c>
+      <c r="P24" s="66"/>
+      <c r="Q24" s="66"/>
+      <c r="R24" s="66"/>
+      <c r="S24" s="66"/>
+      <c r="T24" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="Q24" s="83" t="s">
+      <c r="U24" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="R24" s="66">
+      <c r="V24" s="66">
         <v>264.17120799999998</v>
       </c>
-      <c r="S24" s="66">
+      <c r="W24" s="66">
         <v>282.19649500000003</v>
       </c>
-      <c r="T24" s="66">
+      <c r="X24" s="66">
         <v>284.78245600000002</v>
       </c>
-      <c r="U24" s="66">
+      <c r="Y24" s="66">
         <v>289.63972999999999</v>
       </c>
-      <c r="V24" s="66">
+      <c r="Z24" s="66">
         <v>296.87335300000001</v>
       </c>
-      <c r="W24" s="66"/>
-      <c r="X24" s="66"/>
-      <c r="Y24" s="66"/>
-      <c r="Z24" s="66"/>
       <c r="AA24" s="66"/>
       <c r="AB24" s="66"/>
       <c r="AC24" s="66"/>
@@ -4246,8 +4406,12 @@
       <c r="AM24" s="66"/>
       <c r="AN24" s="66"/>
       <c r="AO24" s="66"/>
-    </row>
-    <row r="25" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP24" s="66"/>
+      <c r="AQ24" s="66"/>
+      <c r="AR24" s="66"/>
+      <c r="AS24" s="66"/>
+    </row>
+    <row r="25" spans="2:45" x14ac:dyDescent="0.2">
       <c r="C25" s="66"/>
       <c r="D25" s="66"/>
       <c r="E25" s="66"/>
@@ -4286,8 +4450,12 @@
       <c r="AM25" s="66"/>
       <c r="AN25" s="66"/>
       <c r="AO25" s="66"/>
-    </row>
-    <row r="26" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP25" s="66"/>
+      <c r="AQ25" s="66"/>
+      <c r="AR25" s="66"/>
+      <c r="AS25" s="66"/>
+    </row>
+    <row r="26" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B26" s="65" t="s">
         <v>42</v>
       </c>
@@ -4308,7 +4476,7 @@
         <v>0.15138888888888902</v>
       </c>
       <c r="J26" s="85">
-        <f t="shared" ref="J26:N34" si="19">+J3/F3-1</f>
+        <f t="shared" ref="J26:O34" si="19">+J3/F3-1</f>
         <v>0.31372549019607776</v>
       </c>
       <c r="K26" s="85">
@@ -4327,38 +4495,41 @@
         <f t="shared" si="19"/>
         <v>0.24151967435549593</v>
       </c>
-      <c r="O26" s="66"/>
-      <c r="P26" s="83" t="s">
+      <c r="O26" s="85">
+        <f t="shared" si="19"/>
+        <v>0.22835112692763948</v>
+      </c>
+      <c r="P26" s="85"/>
+      <c r="Q26" s="85"/>
+      <c r="R26" s="85"/>
+      <c r="S26" s="66"/>
+      <c r="T26" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="Q26" s="85">
-        <f t="shared" ref="Q26:Q34" si="20">+Q3/P3-1</f>
+      <c r="U26" s="85">
+        <f t="shared" ref="U26:U34" si="20">+U3/T3-1</f>
         <v>0.41249672708230301</v>
       </c>
-      <c r="R26" s="85">
-        <f t="shared" ref="R26:R34" si="21">+R3/Q3-1</f>
+      <c r="V26" s="85">
+        <f t="shared" ref="V26:V34" si="21">+V3/U3-1</f>
         <v>0.40262709377107919</v>
       </c>
-      <c r="S26" s="85">
-        <f t="shared" ref="S26:T34" si="22">+S3/R3-1</f>
+      <c r="W26" s="85">
+        <f t="shared" ref="W26:X34" si="22">+W3/V3-1</f>
         <v>0.38803230543318668</v>
       </c>
-      <c r="T26" s="85">
+      <c r="X26" s="85">
         <f t="shared" si="22"/>
         <v>0.29251520761703231</v>
       </c>
-      <c r="U26" s="85">
-        <f>+U3/T3-1</f>
+      <c r="Y26" s="85">
+        <f>+Y3/X3-1</f>
         <v>0.18232044198895014</v>
       </c>
-      <c r="V26" s="85">
-        <f>+V3/U3-1</f>
+      <c r="Z26" s="85">
+        <f>+Z3/Y3-1</f>
         <v>0.32000692281066123</v>
       </c>
-      <c r="W26" s="66"/>
-      <c r="X26" s="66"/>
-      <c r="Y26" s="66"/>
-      <c r="Z26" s="66"/>
       <c r="AA26" s="66"/>
       <c r="AB26" s="66"/>
       <c r="AC26" s="66"/>
@@ -4374,8 +4545,12 @@
       <c r="AM26" s="66"/>
       <c r="AN26" s="66"/>
       <c r="AO26" s="66"/>
-    </row>
-    <row r="27" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP26" s="66"/>
+      <c r="AQ26" s="66"/>
+      <c r="AR26" s="66"/>
+      <c r="AS26" s="66"/>
+    </row>
+    <row r="27" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B27" s="65" t="s">
         <v>43</v>
       </c>
@@ -4415,38 +4590,41 @@
         <f t="shared" si="19"/>
         <v>0.12720664589823416</v>
       </c>
-      <c r="O27" s="66"/>
-      <c r="P27" s="83" t="s">
+      <c r="O27" s="85">
+        <f t="shared" si="19"/>
+        <v>3.0406950160036583E-2</v>
+      </c>
+      <c r="P27" s="85"/>
+      <c r="Q27" s="85"/>
+      <c r="R27" s="85"/>
+      <c r="S27" s="66"/>
+      <c r="T27" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="Q27" s="85">
+      <c r="U27" s="85">
         <f t="shared" si="20"/>
         <v>0.86191068440690399</v>
       </c>
-      <c r="R27" s="85">
+      <c r="V27" s="85">
         <f t="shared" si="21"/>
         <v>0.9679079624583713</v>
       </c>
-      <c r="S27" s="85">
+      <c r="W27" s="85">
         <f t="shared" si="22"/>
         <v>0.86520146520146501</v>
       </c>
-      <c r="T27" s="85">
+      <c r="X27" s="85">
         <f t="shared" si="22"/>
         <v>0.52160251374705435</v>
       </c>
-      <c r="U27" s="85">
-        <f t="shared" ref="U27:V34" si="24">+U4/T4-1</f>
+      <c r="Y27" s="85">
+        <f t="shared" ref="Y27:Z34" si="24">+Y4/X4-1</f>
         <v>0.273705042161418</v>
       </c>
-      <c r="V27" s="85">
+      <c r="Z27" s="85">
         <f t="shared" si="24"/>
         <v>0.17550496520975467</v>
       </c>
-      <c r="W27" s="66"/>
-      <c r="X27" s="66"/>
-      <c r="Y27" s="66"/>
-      <c r="Z27" s="66"/>
       <c r="AA27" s="66"/>
       <c r="AB27" s="66"/>
       <c r="AC27" s="66"/>
@@ -4462,8 +4640,12 @@
       <c r="AM27" s="66"/>
       <c r="AN27" s="66"/>
       <c r="AO27" s="66"/>
-    </row>
-    <row r="28" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP27" s="66"/>
+      <c r="AQ27" s="66"/>
+      <c r="AR27" s="66"/>
+      <c r="AS27" s="66"/>
+    </row>
+    <row r="28" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B28" s="65" t="s">
         <v>44</v>
       </c>
@@ -4503,38 +4685,41 @@
         <f t="shared" si="19"/>
         <v>0.70810810810810776</v>
       </c>
-      <c r="O28" s="66"/>
-      <c r="P28" s="83" t="s">
+      <c r="O28" s="85">
+        <f t="shared" si="19"/>
+        <v>0.44278606965174139</v>
+      </c>
+      <c r="P28" s="85"/>
+      <c r="Q28" s="85"/>
+      <c r="R28" s="85"/>
+      <c r="S28" s="66"/>
+      <c r="T28" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="Q28" s="85">
+      <c r="U28" s="85">
         <f t="shared" si="20"/>
         <v>0.28723344713718024</v>
       </c>
-      <c r="R28" s="85">
+      <c r="V28" s="85">
         <f t="shared" si="21"/>
         <v>0.85660246097656434</v>
       </c>
-      <c r="S28" s="85">
+      <c r="W28" s="85">
         <f t="shared" si="22"/>
         <v>0.87822014051522235</v>
       </c>
-      <c r="T28" s="85">
+      <c r="X28" s="85">
         <f t="shared" si="22"/>
         <v>0.75935162094763076</v>
       </c>
-      <c r="U28" s="85">
+      <c r="Y28" s="85">
         <f t="shared" si="24"/>
         <v>0.84408221119773219</v>
       </c>
-      <c r="V28" s="85">
+      <c r="Z28" s="85">
         <f t="shared" si="24"/>
         <v>0.96425826287471184</v>
       </c>
-      <c r="W28" s="66"/>
-      <c r="X28" s="66"/>
-      <c r="Y28" s="66"/>
-      <c r="Z28" s="66"/>
       <c r="AA28" s="66"/>
       <c r="AB28" s="66"/>
       <c r="AC28" s="66"/>
@@ -4550,8 +4735,12 @@
       <c r="AM28" s="66"/>
       <c r="AN28" s="66"/>
       <c r="AO28" s="66"/>
-    </row>
-    <row r="29" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP28" s="66"/>
+      <c r="AQ28" s="66"/>
+      <c r="AR28" s="66"/>
+      <c r="AS28" s="66"/>
+    </row>
+    <row r="29" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B29" s="65" t="s">
         <v>45</v>
       </c>
@@ -4591,38 +4780,41 @@
         <f t="shared" si="19"/>
         <v>0.20854580622472385</v>
       </c>
-      <c r="O29" s="66"/>
-      <c r="P29" s="83" t="s">
+      <c r="O29" s="85">
+        <f t="shared" si="19"/>
+        <v>0.12160375972976945</v>
+      </c>
+      <c r="P29" s="85"/>
+      <c r="Q29" s="85"/>
+      <c r="R29" s="85"/>
+      <c r="S29" s="66"/>
+      <c r="T29" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="Q29" s="85">
+      <c r="U29" s="85">
         <f t="shared" si="20"/>
         <v>0.58987058510555057</v>
       </c>
-      <c r="R29" s="85">
+      <c r="V29" s="85">
         <f t="shared" si="21"/>
         <v>0.68138979797731247</v>
       </c>
-      <c r="S29" s="85">
+      <c r="W29" s="85">
         <f t="shared" si="22"/>
         <v>0.70861993267964296</v>
       </c>
-      <c r="T29" s="85">
+      <c r="X29" s="85">
         <f t="shared" si="22"/>
         <v>0.46586723768736626</v>
       </c>
-      <c r="U29" s="85">
+      <c r="Y29" s="85">
         <f t="shared" si="24"/>
         <v>0.28526352693701051</v>
       </c>
-      <c r="V29" s="85">
+      <c r="Z29" s="85">
         <f t="shared" si="24"/>
         <v>0.27495908346972175</v>
       </c>
-      <c r="W29" s="66"/>
-      <c r="X29" s="66"/>
-      <c r="Y29" s="66"/>
-      <c r="Z29" s="66"/>
       <c r="AA29" s="66"/>
       <c r="AB29" s="66"/>
       <c r="AC29" s="66"/>
@@ -4638,8 +4830,12 @@
       <c r="AM29" s="66"/>
       <c r="AN29" s="66"/>
       <c r="AO29" s="66"/>
-    </row>
-    <row r="30" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP29" s="66"/>
+      <c r="AQ29" s="66"/>
+      <c r="AR29" s="66"/>
+      <c r="AS29" s="66"/>
+    </row>
+    <row r="30" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B30" s="65" t="s">
         <v>46</v>
       </c>
@@ -4679,38 +4875,41 @@
         <f t="shared" si="19"/>
         <v>0.38036809815950878</v>
       </c>
-      <c r="O30" s="66"/>
-      <c r="P30" s="83" t="s">
+      <c r="O30" s="85">
+        <f t="shared" si="19"/>
+        <v>0.45144356955380571</v>
+      </c>
+      <c r="P30" s="85"/>
+      <c r="Q30" s="85"/>
+      <c r="R30" s="85"/>
+      <c r="S30" s="66"/>
+      <c r="T30" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="Q30" s="85">
+      <c r="U30" s="85">
         <f t="shared" si="20"/>
         <v>0.64576802507836994</v>
       </c>
-      <c r="R30" s="85">
+      <c r="V30" s="85">
         <f t="shared" si="21"/>
         <v>1.3047619047619046</v>
       </c>
-      <c r="S30" s="85">
+      <c r="W30" s="85">
         <f t="shared" si="22"/>
         <v>0.30303030303030298</v>
       </c>
-      <c r="T30" s="85">
+      <c r="X30" s="85">
         <f t="shared" si="22"/>
         <v>0.45665961945031741</v>
       </c>
-      <c r="U30" s="85">
+      <c r="Y30" s="85">
         <f t="shared" si="24"/>
         <v>0.46589259796806948</v>
       </c>
-      <c r="V30" s="85">
+      <c r="Z30" s="85">
         <f t="shared" si="24"/>
         <v>0.68217821782178234</v>
       </c>
-      <c r="W30" s="66"/>
-      <c r="X30" s="66"/>
-      <c r="Y30" s="66"/>
-      <c r="Z30" s="66"/>
       <c r="AA30" s="66"/>
       <c r="AB30" s="66"/>
       <c r="AC30" s="66"/>
@@ -4726,8 +4925,12 @@
       <c r="AM30" s="66"/>
       <c r="AN30" s="66"/>
       <c r="AO30" s="66"/>
-    </row>
-    <row r="31" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP30" s="66"/>
+      <c r="AQ30" s="66"/>
+      <c r="AR30" s="66"/>
+      <c r="AS30" s="66"/>
+    </row>
+    <row r="31" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B31" s="65" t="s">
         <v>47</v>
       </c>
@@ -4767,38 +4970,41 @@
         <f t="shared" si="19"/>
         <v>1.132075471698113</v>
       </c>
-      <c r="O31" s="66"/>
-      <c r="P31" s="83" t="s">
+      <c r="O31" s="85">
+        <f t="shared" si="19"/>
+        <v>0.69736842105263164</v>
+      </c>
+      <c r="P31" s="85"/>
+      <c r="Q31" s="85"/>
+      <c r="R31" s="85"/>
+      <c r="S31" s="66"/>
+      <c r="T31" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="Q31" s="85">
+      <c r="U31" s="85">
         <f t="shared" si="20"/>
         <v>0.62796697626418974</v>
       </c>
-      <c r="R31" s="85">
+      <c r="V31" s="85">
         <f t="shared" si="21"/>
         <v>0.58478605388272586</v>
       </c>
-      <c r="S31" s="85">
+      <c r="W31" s="85">
         <f t="shared" si="22"/>
         <v>0.48</v>
       </c>
-      <c r="T31" s="85">
+      <c r="X31" s="85">
         <f t="shared" si="22"/>
         <v>0.59459459459459452</v>
       </c>
-      <c r="U31" s="85">
+      <c r="Y31" s="85">
         <f t="shared" si="24"/>
         <v>0.49999999999999978</v>
       </c>
-      <c r="V31" s="85">
+      <c r="Z31" s="85">
         <f t="shared" si="24"/>
         <v>1.2372881355932206</v>
       </c>
-      <c r="W31" s="66"/>
-      <c r="X31" s="66"/>
-      <c r="Y31" s="66"/>
-      <c r="Z31" s="66"/>
       <c r="AA31" s="66"/>
       <c r="AB31" s="66"/>
       <c r="AC31" s="66"/>
@@ -4814,8 +5020,12 @@
       <c r="AM31" s="66"/>
       <c r="AN31" s="66"/>
       <c r="AO31" s="66"/>
-    </row>
-    <row r="32" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP31" s="66"/>
+      <c r="AQ31" s="66"/>
+      <c r="AR31" s="66"/>
+      <c r="AS31" s="66"/>
+    </row>
+    <row r="32" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B32" s="65" t="s">
         <v>48</v>
       </c>
@@ -4855,38 +5065,41 @@
         <f t="shared" si="19"/>
         <v>0.23381642512077261</v>
       </c>
-      <c r="O32" s="66"/>
-      <c r="P32" s="83" t="s">
+      <c r="O32" s="85">
+        <f t="shared" si="19"/>
+        <v>0.1331999110518125</v>
+      </c>
+      <c r="P32" s="85"/>
+      <c r="Q32" s="85"/>
+      <c r="R32" s="85"/>
+      <c r="S32" s="66"/>
+      <c r="T32" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="Q32" s="85">
+      <c r="U32" s="85">
         <f t="shared" si="20"/>
         <v>0.31937164949480867</v>
       </c>
-      <c r="R32" s="85">
+      <c r="V32" s="85">
         <f t="shared" si="21"/>
         <v>0.69474244672776497</v>
       </c>
-      <c r="S32" s="85">
+      <c r="W32" s="85">
         <f t="shared" si="22"/>
         <v>0.73128342245989297</v>
       </c>
-      <c r="T32" s="85">
+      <c r="X32" s="85">
         <f t="shared" si="22"/>
         <v>0.44182754182754169</v>
       </c>
-      <c r="U32" s="85">
+      <c r="Y32" s="85">
         <f t="shared" si="24"/>
         <v>0.22779612603766863</v>
       </c>
-      <c r="V32" s="85">
+      <c r="Z32" s="85">
         <f t="shared" si="24"/>
         <v>0.27473645946928404</v>
       </c>
-      <c r="W32" s="66"/>
-      <c r="X32" s="66"/>
-      <c r="Y32" s="66"/>
-      <c r="Z32" s="66"/>
       <c r="AA32" s="66"/>
       <c r="AB32" s="66"/>
       <c r="AC32" s="66"/>
@@ -4902,8 +5115,12 @@
       <c r="AM32" s="66"/>
       <c r="AN32" s="66"/>
       <c r="AO32" s="66"/>
-    </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP32" s="66"/>
+      <c r="AQ32" s="66"/>
+      <c r="AR32" s="66"/>
+      <c r="AS32" s="66"/>
+    </row>
+    <row r="33" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B33" s="65" t="s">
         <v>49</v>
       </c>
@@ -4943,38 +5160,41 @@
         <f t="shared" si="19"/>
         <v>0.21742066171505692</v>
       </c>
-      <c r="O33" s="66"/>
-      <c r="P33" s="83" t="s">
+      <c r="O33" s="85">
+        <f t="shared" si="19"/>
+        <v>0.16395810762007956</v>
+      </c>
+      <c r="P33" s="85"/>
+      <c r="Q33" s="85"/>
+      <c r="R33" s="85"/>
+      <c r="S33" s="66"/>
+      <c r="T33" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="Q33" s="85">
+      <c r="U33" s="85">
         <f t="shared" si="20"/>
         <v>1.4166616468887416</v>
       </c>
-      <c r="R33" s="85">
+      <c r="V33" s="85">
         <f t="shared" si="21"/>
         <v>0.71863705476208284</v>
       </c>
-      <c r="S33" s="85">
+      <c r="W33" s="85">
         <f t="shared" si="22"/>
         <v>0.61385061638868743</v>
       </c>
-      <c r="T33" s="85">
+      <c r="X33" s="85">
         <f t="shared" si="22"/>
         <v>0.50932374747247788</v>
       </c>
-      <c r="U33" s="85">
+      <c r="Y33" s="85">
         <f t="shared" si="24"/>
         <v>0.40339386722238757</v>
       </c>
-      <c r="V33" s="85">
+      <c r="Z33" s="85">
         <f t="shared" si="24"/>
         <v>0.3369749681798897</v>
       </c>
-      <c r="W33" s="66"/>
-      <c r="X33" s="66"/>
-      <c r="Y33" s="66"/>
-      <c r="Z33" s="66"/>
       <c r="AA33" s="66"/>
       <c r="AB33" s="66"/>
       <c r="AC33" s="66"/>
@@ -4990,8 +5210,12 @@
       <c r="AM33" s="66"/>
       <c r="AN33" s="66"/>
       <c r="AO33" s="66"/>
-    </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP33" s="66"/>
+      <c r="AQ33" s="66"/>
+      <c r="AR33" s="66"/>
+      <c r="AS33" s="66"/>
+    </row>
+    <row r="34" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B34" s="64" t="s">
         <v>50</v>
       </c>
@@ -5031,38 +5255,41 @@
         <f t="shared" si="19"/>
         <v>0.22617870095614823</v>
       </c>
-      <c r="O34" s="81"/>
-      <c r="P34" s="87" t="s">
+      <c r="O34" s="86">
+        <f t="shared" si="19"/>
+        <v>0.14492155243600324</v>
+      </c>
+      <c r="P34" s="86"/>
+      <c r="Q34" s="86"/>
+      <c r="R34" s="86"/>
+      <c r="S34" s="81"/>
+      <c r="T34" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="Q34" s="86">
+      <c r="U34" s="86">
         <f t="shared" si="20"/>
         <v>0.59213087750823612</v>
       </c>
-      <c r="R34" s="86">
+      <c r="V34" s="86">
         <f t="shared" si="21"/>
         <v>0.70377859813303867</v>
       </c>
-      <c r="S34" s="86">
+      <c r="W34" s="86">
         <f t="shared" si="22"/>
         <v>0.68658570245652761</v>
       </c>
-      <c r="T34" s="86">
+      <c r="X34" s="86">
         <f t="shared" si="22"/>
         <v>0.46641027739137564</v>
       </c>
-      <c r="U34" s="86">
+      <c r="Y34" s="86">
         <f t="shared" si="24"/>
         <v>0.29362200770046321</v>
       </c>
-      <c r="V34" s="86">
+      <c r="Z34" s="86">
         <f t="shared" si="24"/>
         <v>0.30009058361730578</v>
       </c>
-      <c r="W34" s="66"/>
-      <c r="X34" s="66"/>
-      <c r="Y34" s="66"/>
-      <c r="Z34" s="66"/>
       <c r="AA34" s="66"/>
       <c r="AB34" s="66"/>
       <c r="AC34" s="66"/>
@@ -5078,8 +5305,12 @@
       <c r="AM34" s="66"/>
       <c r="AN34" s="66"/>
       <c r="AO34" s="66"/>
-    </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP34" s="66"/>
+      <c r="AQ34" s="66"/>
+      <c r="AR34" s="66"/>
+      <c r="AS34" s="66"/>
+    </row>
+    <row r="35" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B35" s="65" t="s">
         <v>51</v>
       </c>
@@ -5108,62 +5339,65 @@
         <v>0.59943632200105701</v>
       </c>
       <c r="I35" s="85">
-        <f>+I13/I11</f>
+        <f t="shared" ref="I35:N35" si="33">+I13/I11</f>
         <v>0.60600817867253853</v>
       </c>
       <c r="J35" s="85">
-        <f>+J13/J11</f>
+        <f t="shared" si="33"/>
         <v>0.62116716122650839</v>
       </c>
       <c r="K35" s="85">
-        <f>+K13/K11</f>
+        <f t="shared" si="33"/>
         <v>0.59909165978530143</v>
       </c>
       <c r="L35" s="85">
-        <f>+L13/L11</f>
+        <f t="shared" si="33"/>
         <v>0.61505605979711697</v>
       </c>
       <c r="M35" s="85">
-        <f>+M13/M11</f>
+        <f t="shared" si="33"/>
         <v>0.65747734138972802</v>
       </c>
       <c r="N35" s="85">
-        <f>+N13/N11</f>
+        <f t="shared" si="33"/>
         <v>0.63901586447969883</v>
       </c>
-      <c r="O35" s="66"/>
-      <c r="P35" s="85">
-        <f t="shared" ref="P35:R35" si="33">+P13/P11</f>
+      <c r="O35" s="85">
+        <f t="shared" ref="O35" si="34">+O13/O11</f>
+        <v>0.64226469527587449</v>
+      </c>
+      <c r="P35" s="85"/>
+      <c r="Q35" s="85"/>
+      <c r="R35" s="85"/>
+      <c r="S35" s="66"/>
+      <c r="T35" s="85">
+        <f t="shared" ref="T35:V35" si="35">+T13/T11</f>
         <v>0.53577792752321063</v>
       </c>
-      <c r="Q35" s="85">
-        <f t="shared" si="33"/>
+      <c r="U35" s="85">
+        <f t="shared" si="35"/>
         <v>0.54339391944320348</v>
       </c>
-      <c r="R35" s="85">
-        <f t="shared" si="33"/>
+      <c r="V35" s="85">
+        <f t="shared" si="35"/>
         <v>0.59384487993375656</v>
       </c>
-      <c r="S35" s="85">
-        <f t="shared" ref="S35:T35" si="34">+S13/S11</f>
+      <c r="W35" s="85">
+        <f t="shared" ref="W35:X35" si="36">+W13/W11</f>
         <v>0.56042877014974213</v>
       </c>
-      <c r="T35" s="85">
-        <f t="shared" si="34"/>
+      <c r="X35" s="85">
+        <f t="shared" si="36"/>
         <v>0.5955582835779254</v>
       </c>
-      <c r="U35" s="85">
-        <f>+U13/U11</f>
+      <c r="Y35" s="85">
+        <f>+Y13/Y11</f>
         <v>0.60634948022257695</v>
       </c>
-      <c r="V35" s="85">
-        <f>+V13/V11</f>
+      <c r="Z35" s="85">
+        <f>+Z13/Z11</f>
         <v>0.62830126078301263</v>
       </c>
-      <c r="W35" s="66"/>
-      <c r="X35" s="66"/>
-      <c r="Y35" s="66"/>
-      <c r="Z35" s="66"/>
       <c r="AA35" s="66"/>
       <c r="AB35" s="66"/>
       <c r="AC35" s="66"/>
@@ -5179,92 +5413,99 @@
       <c r="AM35" s="66"/>
       <c r="AN35" s="66"/>
       <c r="AO35" s="66"/>
-    </row>
-    <row r="36" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP35" s="66"/>
+      <c r="AQ35" s="66"/>
+      <c r="AR35" s="66"/>
+      <c r="AS35" s="66"/>
+    </row>
+    <row r="36" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B36" s="65" t="s">
         <v>52</v>
       </c>
       <c r="C36" s="85">
-        <f t="shared" ref="C36:H36" si="35">+C15/C11</f>
+        <f t="shared" ref="C36:H36" si="37">+C15/C11</f>
         <v>0.10066634935744879</v>
       </c>
       <c r="D36" s="85">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>8.8678820616700432E-2</v>
       </c>
       <c r="E36" s="85">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.12029136316337145</v>
       </c>
       <c r="F36" s="85">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>9.1254752851711196E-2</v>
       </c>
       <c r="G36" s="85">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>7.5757575757575649E-2</v>
       </c>
       <c r="H36" s="85">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>8.3494803593447395E-2</v>
       </c>
       <c r="I36" s="85">
-        <f>+I15/I11</f>
+        <f t="shared" ref="I36:N36" si="38">+I15/I11</f>
         <v>0.11418685121107262</v>
       </c>
       <c r="J36" s="85">
-        <f>+J15/J11</f>
+        <f t="shared" si="38"/>
         <v>8.7372238707550454E-2</v>
       </c>
       <c r="K36" s="85">
-        <f>+K15/K11</f>
+        <f t="shared" si="38"/>
         <v>0.10611065235342695</v>
       </c>
       <c r="L36" s="85">
-        <f>+L15/L11</f>
+        <f t="shared" si="38"/>
         <v>0.12386545648691946</v>
       </c>
       <c r="M36" s="85">
-        <f>+M15/M11</f>
+        <f t="shared" si="38"/>
         <v>0.15709969788519632</v>
       </c>
       <c r="N36" s="85">
-        <f>+N15/N11</f>
+        <f t="shared" si="38"/>
         <v>0.11078246840548535</v>
       </c>
-      <c r="O36" s="66"/>
-      <c r="P36" s="85">
-        <f t="shared" ref="P36:R36" si="36">+P15/P11</f>
+      <c r="O36" s="85">
+        <f t="shared" ref="O36" si="39">+O15/O11</f>
+        <v>0.14112273109748766</v>
+      </c>
+      <c r="P36" s="85"/>
+      <c r="Q36" s="85"/>
+      <c r="R36" s="85"/>
+      <c r="S36" s="66"/>
+      <c r="T36" s="85">
+        <f t="shared" ref="T36:V36" si="40">+T15/T11</f>
         <v>2.1297544174902747E-2</v>
       </c>
-      <c r="Q36" s="85">
-        <f t="shared" si="36"/>
+      <c r="U36" s="85">
+        <f t="shared" si="40"/>
         <v>-4.0205506830633189E-2</v>
       </c>
-      <c r="R36" s="85">
-        <f t="shared" si="36"/>
+      <c r="V36" s="85">
+        <f t="shared" si="40"/>
         <v>-0.19472812586254479</v>
       </c>
-      <c r="S36" s="85">
-        <f t="shared" ref="S36:T36" si="37">+S15/S11</f>
+      <c r="W36" s="85">
+        <f t="shared" ref="W36:X36" si="41">+W15/W11</f>
         <v>6.9634236150887749E-2</v>
       </c>
-      <c r="T36" s="85">
-        <f t="shared" si="37"/>
+      <c r="X36" s="85">
+        <f t="shared" si="41"/>
         <v>0.10060822498744487</v>
       </c>
-      <c r="U36" s="85">
-        <f>+U15/U11</f>
+      <c r="Y36" s="85">
+        <f>+Y15/Y11</f>
         <v>9.1230643143682968E-2</v>
       </c>
-      <c r="V36" s="85">
-        <f>+V15/V11</f>
+      <c r="Z36" s="85">
+        <f>+Z15/Z11</f>
         <v>0.1251161247511613</v>
       </c>
-      <c r="W36" s="66"/>
-      <c r="X36" s="66"/>
-      <c r="Y36" s="66"/>
-      <c r="Z36" s="66"/>
       <c r="AA36" s="66"/>
       <c r="AB36" s="66"/>
       <c r="AC36" s="66"/>
@@ -5280,92 +5521,99 @@
       <c r="AM36" s="66"/>
       <c r="AN36" s="66"/>
       <c r="AO36" s="66"/>
-    </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP36" s="66"/>
+      <c r="AQ36" s="66"/>
+      <c r="AR36" s="66"/>
+      <c r="AS36" s="66"/>
+    </row>
+    <row r="37" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B37" s="65" t="s">
         <v>53</v>
       </c>
       <c r="C37" s="85">
-        <f t="shared" ref="C37:H37" si="38">+C20/C19</f>
+        <f t="shared" ref="C37:H37" si="42">+C20/C19</f>
         <v>0.13786407766990294</v>
       </c>
       <c r="D37" s="85">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>1.4925373134328368</v>
       </c>
       <c r="E37" s="85">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>0.15273775216138333</v>
       </c>
       <c r="F37" s="85">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>-0.10241980866629145</v>
       </c>
       <c r="G37" s="85">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>0.21070811744386883</v>
       </c>
       <c r="H37" s="85">
-        <f t="shared" si="38"/>
+        <f t="shared" si="42"/>
         <v>0.27570093457943867</v>
       </c>
       <c r="I37" s="85">
-        <f>+I20/I19</f>
+        <f t="shared" ref="I37:N37" si="43">+I20/I19</f>
         <v>-3.0508474576271222E-2</v>
       </c>
       <c r="J37" s="85">
-        <f>+J20/J19</f>
+        <f t="shared" si="43"/>
         <v>-4.7835990888382675E-2</v>
       </c>
       <c r="K37" s="85">
-        <f>+K20/K19</f>
+        <f t="shared" si="43"/>
         <v>0.11249999999999998</v>
       </c>
       <c r="L37" s="85">
-        <f>+L20/L19</f>
+        <f t="shared" si="43"/>
         <v>0.13530655391120525</v>
       </c>
       <c r="M37" s="85">
-        <f>+M20/M19</f>
+        <f t="shared" si="43"/>
         <v>-2.5273799494524019E-3</v>
       </c>
       <c r="N37" s="85">
-        <f>+N20/N19</f>
+        <f t="shared" si="43"/>
         <v>2.4026910139356089E-3</v>
       </c>
-      <c r="O37" s="66"/>
-      <c r="P37" s="85">
-        <f t="shared" ref="P37:R37" si="39">+P20/P19</f>
+      <c r="O37" s="85">
+        <f t="shared" ref="O37" si="44">+O20/O19</f>
+        <v>0.11024978466838935</v>
+      </c>
+      <c r="P37" s="85"/>
+      <c r="Q37" s="85"/>
+      <c r="R37" s="85"/>
+      <c r="S37" s="66"/>
+      <c r="T37" s="85">
+        <f t="shared" ref="T37:V37" si="45">+T20/T19</f>
         <v>1.4685314685314586</v>
       </c>
-      <c r="Q37" s="85">
-        <f t="shared" si="39"/>
+      <c r="U37" s="85">
+        <f t="shared" si="45"/>
         <v>-0.12616631199869052</v>
       </c>
-      <c r="R37" s="85">
-        <f t="shared" si="39"/>
+      <c r="V37" s="85">
+        <f t="shared" si="45"/>
         <v>-6.6416040100250637E-2</v>
       </c>
-      <c r="S37" s="85">
-        <f t="shared" ref="S37:T37" si="40">+S20/S19</f>
+      <c r="W37" s="85">
+        <f t="shared" ref="W37:X37" si="46">+W20/W19</f>
         <v>0.25930680359435204</v>
       </c>
-      <c r="T37" s="85">
-        <f t="shared" si="40"/>
+      <c r="X37" s="85">
+        <f t="shared" si="46"/>
         <v>-0.15195369030390751</v>
       </c>
-      <c r="U37" s="85">
-        <f>+U20/U19</f>
+      <c r="Y37" s="85">
+        <f>+Y20/Y19</f>
         <v>0.13376251788268942</v>
       </c>
-      <c r="V37" s="85">
-        <f>+V20/V19</f>
+      <c r="Z37" s="85">
+        <f>+Z20/Z19</f>
         <v>7.3099415204678324E-3</v>
       </c>
-      <c r="W37" s="66"/>
-      <c r="X37" s="66"/>
-      <c r="Y37" s="66"/>
-      <c r="Z37" s="66"/>
       <c r="AA37" s="66"/>
       <c r="AB37" s="66"/>
       <c r="AC37" s="66"/>
@@ -5381,8 +5629,12 @@
       <c r="AM37" s="66"/>
       <c r="AN37" s="66"/>
       <c r="AO37" s="66"/>
-    </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP37" s="66"/>
+      <c r="AQ37" s="66"/>
+      <c r="AR37" s="66"/>
+      <c r="AS37" s="66"/>
+    </row>
+    <row r="38" spans="2:45" x14ac:dyDescent="0.2">
       <c r="C38" s="66"/>
       <c r="D38" s="66"/>
       <c r="E38" s="66"/>
@@ -5422,8 +5674,12 @@
       <c r="AM38" s="66"/>
       <c r="AN38" s="66"/>
       <c r="AO38" s="66"/>
-    </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP38" s="66"/>
+      <c r="AQ38" s="66"/>
+      <c r="AR38" s="66"/>
+      <c r="AS38" s="66"/>
+    </row>
+    <row r="39" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B39" s="65" t="s">
         <v>67</v>
       </c>
@@ -5441,28 +5697,28 @@
       <c r="N39" s="66"/>
       <c r="O39" s="66"/>
       <c r="P39" s="66"/>
-      <c r="Q39" s="66">
+      <c r="Q39" s="66"/>
+      <c r="R39" s="66"/>
+      <c r="S39" s="66"/>
+      <c r="T39" s="66"/>
+      <c r="U39" s="66">
         <v>90.641999999999996</v>
       </c>
-      <c r="R39" s="66">
+      <c r="V39" s="66">
         <v>653.08100000000002</v>
       </c>
-      <c r="S39" s="66">
+      <c r="W39" s="66">
         <v>371</v>
       </c>
-      <c r="T39" s="66">
+      <c r="X39" s="66">
         <v>494.6</v>
       </c>
-      <c r="U39" s="66">
+      <c r="Y39" s="66">
         <v>924.3</v>
       </c>
-      <c r="V39" s="66">
+      <c r="Z39" s="66">
         <v>1019.9</v>
       </c>
-      <c r="W39" s="66"/>
-      <c r="X39" s="66"/>
-      <c r="Y39" s="66"/>
-      <c r="Z39" s="66"/>
       <c r="AA39" s="66"/>
       <c r="AB39" s="66"/>
       <c r="AC39" s="66"/>
@@ -5478,8 +5734,12 @@
       <c r="AM39" s="66"/>
       <c r="AN39" s="66"/>
       <c r="AO39" s="66"/>
-    </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP39" s="66"/>
+      <c r="AQ39" s="66"/>
+      <c r="AR39" s="66"/>
+      <c r="AS39" s="66"/>
+    </row>
+    <row r="40" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B40" s="65" t="s">
         <v>68</v>
       </c>
@@ -5497,28 +5757,28 @@
       <c r="N40" s="66"/>
       <c r="O40" s="66"/>
       <c r="P40" s="66"/>
-      <c r="Q40" s="66">
+      <c r="Q40" s="66"/>
+      <c r="R40" s="66"/>
+      <c r="S40" s="66"/>
+      <c r="T40" s="66"/>
+      <c r="U40" s="66">
         <v>51.631</v>
       </c>
-      <c r="R40" s="66">
+      <c r="V40" s="66">
         <v>99.263999999999996</v>
       </c>
-      <c r="S40" s="66">
+      <c r="W40" s="66">
         <v>174.6</v>
       </c>
-      <c r="T40" s="66">
+      <c r="X40" s="66">
         <v>204.8</v>
       </c>
-      <c r="U40" s="66">
+      <c r="Y40" s="66">
         <v>246.1</v>
       </c>
-      <c r="V40" s="66">
+      <c r="Z40" s="66">
         <v>305.39999999999998</v>
       </c>
-      <c r="W40" s="66"/>
-      <c r="X40" s="66"/>
-      <c r="Y40" s="66"/>
-      <c r="Z40" s="66"/>
       <c r="AA40" s="66"/>
       <c r="AB40" s="66"/>
       <c r="AC40" s="66"/>
@@ -5534,8 +5794,12 @@
       <c r="AM40" s="66"/>
       <c r="AN40" s="66"/>
       <c r="AO40" s="66"/>
-    </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP40" s="66"/>
+      <c r="AQ40" s="66"/>
+      <c r="AR40" s="66"/>
+      <c r="AS40" s="66"/>
+    </row>
+    <row r="41" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B41" s="65" t="s">
         <v>69</v>
       </c>
@@ -5553,28 +5817,28 @@
       <c r="N41" s="66"/>
       <c r="O41" s="66"/>
       <c r="P41" s="66"/>
-      <c r="Q41" s="66">
+      <c r="Q41" s="66"/>
+      <c r="R41" s="66"/>
+      <c r="S41" s="66"/>
+      <c r="T41" s="66"/>
+      <c r="U41" s="66">
         <v>102.878</v>
       </c>
-      <c r="R41" s="66">
+      <c r="V41" s="66">
         <v>134.178</v>
       </c>
-      <c r="S41" s="66">
+      <c r="W41" s="66">
         <v>395.6</v>
       </c>
-      <c r="T41" s="66">
+      <c r="X41" s="66">
         <v>356.5</v>
       </c>
-      <c r="U41" s="66">
+      <c r="Y41" s="66">
         <v>419.2</v>
       </c>
-      <c r="V41" s="66">
+      <c r="Z41" s="66">
         <v>419.8</v>
       </c>
-      <c r="W41" s="66"/>
-      <c r="X41" s="66"/>
-      <c r="Y41" s="66"/>
-      <c r="Z41" s="66"/>
       <c r="AA41" s="66"/>
       <c r="AB41" s="66"/>
       <c r="AC41" s="66"/>
@@ -5590,8 +5854,12 @@
       <c r="AM41" s="66"/>
       <c r="AN41" s="66"/>
       <c r="AO41" s="66"/>
-    </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP41" s="66"/>
+      <c r="AQ41" s="66"/>
+      <c r="AR41" s="66"/>
+      <c r="AS41" s="66"/>
+    </row>
+    <row r="42" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B42" s="65" t="s">
         <v>70</v>
       </c>
@@ -5609,28 +5877,28 @@
       <c r="N42" s="66"/>
       <c r="O42" s="66"/>
       <c r="P42" s="66"/>
-      <c r="Q42" s="66">
+      <c r="Q42" s="66"/>
+      <c r="R42" s="66"/>
+      <c r="S42" s="66"/>
+      <c r="T42" s="66"/>
+      <c r="U42" s="66">
         <v>17.135000000000002</v>
       </c>
-      <c r="R42" s="66">
+      <c r="V42" s="66">
         <v>30.053999999999998</v>
       </c>
-      <c r="S42" s="66">
+      <c r="W42" s="66">
         <v>33.200000000000003</v>
       </c>
-      <c r="T42" s="66">
+      <c r="X42" s="66">
         <v>34.200000000000003</v>
       </c>
-      <c r="U42" s="66">
+      <c r="Y42" s="66">
         <v>56.4</v>
       </c>
-      <c r="V42" s="66">
+      <c r="Z42" s="66">
         <v>59.2</v>
       </c>
-      <c r="W42" s="66"/>
-      <c r="X42" s="66"/>
-      <c r="Y42" s="66"/>
-      <c r="Z42" s="66"/>
       <c r="AA42" s="66"/>
       <c r="AB42" s="66"/>
       <c r="AC42" s="66"/>
@@ -5646,8 +5914,12 @@
       <c r="AM42" s="66"/>
       <c r="AN42" s="66"/>
       <c r="AO42" s="66"/>
-    </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP42" s="66"/>
+      <c r="AQ42" s="66"/>
+      <c r="AR42" s="66"/>
+      <c r="AS42" s="66"/>
+    </row>
+    <row r="43" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B43" s="65" t="s">
         <v>71</v>
       </c>
@@ -5665,28 +5937,28 @@
       <c r="N43" s="66"/>
       <c r="O43" s="66"/>
       <c r="P43" s="66"/>
-      <c r="Q43" s="66">
+      <c r="Q43" s="66"/>
+      <c r="R43" s="66"/>
+      <c r="S43" s="66"/>
+      <c r="T43" s="66"/>
+      <c r="U43" s="66">
         <v>19.978999999999999</v>
       </c>
-      <c r="R43" s="66">
+      <c r="V43" s="66">
         <v>48.024000000000001</v>
       </c>
-      <c r="S43" s="66">
+      <c r="W43" s="66">
         <v>77</v>
       </c>
-      <c r="T43" s="66">
+      <c r="X43" s="66">
         <v>61.2</v>
       </c>
-      <c r="U43" s="66">
+      <c r="Y43" s="66">
         <v>113.7</v>
       </c>
-      <c r="V43" s="66">
+      <c r="Z43" s="66">
         <v>158.19999999999999</v>
       </c>
-      <c r="W43" s="66"/>
-      <c r="X43" s="66"/>
-      <c r="Y43" s="66"/>
-      <c r="Z43" s="66"/>
       <c r="AA43" s="66"/>
       <c r="AB43" s="66"/>
       <c r="AC43" s="66"/>
@@ -5702,8 +5974,12 @@
       <c r="AM43" s="66"/>
       <c r="AN43" s="66"/>
       <c r="AO43" s="66"/>
-    </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP43" s="66"/>
+      <c r="AQ43" s="66"/>
+      <c r="AR43" s="66"/>
+      <c r="AS43" s="66"/>
+    </row>
+    <row r="44" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B44" s="65" t="s">
         <v>72</v>
       </c>
@@ -5720,38 +5996,38 @@
       <c r="M44" s="66"/>
       <c r="N44" s="66"/>
       <c r="O44" s="66"/>
-      <c r="P44" s="66">
-        <f t="shared" ref="P44:T44" si="41">+SUM(P39:P43)</f>
+      <c r="P44" s="66"/>
+      <c r="Q44" s="66"/>
+      <c r="R44" s="66"/>
+      <c r="S44" s="66"/>
+      <c r="T44" s="66">
+        <f t="shared" ref="T44:X44" si="47">+SUM(T39:T43)</f>
         <v>0</v>
       </c>
-      <c r="Q44" s="66">
-        <f t="shared" si="41"/>
+      <c r="U44" s="66">
+        <f t="shared" si="47"/>
         <v>282.26499999999999</v>
       </c>
-      <c r="R44" s="66">
-        <f t="shared" si="41"/>
+      <c r="V44" s="66">
+        <f t="shared" si="47"/>
         <v>964.601</v>
       </c>
-      <c r="S44" s="66">
-        <f t="shared" si="41"/>
+      <c r="W44" s="66">
+        <f t="shared" si="47"/>
         <v>1051.4000000000001</v>
       </c>
-      <c r="T44" s="66">
-        <f t="shared" si="41"/>
+      <c r="X44" s="66">
+        <f t="shared" si="47"/>
         <v>1151.3000000000002</v>
       </c>
-      <c r="U44" s="66">
-        <f>+SUM(U39:U43)</f>
+      <c r="Y44" s="66">
+        <f>+SUM(Y39:Y43)</f>
         <v>1759.7</v>
       </c>
-      <c r="V44" s="66">
-        <f>+SUM(V39:V43)</f>
+      <c r="Z44" s="66">
+        <f>+SUM(Z39:Z43)</f>
         <v>1962.5</v>
       </c>
-      <c r="W44" s="66"/>
-      <c r="X44" s="66"/>
-      <c r="Y44" s="66"/>
-      <c r="Z44" s="66"/>
       <c r="AA44" s="66"/>
       <c r="AB44" s="66"/>
       <c r="AC44" s="66"/>
@@ -5767,8 +6043,12 @@
       <c r="AM44" s="66"/>
       <c r="AN44" s="66"/>
       <c r="AO44" s="66"/>
-    </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP44" s="66"/>
+      <c r="AQ44" s="66"/>
+      <c r="AR44" s="66"/>
+      <c r="AS44" s="66"/>
+    </row>
+    <row r="45" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B45" s="65" t="s">
         <v>73</v>
       </c>
@@ -5786,28 +6066,28 @@
       <c r="N45" s="66"/>
       <c r="O45" s="66"/>
       <c r="P45" s="66"/>
-      <c r="Q45" s="66">
+      <c r="Q45" s="66"/>
+      <c r="R45" s="66"/>
+      <c r="S45" s="66"/>
+      <c r="T45" s="66"/>
+      <c r="U45" s="66">
         <v>17.004000000000001</v>
       </c>
-      <c r="R45" s="66">
+      <c r="V45" s="66">
         <v>34.399000000000001</v>
       </c>
-      <c r="S45" s="66">
+      <c r="W45" s="66">
         <v>77.2</v>
       </c>
-      <c r="T45" s="66">
+      <c r="X45" s="66">
         <v>93.6</v>
       </c>
-      <c r="U45" s="66">
+      <c r="Y45" s="66">
         <v>127.2</v>
       </c>
-      <c r="V45" s="66">
+      <c r="Z45" s="66">
         <v>148.80000000000001</v>
       </c>
-      <c r="W45" s="66"/>
-      <c r="X45" s="66"/>
-      <c r="Y45" s="66"/>
-      <c r="Z45" s="66"/>
       <c r="AA45" s="66"/>
       <c r="AB45" s="66"/>
       <c r="AC45" s="66"/>
@@ -5823,8 +6103,12 @@
       <c r="AM45" s="66"/>
       <c r="AN45" s="66"/>
       <c r="AO45" s="66"/>
-    </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP45" s="66"/>
+      <c r="AQ45" s="66"/>
+      <c r="AR45" s="66"/>
+      <c r="AS45" s="66"/>
+    </row>
+    <row r="46" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B46" s="65" t="s">
         <v>74</v>
       </c>
@@ -5842,28 +6126,28 @@
       <c r="N46" s="66"/>
       <c r="O46" s="66"/>
       <c r="P46" s="66"/>
-      <c r="Q46" s="66">
+      <c r="Q46" s="66"/>
+      <c r="R46" s="66"/>
+      <c r="S46" s="66"/>
+      <c r="T46" s="66"/>
+      <c r="U46" s="66">
         <v>22.719000000000001</v>
       </c>
-      <c r="R46" s="66">
+      <c r="V46" s="66">
         <v>177.89</v>
       </c>
-      <c r="S46" s="66">
+      <c r="W46" s="66">
         <v>151.6</v>
       </c>
-      <c r="T46" s="66">
+      <c r="X46" s="66">
         <v>214</v>
       </c>
-      <c r="U46" s="66">
+      <c r="Y46" s="66">
         <v>323.60000000000002</v>
       </c>
-      <c r="V46" s="66">
+      <c r="Z46" s="66">
         <v>494.1</v>
       </c>
-      <c r="W46" s="66"/>
-      <c r="X46" s="66"/>
-      <c r="Y46" s="66"/>
-      <c r="Z46" s="66"/>
       <c r="AA46" s="66"/>
       <c r="AB46" s="66"/>
       <c r="AC46" s="66"/>
@@ -5879,8 +6163,12 @@
       <c r="AM46" s="66"/>
       <c r="AN46" s="66"/>
       <c r="AO46" s="66"/>
-    </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP46" s="66"/>
+      <c r="AQ46" s="66"/>
+      <c r="AR46" s="66"/>
+      <c r="AS46" s="66"/>
+    </row>
+    <row r="47" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B47" s="65" t="s">
         <v>75</v>
       </c>
@@ -5898,28 +6186,28 @@
       <c r="N47" s="66"/>
       <c r="O47" s="66"/>
       <c r="P47" s="66"/>
-      <c r="Q47" s="66">
+      <c r="Q47" s="66"/>
+      <c r="R47" s="66"/>
+      <c r="S47" s="66"/>
+      <c r="T47" s="66"/>
+      <c r="U47" s="66">
         <v>54.667000000000002</v>
       </c>
-      <c r="R47" s="66">
+      <c r="V47" s="66">
         <v>57.463999999999999</v>
       </c>
-      <c r="S47" s="66">
+      <c r="W47" s="66">
         <v>70.3</v>
       </c>
-      <c r="T47" s="66">
+      <c r="X47" s="66">
         <v>64.599999999999994</v>
       </c>
-      <c r="U47" s="66">
+      <c r="Y47" s="66">
         <v>58.3</v>
       </c>
-      <c r="V47" s="66">
+      <c r="Z47" s="66">
         <v>54.2</v>
       </c>
-      <c r="W47" s="66"/>
-      <c r="X47" s="66"/>
-      <c r="Y47" s="66"/>
-      <c r="Z47" s="66"/>
       <c r="AA47" s="66"/>
       <c r="AB47" s="66"/>
       <c r="AC47" s="66"/>
@@ -5935,8 +6223,12 @@
       <c r="AM47" s="66"/>
       <c r="AN47" s="66"/>
       <c r="AO47" s="66"/>
-    </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP47" s="66"/>
+      <c r="AQ47" s="66"/>
+      <c r="AR47" s="66"/>
+      <c r="AS47" s="66"/>
+    </row>
+    <row r="48" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B48" s="65" t="s">
         <v>76</v>
       </c>
@@ -5954,28 +6246,28 @@
       <c r="N48" s="66"/>
       <c r="O48" s="66"/>
       <c r="P48" s="66"/>
-      <c r="Q48" s="66">
+      <c r="Q48" s="66"/>
+      <c r="R48" s="66"/>
+      <c r="S48" s="66"/>
+      <c r="T48" s="66"/>
+      <c r="U48" s="66">
         <v>5.915</v>
       </c>
-      <c r="R48" s="66">
+      <c r="V48" s="66">
         <v>2.1709999999999998</v>
       </c>
-      <c r="S48" s="66">
+      <c r="W48" s="66">
         <v>31.7</v>
       </c>
-      <c r="T48" s="66">
+      <c r="X48" s="66">
         <v>69.5</v>
       </c>
-      <c r="U48" s="66">
+      <c r="Y48" s="66">
         <v>107.8</v>
       </c>
-      <c r="V48" s="66">
+      <c r="Z48" s="66">
         <v>175.9</v>
       </c>
-      <c r="W48" s="66"/>
-      <c r="X48" s="66"/>
-      <c r="Y48" s="66"/>
-      <c r="Z48" s="66"/>
       <c r="AA48" s="66"/>
       <c r="AB48" s="66"/>
       <c r="AC48" s="66"/>
@@ -5991,8 +6283,12 @@
       <c r="AM48" s="66"/>
       <c r="AN48" s="66"/>
       <c r="AO48" s="66"/>
-    </row>
-    <row r="49" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP48" s="66"/>
+      <c r="AQ48" s="66"/>
+      <c r="AR48" s="66"/>
+      <c r="AS48" s="66"/>
+    </row>
+    <row r="49" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B49" s="65" t="s">
         <v>77</v>
       </c>
@@ -6009,38 +6305,38 @@
       <c r="M49" s="66"/>
       <c r="N49" s="66"/>
       <c r="O49" s="66"/>
-      <c r="P49" s="66">
-        <f t="shared" ref="P49:T49" si="42">+SUM(P45:P48)</f>
+      <c r="P49" s="66"/>
+      <c r="Q49" s="66"/>
+      <c r="R49" s="66"/>
+      <c r="S49" s="66"/>
+      <c r="T49" s="66">
+        <f t="shared" ref="T49:X49" si="48">+SUM(T45:T48)</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="66">
-        <f t="shared" si="42"/>
+      <c r="U49" s="66">
+        <f t="shared" si="48"/>
         <v>100.30500000000001</v>
       </c>
-      <c r="R49" s="66">
-        <f t="shared" si="42"/>
+      <c r="V49" s="66">
+        <f t="shared" si="48"/>
         <v>271.92399999999998</v>
       </c>
-      <c r="S49" s="66">
-        <f t="shared" si="42"/>
+      <c r="W49" s="66">
+        <f t="shared" si="48"/>
         <v>330.8</v>
       </c>
-      <c r="T49" s="66">
-        <f t="shared" si="42"/>
+      <c r="X49" s="66">
+        <f t="shared" si="48"/>
         <v>441.70000000000005</v>
       </c>
-      <c r="U49" s="66">
-        <f>+SUM(U45:U48)</f>
+      <c r="Y49" s="66">
+        <f>+SUM(Y45:Y48)</f>
         <v>616.9</v>
       </c>
-      <c r="V49" s="66">
-        <f>+SUM(V45:V48)</f>
+      <c r="Z49" s="66">
+        <f>+SUM(Z45:Z48)</f>
         <v>873.00000000000011</v>
       </c>
-      <c r="W49" s="66"/>
-      <c r="X49" s="66"/>
-      <c r="Y49" s="66"/>
-      <c r="Z49" s="66"/>
       <c r="AA49" s="66"/>
       <c r="AB49" s="66"/>
       <c r="AC49" s="66"/>
@@ -6056,8 +6352,12 @@
       <c r="AM49" s="66"/>
       <c r="AN49" s="66"/>
       <c r="AO49" s="66"/>
-    </row>
-    <row r="50" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP49" s="66"/>
+      <c r="AQ49" s="66"/>
+      <c r="AR49" s="66"/>
+      <c r="AS49" s="66"/>
+    </row>
+    <row r="50" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B50" s="64" t="s">
         <v>78</v>
       </c>
@@ -6074,38 +6374,38 @@
       <c r="M50" s="66"/>
       <c r="N50" s="66"/>
       <c r="O50" s="66"/>
-      <c r="P50" s="81">
-        <f t="shared" ref="P50:T50" si="43">+P49+P44</f>
+      <c r="P50" s="66"/>
+      <c r="Q50" s="66"/>
+      <c r="R50" s="66"/>
+      <c r="S50" s="66"/>
+      <c r="T50" s="81">
+        <f t="shared" ref="T50:X50" si="49">+T49+T44</f>
         <v>0</v>
       </c>
-      <c r="Q50" s="81">
-        <f t="shared" si="43"/>
+      <c r="U50" s="81">
+        <f t="shared" si="49"/>
         <v>382.57</v>
       </c>
-      <c r="R50" s="81">
-        <f t="shared" si="43"/>
+      <c r="V50" s="81">
+        <f t="shared" si="49"/>
         <v>1236.5250000000001</v>
       </c>
-      <c r="S50" s="81">
-        <f t="shared" si="43"/>
+      <c r="W50" s="81">
+        <f t="shared" si="49"/>
         <v>1382.2</v>
       </c>
-      <c r="T50" s="81">
-        <f t="shared" si="43"/>
+      <c r="X50" s="81">
+        <f t="shared" si="49"/>
         <v>1593.0000000000002</v>
       </c>
-      <c r="U50" s="81">
-        <f>+U49+U44</f>
+      <c r="Y50" s="81">
+        <f>+Y49+Y44</f>
         <v>2376.6</v>
       </c>
-      <c r="V50" s="81">
-        <f>+V49+V44</f>
+      <c r="Z50" s="81">
+        <f>+Z49+Z44</f>
         <v>2835.5</v>
       </c>
-      <c r="W50" s="66"/>
-      <c r="X50" s="66"/>
-      <c r="Y50" s="66"/>
-      <c r="Z50" s="66"/>
       <c r="AA50" s="66"/>
       <c r="AB50" s="66"/>
       <c r="AC50" s="66"/>
@@ -6121,8 +6421,12 @@
       <c r="AM50" s="66"/>
       <c r="AN50" s="66"/>
       <c r="AO50" s="66"/>
-    </row>
-    <row r="51" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP50" s="66"/>
+      <c r="AQ50" s="66"/>
+      <c r="AR50" s="66"/>
+      <c r="AS50" s="66"/>
+    </row>
+    <row r="51" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B51" s="65" t="s">
         <v>79</v>
       </c>
@@ -6140,28 +6444,28 @@
       <c r="N51" s="66"/>
       <c r="O51" s="66"/>
       <c r="P51" s="66"/>
-      <c r="Q51" s="66">
+      <c r="Q51" s="66"/>
+      <c r="R51" s="66"/>
+      <c r="S51" s="66"/>
+      <c r="T51" s="66"/>
+      <c r="U51" s="66">
         <v>41.542999999999999</v>
       </c>
-      <c r="R51" s="66">
+      <c r="V51" s="66">
         <v>45.939</v>
       </c>
-      <c r="S51" s="66">
+      <c r="W51" s="66">
         <v>111</v>
       </c>
-      <c r="T51" s="66">
+      <c r="X51" s="66">
         <v>65.099999999999994</v>
       </c>
-      <c r="U51" s="66">
+      <c r="Y51" s="66">
         <v>166.5</v>
       </c>
-      <c r="V51" s="66">
+      <c r="Z51" s="66">
         <v>154.80000000000001</v>
       </c>
-      <c r="W51" s="66"/>
-      <c r="X51" s="66"/>
-      <c r="Y51" s="66"/>
-      <c r="Z51" s="66"/>
       <c r="AA51" s="66"/>
       <c r="AB51" s="66"/>
       <c r="AC51" s="66"/>
@@ -6177,8 +6481,12 @@
       <c r="AM51" s="66"/>
       <c r="AN51" s="66"/>
       <c r="AO51" s="66"/>
-    </row>
-    <row r="52" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP51" s="66"/>
+      <c r="AQ51" s="66"/>
+      <c r="AR51" s="66"/>
+      <c r="AS51" s="66"/>
+    </row>
+    <row r="52" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B52" s="65" t="s">
         <v>80</v>
       </c>
@@ -6196,28 +6504,28 @@
       <c r="N52" s="66"/>
       <c r="O52" s="66"/>
       <c r="P52" s="66"/>
-      <c r="Q52" s="66">
+      <c r="Q52" s="66"/>
+      <c r="R52" s="66"/>
+      <c r="S52" s="66"/>
+      <c r="T52" s="66"/>
+      <c r="U52" s="66">
         <v>0</v>
       </c>
-      <c r="R52" s="66">
+      <c r="V52" s="66">
         <v>0</v>
       </c>
-      <c r="S52" s="66">
+      <c r="W52" s="66">
         <v>0</v>
       </c>
-      <c r="T52" s="66">
+      <c r="X52" s="66">
         <v>38.700000000000003</v>
       </c>
-      <c r="U52" s="66">
+      <c r="Y52" s="66">
         <v>59.1</v>
       </c>
-      <c r="V52" s="66">
+      <c r="Z52" s="66">
         <v>81.2</v>
       </c>
-      <c r="W52" s="66"/>
-      <c r="X52" s="66"/>
-      <c r="Y52" s="66"/>
-      <c r="Z52" s="66"/>
       <c r="AA52" s="66"/>
       <c r="AB52" s="66"/>
       <c r="AC52" s="66"/>
@@ -6233,8 +6541,12 @@
       <c r="AM52" s="66"/>
       <c r="AN52" s="66"/>
       <c r="AO52" s="66"/>
-    </row>
-    <row r="53" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP52" s="66"/>
+      <c r="AQ52" s="66"/>
+      <c r="AR52" s="66"/>
+      <c r="AS52" s="66"/>
+    </row>
+    <row r="53" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B53" s="65" t="s">
         <v>81</v>
       </c>
@@ -6252,28 +6564,28 @@
       <c r="N53" s="66"/>
       <c r="O53" s="66"/>
       <c r="P53" s="66"/>
-      <c r="Q53" s="66">
+      <c r="Q53" s="66"/>
+      <c r="R53" s="66"/>
+      <c r="S53" s="66"/>
+      <c r="T53" s="66"/>
+      <c r="U53" s="66">
         <v>7.2759999999999998</v>
       </c>
-      <c r="R53" s="66">
+      <c r="V53" s="66">
         <v>20.097000000000001</v>
       </c>
-      <c r="S53" s="66">
+      <c r="W53" s="66">
         <v>31</v>
       </c>
-      <c r="T53" s="66">
+      <c r="X53" s="66">
         <v>14.8</v>
       </c>
-      <c r="U53" s="66">
+      <c r="Y53" s="66">
         <v>51.3</v>
       </c>
-      <c r="V53" s="66">
+      <c r="Z53" s="66">
         <v>56.7</v>
       </c>
-      <c r="W53" s="66"/>
-      <c r="X53" s="66"/>
-      <c r="Y53" s="66"/>
-      <c r="Z53" s="66"/>
       <c r="AA53" s="66"/>
       <c r="AB53" s="66"/>
       <c r="AC53" s="66"/>
@@ -6289,8 +6601,12 @@
       <c r="AM53" s="66"/>
       <c r="AN53" s="66"/>
       <c r="AO53" s="66"/>
-    </row>
-    <row r="54" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP53" s="66"/>
+      <c r="AQ53" s="66"/>
+      <c r="AR53" s="66"/>
+      <c r="AS53" s="66"/>
+    </row>
+    <row r="54" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B54" s="65" t="s">
         <v>82</v>
       </c>
@@ -6308,28 +6624,28 @@
       <c r="N54" s="66"/>
       <c r="O54" s="66"/>
       <c r="P54" s="66"/>
-      <c r="Q54" s="66">
+      <c r="Q54" s="66"/>
+      <c r="R54" s="66"/>
+      <c r="S54" s="66"/>
+      <c r="T54" s="66"/>
+      <c r="U54" s="66">
         <v>36.113</v>
       </c>
-      <c r="R54" s="66">
+      <c r="V54" s="66">
         <v>121.673</v>
       </c>
-      <c r="S54" s="66">
+      <c r="W54" s="66">
         <v>81.7</v>
       </c>
-      <c r="T54" s="66">
+      <c r="X54" s="66">
         <v>156.4</v>
       </c>
-      <c r="U54" s="66">
+      <c r="Y54" s="66">
         <v>299.3</v>
       </c>
-      <c r="V54" s="66">
+      <c r="Z54" s="66">
         <v>355.4</v>
       </c>
-      <c r="W54" s="66"/>
-      <c r="X54" s="66"/>
-      <c r="Y54" s="66"/>
-      <c r="Z54" s="66"/>
       <c r="AA54" s="66"/>
       <c r="AB54" s="66"/>
       <c r="AC54" s="66"/>
@@ -6345,8 +6661,12 @@
       <c r="AM54" s="66"/>
       <c r="AN54" s="66"/>
       <c r="AO54" s="66"/>
-    </row>
-    <row r="55" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP54" s="66"/>
+      <c r="AQ54" s="66"/>
+      <c r="AR54" s="66"/>
+      <c r="AS54" s="66"/>
+    </row>
+    <row r="55" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B55" s="65" t="s">
         <v>83</v>
       </c>
@@ -6364,28 +6684,28 @@
       <c r="N55" s="66"/>
       <c r="O55" s="66"/>
       <c r="P55" s="66"/>
-      <c r="Q55" s="66">
+      <c r="Q55" s="66"/>
+      <c r="R55" s="66"/>
+      <c r="S55" s="66"/>
+      <c r="T55" s="66"/>
+      <c r="U55" s="66">
         <v>0.376</v>
       </c>
-      <c r="R55" s="66">
+      <c r="V55" s="66">
         <v>14.901999999999999</v>
       </c>
-      <c r="S55" s="66">
+      <c r="W55" s="66">
         <v>5</v>
       </c>
-      <c r="T55" s="66">
+      <c r="X55" s="66">
         <v>7.1</v>
       </c>
-      <c r="U55" s="66">
+      <c r="Y55" s="66">
         <v>21.7</v>
       </c>
-      <c r="V55" s="66">
+      <c r="Z55" s="66">
         <v>13</v>
       </c>
-      <c r="W55" s="66"/>
-      <c r="X55" s="66"/>
-      <c r="Y55" s="66"/>
-      <c r="Z55" s="66"/>
       <c r="AA55" s="66"/>
       <c r="AB55" s="66"/>
       <c r="AC55" s="66"/>
@@ -6401,8 +6721,12 @@
       <c r="AM55" s="66"/>
       <c r="AN55" s="66"/>
       <c r="AO55" s="66"/>
-    </row>
-    <row r="56" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP55" s="66"/>
+      <c r="AQ55" s="66"/>
+      <c r="AR55" s="66"/>
+      <c r="AS55" s="66"/>
+    </row>
+    <row r="56" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B56" s="65" t="s">
         <v>84</v>
       </c>
@@ -6420,28 +6744,28 @@
       <c r="N56" s="66"/>
       <c r="O56" s="66"/>
       <c r="P56" s="66"/>
-      <c r="Q56" s="66">
+      <c r="Q56" s="66"/>
+      <c r="R56" s="66"/>
+      <c r="S56" s="66"/>
+      <c r="T56" s="66"/>
+      <c r="U56" s="66">
         <v>1.054</v>
       </c>
-      <c r="R56" s="66">
+      <c r="V56" s="66">
         <v>2.4</v>
       </c>
-      <c r="S56" s="66">
+      <c r="W56" s="66">
         <v>13.9</v>
       </c>
-      <c r="T56" s="66">
+      <c r="X56" s="66">
         <v>23.5</v>
       </c>
-      <c r="U56" s="66">
+      <c r="Y56" s="66">
         <v>62.5</v>
       </c>
-      <c r="V56" s="66">
+      <c r="Z56" s="66">
         <v>63.2</v>
       </c>
-      <c r="W56" s="66"/>
-      <c r="X56" s="66"/>
-      <c r="Y56" s="66"/>
-      <c r="Z56" s="66"/>
       <c r="AA56" s="66"/>
       <c r="AB56" s="66"/>
       <c r="AC56" s="66"/>
@@ -6457,8 +6781,12 @@
       <c r="AM56" s="66"/>
       <c r="AN56" s="66"/>
       <c r="AO56" s="66"/>
-    </row>
-    <row r="57" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP56" s="66"/>
+      <c r="AQ56" s="66"/>
+      <c r="AR56" s="66"/>
+      <c r="AS56" s="66"/>
+    </row>
+    <row r="57" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B57" s="65" t="s">
         <v>85</v>
       </c>
@@ -6475,38 +6803,38 @@
       <c r="M57" s="66"/>
       <c r="N57" s="66"/>
       <c r="O57" s="66"/>
-      <c r="P57" s="66">
-        <f t="shared" ref="P57:T57" si="44">+SUM(P51:P56)</f>
+      <c r="P57" s="66"/>
+      <c r="Q57" s="66"/>
+      <c r="R57" s="66"/>
+      <c r="S57" s="66"/>
+      <c r="T57" s="66">
+        <f t="shared" ref="T57:X57" si="50">+SUM(T51:T56)</f>
         <v>0</v>
       </c>
-      <c r="Q57" s="66">
-        <f t="shared" si="44"/>
+      <c r="U57" s="66">
+        <f t="shared" si="50"/>
         <v>86.362000000000009</v>
       </c>
-      <c r="R57" s="66">
-        <f t="shared" si="44"/>
+      <c r="V57" s="66">
+        <f t="shared" si="50"/>
         <v>205.011</v>
       </c>
-      <c r="S57" s="66">
-        <f t="shared" si="44"/>
+      <c r="W57" s="66">
+        <f t="shared" si="50"/>
         <v>242.6</v>
       </c>
-      <c r="T57" s="66">
-        <f t="shared" si="44"/>
+      <c r="X57" s="66">
+        <f t="shared" si="50"/>
         <v>305.60000000000002</v>
       </c>
-      <c r="U57" s="66">
-        <f>+SUM(U51:U56)</f>
+      <c r="Y57" s="66">
+        <f>+SUM(Y51:Y56)</f>
         <v>660.40000000000009</v>
       </c>
-      <c r="V57" s="66">
-        <f>+SUM(V51:V56)</f>
+      <c r="Z57" s="66">
+        <f>+SUM(Z51:Z56)</f>
         <v>724.3</v>
       </c>
-      <c r="W57" s="66"/>
-      <c r="X57" s="66"/>
-      <c r="Y57" s="66"/>
-      <c r="Z57" s="66"/>
       <c r="AA57" s="66"/>
       <c r="AB57" s="66"/>
       <c r="AC57" s="66"/>
@@ -6522,8 +6850,12 @@
       <c r="AM57" s="66"/>
       <c r="AN57" s="66"/>
       <c r="AO57" s="66"/>
-    </row>
-    <row r="58" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP57" s="66"/>
+      <c r="AQ57" s="66"/>
+      <c r="AR57" s="66"/>
+      <c r="AS57" s="66"/>
+    </row>
+    <row r="58" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B58" s="65" t="s">
         <v>87</v>
       </c>
@@ -6541,28 +6873,28 @@
       <c r="N58" s="66"/>
       <c r="O58" s="66"/>
       <c r="P58" s="66"/>
-      <c r="Q58" s="66">
+      <c r="Q58" s="66"/>
+      <c r="R58" s="66"/>
+      <c r="S58" s="66"/>
+      <c r="T58" s="66"/>
+      <c r="U58" s="66">
         <v>5.63</v>
       </c>
-      <c r="R58" s="66">
+      <c r="V58" s="66">
         <v>5.8529999999999998</v>
       </c>
-      <c r="S58" s="66">
+      <c r="W58" s="66">
         <v>6.3</v>
       </c>
-      <c r="T58" s="66">
+      <c r="X58" s="66">
         <v>2.2000000000000002</v>
       </c>
-      <c r="U58" s="66">
+      <c r="Y58" s="66">
         <v>8.6</v>
       </c>
-      <c r="V58" s="66">
+      <c r="Z58" s="66">
         <v>5.5</v>
       </c>
-      <c r="W58" s="66"/>
-      <c r="X58" s="66"/>
-      <c r="Y58" s="66"/>
-      <c r="Z58" s="66"/>
       <c r="AA58" s="66"/>
       <c r="AB58" s="66"/>
       <c r="AC58" s="66"/>
@@ -6578,8 +6910,12 @@
       <c r="AM58" s="66"/>
       <c r="AN58" s="66"/>
       <c r="AO58" s="66"/>
-    </row>
-    <row r="59" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP58" s="66"/>
+      <c r="AQ58" s="66"/>
+      <c r="AR58" s="66"/>
+      <c r="AS58" s="66"/>
+    </row>
+    <row r="59" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B59" s="65" t="s">
         <v>86</v>
       </c>
@@ -6597,28 +6933,28 @@
       <c r="N59" s="66"/>
       <c r="O59" s="66"/>
       <c r="P59" s="66"/>
-      <c r="Q59" s="66">
+      <c r="Q59" s="66"/>
+      <c r="R59" s="66"/>
+      <c r="S59" s="66"/>
+      <c r="T59" s="66"/>
+      <c r="U59" s="66">
         <v>20.645</v>
       </c>
-      <c r="R59" s="66">
+      <c r="V59" s="66">
         <v>4.4420000000000002</v>
       </c>
-      <c r="S59" s="66">
+      <c r="W59" s="66">
         <v>7.2</v>
       </c>
-      <c r="T59" s="66">
+      <c r="X59" s="66">
         <v>10</v>
       </c>
-      <c r="U59" s="66">
+      <c r="Y59" s="66">
         <v>14.9</v>
       </c>
-      <c r="V59" s="66">
+      <c r="Z59" s="66">
         <v>20.7</v>
       </c>
-      <c r="W59" s="66"/>
-      <c r="X59" s="66"/>
-      <c r="Y59" s="66"/>
-      <c r="Z59" s="66"/>
       <c r="AA59" s="66"/>
       <c r="AB59" s="66"/>
       <c r="AC59" s="66"/>
@@ -6634,8 +6970,12 @@
       <c r="AM59" s="66"/>
       <c r="AN59" s="66"/>
       <c r="AO59" s="66"/>
-    </row>
-    <row r="60" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP59" s="66"/>
+      <c r="AQ59" s="66"/>
+      <c r="AR59" s="66"/>
+      <c r="AS59" s="66"/>
+    </row>
+    <row r="60" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B60" s="65" t="s">
         <v>88</v>
       </c>
@@ -6652,31 +6992,31 @@
       <c r="M60" s="66"/>
       <c r="N60" s="66"/>
       <c r="O60" s="66"/>
-      <c r="P60" s="66">
+      <c r="P60" s="66"/>
+      <c r="Q60" s="66"/>
+      <c r="R60" s="66"/>
+      <c r="S60" s="66"/>
+      <c r="T60" s="66">
         <v>0</v>
       </c>
-      <c r="Q60" s="66">
+      <c r="U60" s="66">
         <v>0</v>
       </c>
-      <c r="R60" s="66">
+      <c r="V60" s="66">
         <v>0</v>
       </c>
-      <c r="S60" s="66">
+      <c r="W60" s="66">
         <v>0</v>
       </c>
-      <c r="T60" s="66">
+      <c r="X60" s="66">
         <v>190.3</v>
       </c>
-      <c r="U60" s="66">
+      <c r="Y60" s="66">
         <v>288.5</v>
       </c>
-      <c r="V60" s="66">
+      <c r="Z60" s="66">
         <v>440.3</v>
       </c>
-      <c r="W60" s="66"/>
-      <c r="X60" s="66"/>
-      <c r="Y60" s="66"/>
-      <c r="Z60" s="66"/>
       <c r="AA60" s="66"/>
       <c r="AB60" s="66"/>
       <c r="AC60" s="66"/>
@@ -6692,8 +7032,12 @@
       <c r="AM60" s="66"/>
       <c r="AN60" s="66"/>
       <c r="AO60" s="66"/>
-    </row>
-    <row r="61" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP60" s="66"/>
+      <c r="AQ60" s="66"/>
+      <c r="AR60" s="66"/>
+      <c r="AS60" s="66"/>
+    </row>
+    <row r="61" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B61" s="65" t="s">
         <v>81</v>
       </c>
@@ -6711,28 +7055,28 @@
       <c r="N61" s="66"/>
       <c r="O61" s="66"/>
       <c r="P61" s="66"/>
-      <c r="Q61" s="66">
+      <c r="Q61" s="66"/>
+      <c r="R61" s="66"/>
+      <c r="S61" s="66"/>
+      <c r="T61" s="66"/>
+      <c r="U61" s="66">
         <v>19.173999999999999</v>
       </c>
-      <c r="R61" s="66">
+      <c r="V61" s="66">
         <v>167.22800000000001</v>
       </c>
-      <c r="S61" s="66">
+      <c r="W61" s="66">
         <v>138.80000000000001</v>
       </c>
-      <c r="T61" s="66">
+      <c r="X61" s="66">
         <v>0</v>
       </c>
-      <c r="U61" s="66">
+      <c r="Y61" s="66">
         <v>1.7</v>
       </c>
-      <c r="V61" s="66">
+      <c r="Z61" s="66">
         <v>2.8</v>
       </c>
-      <c r="W61" s="66"/>
-      <c r="X61" s="66"/>
-      <c r="Y61" s="66"/>
-      <c r="Z61" s="66"/>
       <c r="AA61" s="66"/>
       <c r="AB61" s="66"/>
       <c r="AC61" s="66"/>
@@ -6748,8 +7092,12 @@
       <c r="AM61" s="66"/>
       <c r="AN61" s="66"/>
       <c r="AO61" s="66"/>
-    </row>
-    <row r="62" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP61" s="66"/>
+      <c r="AQ61" s="66"/>
+      <c r="AR61" s="66"/>
+      <c r="AS61" s="66"/>
+    </row>
+    <row r="62" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B62" s="65" t="s">
         <v>89</v>
       </c>
@@ -6767,28 +7115,28 @@
       <c r="N62" s="66"/>
       <c r="O62" s="66"/>
       <c r="P62" s="66"/>
-      <c r="Q62" s="66">
+      <c r="Q62" s="66"/>
+      <c r="R62" s="66"/>
+      <c r="S62" s="66"/>
+      <c r="T62" s="66"/>
+      <c r="U62" s="66">
         <v>5.6639999999999997</v>
       </c>
-      <c r="R62" s="66">
+      <c r="V62" s="66">
         <v>5.6109999999999998</v>
       </c>
-      <c r="S62" s="66">
+      <c r="W62" s="66">
         <v>17.899999999999999</v>
       </c>
-      <c r="T62" s="66">
+      <c r="X62" s="66">
         <v>10.4</v>
       </c>
-      <c r="U62" s="66">
+      <c r="Y62" s="66">
         <v>10.8</v>
       </c>
-      <c r="V62" s="66">
+      <c r="Z62" s="66">
         <v>9.3000000000000007</v>
       </c>
-      <c r="W62" s="66"/>
-      <c r="X62" s="66"/>
-      <c r="Y62" s="66"/>
-      <c r="Z62" s="66"/>
       <c r="AA62" s="66"/>
       <c r="AB62" s="66"/>
       <c r="AC62" s="66"/>
@@ -6804,8 +7152,12 @@
       <c r="AM62" s="66"/>
       <c r="AN62" s="66"/>
       <c r="AO62" s="66"/>
-    </row>
-    <row r="63" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP62" s="66"/>
+      <c r="AQ62" s="66"/>
+      <c r="AR62" s="66"/>
+      <c r="AS62" s="66"/>
+    </row>
+    <row r="63" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B63" s="65" t="s">
         <v>90</v>
       </c>
@@ -6822,38 +7174,38 @@
       <c r="M63" s="66"/>
       <c r="N63" s="66"/>
       <c r="O63" s="66"/>
-      <c r="P63" s="66">
-        <f t="shared" ref="P63:T63" si="45">+SUM(P58:P62)</f>
+      <c r="P63" s="66"/>
+      <c r="Q63" s="66"/>
+      <c r="R63" s="66"/>
+      <c r="S63" s="66"/>
+      <c r="T63" s="66">
+        <f t="shared" ref="T63:X63" si="51">+SUM(T58:T62)</f>
         <v>0</v>
       </c>
-      <c r="Q63" s="66">
-        <f t="shared" si="45"/>
+      <c r="U63" s="66">
+        <f t="shared" si="51"/>
         <v>51.113</v>
       </c>
-      <c r="R63" s="66">
-        <f t="shared" si="45"/>
+      <c r="V63" s="66">
+        <f t="shared" si="51"/>
         <v>183.13399999999999</v>
       </c>
-      <c r="S63" s="66">
-        <f t="shared" si="45"/>
+      <c r="W63" s="66">
+        <f t="shared" si="51"/>
         <v>170.20000000000002</v>
       </c>
-      <c r="T63" s="66">
-        <f t="shared" si="45"/>
+      <c r="X63" s="66">
+        <f t="shared" si="51"/>
         <v>212.9</v>
       </c>
-      <c r="U63" s="66">
-        <f>+SUM(U58:U62)</f>
+      <c r="Y63" s="66">
+        <f>+SUM(Y58:Y62)</f>
         <v>324.5</v>
       </c>
-      <c r="V63" s="66">
-        <f>+SUM(V58:V62)</f>
+      <c r="Z63" s="66">
+        <f>+SUM(Z58:Z62)</f>
         <v>478.6</v>
       </c>
-      <c r="W63" s="66"/>
-      <c r="X63" s="66"/>
-      <c r="Y63" s="66"/>
-      <c r="Z63" s="66"/>
       <c r="AA63" s="66"/>
       <c r="AB63" s="66"/>
       <c r="AC63" s="66"/>
@@ -6869,8 +7221,12 @@
       <c r="AM63" s="66"/>
       <c r="AN63" s="66"/>
       <c r="AO63" s="66"/>
-    </row>
-    <row r="64" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP63" s="66"/>
+      <c r="AQ63" s="66"/>
+      <c r="AR63" s="66"/>
+      <c r="AS63" s="66"/>
+    </row>
+    <row r="64" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B64" s="65" t="s">
         <v>91</v>
       </c>
@@ -6887,38 +7243,38 @@
       <c r="M64" s="66"/>
       <c r="N64" s="66"/>
       <c r="O64" s="66"/>
-      <c r="P64" s="66">
-        <f t="shared" ref="P64:T64" si="46">+P63+P57</f>
+      <c r="P64" s="66"/>
+      <c r="Q64" s="66"/>
+      <c r="R64" s="66"/>
+      <c r="S64" s="66"/>
+      <c r="T64" s="66">
+        <f t="shared" ref="T64:X64" si="52">+T63+T57</f>
         <v>0</v>
       </c>
-      <c r="Q64" s="66">
-        <f t="shared" si="46"/>
+      <c r="U64" s="66">
+        <f t="shared" si="52"/>
         <v>137.47500000000002</v>
       </c>
-      <c r="R64" s="66">
-        <f t="shared" si="46"/>
+      <c r="V64" s="66">
+        <f t="shared" si="52"/>
         <v>388.14499999999998</v>
       </c>
-      <c r="S64" s="66">
-        <f t="shared" si="46"/>
+      <c r="W64" s="66">
+        <f t="shared" si="52"/>
         <v>412.8</v>
       </c>
-      <c r="T64" s="66">
-        <f t="shared" si="46"/>
+      <c r="X64" s="66">
+        <f t="shared" si="52"/>
         <v>518.5</v>
       </c>
-      <c r="U64" s="66">
-        <f>+U63+U57</f>
+      <c r="Y64" s="66">
+        <f>+Y63+Y57</f>
         <v>984.90000000000009</v>
       </c>
-      <c r="V64" s="66">
-        <f>+V63+V57</f>
+      <c r="Z64" s="66">
+        <f>+Z63+Z57</f>
         <v>1202.9000000000001</v>
       </c>
-      <c r="W64" s="66"/>
-      <c r="X64" s="66"/>
-      <c r="Y64" s="66"/>
-      <c r="Z64" s="66"/>
       <c r="AA64" s="66"/>
       <c r="AB64" s="66"/>
       <c r="AC64" s="66"/>
@@ -6934,8 +7290,12 @@
       <c r="AM64" s="66"/>
       <c r="AN64" s="66"/>
       <c r="AO64" s="66"/>
-    </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP64" s="66"/>
+      <c r="AQ64" s="66"/>
+      <c r="AR64" s="66"/>
+      <c r="AS64" s="66"/>
+    </row>
+    <row r="65" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B65" s="65" t="s">
         <v>92</v>
       </c>
@@ -6953,28 +7313,28 @@
       <c r="N65" s="66"/>
       <c r="O65" s="66"/>
       <c r="P65" s="66"/>
-      <c r="Q65" s="66">
+      <c r="Q65" s="66"/>
+      <c r="R65" s="66"/>
+      <c r="S65" s="66"/>
+      <c r="T65" s="66"/>
+      <c r="U65" s="66">
         <v>245.09299999999999</v>
       </c>
-      <c r="R65" s="66">
+      <c r="V65" s="66">
         <v>838.37900000000002</v>
       </c>
-      <c r="S65" s="66">
+      <c r="W65" s="66">
         <v>969.5</v>
       </c>
-      <c r="T65" s="66">
+      <c r="X65" s="66">
         <v>1074.5</v>
       </c>
-      <c r="U65" s="66">
+      <c r="Y65" s="66">
         <v>1391.8</v>
       </c>
-      <c r="V65" s="66">
+      <c r="Z65" s="66">
         <v>1632.4</v>
       </c>
-      <c r="W65" s="66"/>
-      <c r="X65" s="66"/>
-      <c r="Y65" s="66"/>
-      <c r="Z65" s="66"/>
       <c r="AA65" s="66"/>
       <c r="AB65" s="66"/>
       <c r="AC65" s="66"/>
@@ -6990,8 +7350,12 @@
       <c r="AM65" s="66"/>
       <c r="AN65" s="66"/>
       <c r="AO65" s="66"/>
-    </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP65" s="66"/>
+      <c r="AQ65" s="66"/>
+      <c r="AR65" s="66"/>
+      <c r="AS65" s="66"/>
+    </row>
+    <row r="66" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B66" s="64" t="s">
         <v>93</v>
       </c>
@@ -7008,38 +7372,38 @@
       <c r="M66" s="66"/>
       <c r="N66" s="66"/>
       <c r="O66" s="66"/>
-      <c r="P66" s="81">
-        <f t="shared" ref="P66:T66" si="47">+P64+P65</f>
+      <c r="P66" s="66"/>
+      <c r="Q66" s="66"/>
+      <c r="R66" s="66"/>
+      <c r="S66" s="66"/>
+      <c r="T66" s="81">
+        <f t="shared" ref="T66:X66" si="53">+T64+T65</f>
         <v>0</v>
       </c>
-      <c r="Q66" s="81">
-        <f t="shared" si="47"/>
+      <c r="U66" s="81">
+        <f t="shared" si="53"/>
         <v>382.56799999999998</v>
       </c>
-      <c r="R66" s="81">
-        <f t="shared" si="47"/>
+      <c r="V66" s="81">
+        <f t="shared" si="53"/>
         <v>1226.5239999999999</v>
       </c>
-      <c r="S66" s="81">
-        <f t="shared" si="47"/>
+      <c r="W66" s="81">
+        <f t="shared" si="53"/>
         <v>1382.3</v>
       </c>
-      <c r="T66" s="81">
-        <f t="shared" si="47"/>
+      <c r="X66" s="81">
+        <f t="shared" si="53"/>
         <v>1593</v>
       </c>
-      <c r="U66" s="81">
-        <f>+U64+U65</f>
+      <c r="Y66" s="81">
+        <f>+Y64+Y65</f>
         <v>2376.6999999999998</v>
       </c>
-      <c r="V66" s="81">
-        <f>+V64+V65</f>
+      <c r="Z66" s="81">
+        <f>+Z64+Z65</f>
         <v>2835.3</v>
       </c>
-      <c r="W66" s="66"/>
-      <c r="X66" s="66"/>
-      <c r="Y66" s="66"/>
-      <c r="Z66" s="66"/>
       <c r="AA66" s="66"/>
       <c r="AB66" s="66"/>
       <c r="AC66" s="66"/>
@@ -7055,8 +7419,12 @@
       <c r="AM66" s="66"/>
       <c r="AN66" s="66"/>
       <c r="AO66" s="66"/>
-    </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP66" s="66"/>
+      <c r="AQ66" s="66"/>
+      <c r="AR66" s="66"/>
+      <c r="AS66" s="66"/>
+    </row>
+    <row r="67" spans="2:45" x14ac:dyDescent="0.2">
       <c r="C67" s="66"/>
       <c r="D67" s="66"/>
       <c r="E67" s="66"/>
@@ -7096,8 +7464,12 @@
       <c r="AM67" s="66"/>
       <c r="AN67" s="66"/>
       <c r="AO67" s="66"/>
-    </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP67" s="66"/>
+      <c r="AQ67" s="66"/>
+      <c r="AR67" s="66"/>
+      <c r="AS67" s="66"/>
+    </row>
+    <row r="68" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B68" s="65" t="s">
         <v>36</v>
       </c>
@@ -7114,31 +7486,31 @@
       <c r="M68" s="66"/>
       <c r="N68" s="66"/>
       <c r="O68" s="66"/>
-      <c r="P68" s="66">
+      <c r="P68" s="66"/>
+      <c r="Q68" s="66"/>
+      <c r="R68" s="66"/>
+      <c r="S68" s="66"/>
+      <c r="T68" s="66">
         <v>-1.4730000000000001</v>
       </c>
-      <c r="Q68" s="66">
+      <c r="U68" s="66">
         <v>-27.524000000000001</v>
       </c>
-      <c r="R68" s="66">
+      <c r="V68" s="66">
         <v>-170.22800000000001</v>
       </c>
-      <c r="S68" s="66">
+      <c r="W68" s="66">
         <v>57.7</v>
       </c>
-      <c r="T68" s="66">
+      <c r="X68" s="66">
         <v>79.599999999999994</v>
       </c>
-      <c r="U68" s="66">
+      <c r="Y68" s="66">
         <v>242.3</v>
       </c>
-      <c r="V68" s="66">
+      <c r="Z68" s="66">
         <v>203.7</v>
       </c>
-      <c r="W68" s="66"/>
-      <c r="X68" s="66"/>
-      <c r="Y68" s="66"/>
-      <c r="Z68" s="66"/>
       <c r="AA68" s="66"/>
       <c r="AB68" s="66"/>
       <c r="AC68" s="66"/>
@@ -7154,8 +7526,12 @@
       <c r="AM68" s="66"/>
       <c r="AN68" s="66"/>
       <c r="AO68" s="66"/>
-    </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP68" s="66"/>
+      <c r="AQ68" s="66"/>
+      <c r="AR68" s="66"/>
+      <c r="AS68" s="66"/>
+    </row>
+    <row r="69" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B69" s="65" t="s">
         <v>94</v>
       </c>
@@ -7172,31 +7548,31 @@
       <c r="M69" s="66"/>
       <c r="N69" s="66"/>
       <c r="O69" s="66"/>
-      <c r="P69" s="66">
+      <c r="P69" s="66"/>
+      <c r="Q69" s="66"/>
+      <c r="R69" s="66"/>
+      <c r="S69" s="66"/>
+      <c r="T69" s="66">
         <v>18.838000000000001</v>
       </c>
-      <c r="Q69" s="66">
+      <c r="U69" s="66">
         <v>48.631</v>
       </c>
-      <c r="R69" s="66">
+      <c r="V69" s="66">
         <v>192.43600000000001</v>
       </c>
-      <c r="S69" s="66">
+      <c r="W69" s="66">
         <v>38.299999999999997</v>
       </c>
-      <c r="T69" s="66">
+      <c r="X69" s="66">
         <v>27.3</v>
       </c>
-      <c r="U69" s="66">
+      <c r="Y69" s="66">
         <v>57.5</v>
       </c>
-      <c r="V69" s="66">
+      <c r="Z69" s="66">
         <v>66.599999999999994</v>
       </c>
-      <c r="W69" s="66"/>
-      <c r="X69" s="66"/>
-      <c r="Y69" s="66"/>
-      <c r="Z69" s="66"/>
       <c r="AA69" s="66"/>
       <c r="AB69" s="66"/>
       <c r="AC69" s="66"/>
@@ -7212,8 +7588,12 @@
       <c r="AM69" s="66"/>
       <c r="AN69" s="66"/>
       <c r="AO69" s="66"/>
-    </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP69" s="66"/>
+      <c r="AQ69" s="66"/>
+      <c r="AR69" s="66"/>
+      <c r="AS69" s="66"/>
+    </row>
+    <row r="70" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B70" s="65" t="s">
         <v>95</v>
       </c>
@@ -7230,31 +7610,31 @@
       <c r="M70" s="66"/>
       <c r="N70" s="66"/>
       <c r="O70" s="66"/>
-      <c r="P70" s="66">
+      <c r="P70" s="66"/>
+      <c r="Q70" s="66"/>
+      <c r="R70" s="66"/>
+      <c r="S70" s="66"/>
+      <c r="T70" s="66">
         <v>-0.14299999999999999</v>
       </c>
-      <c r="Q70" s="66">
+      <c r="U70" s="66">
         <v>0.95699999999999996</v>
       </c>
-      <c r="R70" s="66">
+      <c r="V70" s="66">
         <v>1.121</v>
       </c>
-      <c r="S70" s="66">
+      <c r="W70" s="66">
         <v>4.8</v>
       </c>
-      <c r="T70" s="66">
+      <c r="X70" s="66">
         <v>-7.5</v>
       </c>
-      <c r="U70" s="66">
+      <c r="Y70" s="66">
         <v>5.2</v>
       </c>
-      <c r="V70" s="66">
+      <c r="Z70" s="66">
         <v>4</v>
       </c>
-      <c r="W70" s="66"/>
-      <c r="X70" s="66"/>
-      <c r="Y70" s="66"/>
-      <c r="Z70" s="66"/>
       <c r="AA70" s="66"/>
       <c r="AB70" s="66"/>
       <c r="AC70" s="66"/>
@@ -7270,8 +7650,12 @@
       <c r="AM70" s="66"/>
       <c r="AN70" s="66"/>
       <c r="AO70" s="66"/>
-    </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP70" s="66"/>
+      <c r="AQ70" s="66"/>
+      <c r="AR70" s="66"/>
+      <c r="AS70" s="66"/>
+    </row>
+    <row r="71" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B71" s="65" t="s">
         <v>96</v>
       </c>
@@ -7288,31 +7672,31 @@
       <c r="M71" s="66"/>
       <c r="N71" s="66"/>
       <c r="O71" s="66"/>
-      <c r="P71" s="66">
+      <c r="P71" s="66"/>
+      <c r="Q71" s="66"/>
+      <c r="R71" s="66"/>
+      <c r="S71" s="66"/>
+      <c r="T71" s="66">
         <v>5.3419999999999996</v>
       </c>
-      <c r="Q71" s="66">
+      <c r="U71" s="66">
         <v>12.090999999999999</v>
       </c>
-      <c r="R71" s="66">
+      <c r="V71" s="66">
         <v>31.413</v>
       </c>
-      <c r="S71" s="66">
+      <c r="W71" s="66">
         <v>46.4</v>
       </c>
-      <c r="T71" s="66">
+      <c r="X71" s="66">
         <v>64.900000000000006</v>
       </c>
-      <c r="U71" s="66">
+      <c r="Y71" s="66">
         <v>104.6</v>
       </c>
-      <c r="V71" s="66">
+      <c r="Z71" s="66">
         <v>127.4</v>
       </c>
-      <c r="W71" s="66"/>
-      <c r="X71" s="66"/>
-      <c r="Y71" s="66"/>
-      <c r="Z71" s="66"/>
       <c r="AA71" s="66"/>
       <c r="AB71" s="66"/>
       <c r="AC71" s="66"/>
@@ -7328,8 +7712,12 @@
       <c r="AM71" s="66"/>
       <c r="AN71" s="66"/>
       <c r="AO71" s="66"/>
-    </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP71" s="66"/>
+      <c r="AQ71" s="66"/>
+      <c r="AR71" s="66"/>
+      <c r="AS71" s="66"/>
+    </row>
+    <row r="72" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B72" s="65" t="s">
         <v>98</v>
       </c>
@@ -7346,31 +7734,31 @@
       <c r="M72" s="66"/>
       <c r="N72" s="66"/>
       <c r="O72" s="66"/>
-      <c r="P72" s="66">
+      <c r="P72" s="66"/>
+      <c r="Q72" s="66"/>
+      <c r="R72" s="66"/>
+      <c r="S72" s="66"/>
+      <c r="T72" s="66">
         <v>0</v>
       </c>
-      <c r="Q72" s="66">
+      <c r="U72" s="66">
         <v>0</v>
       </c>
-      <c r="R72" s="66">
+      <c r="V72" s="66">
         <v>0</v>
       </c>
-      <c r="S72" s="66">
+      <c r="W72" s="66">
         <v>0.9</v>
       </c>
-      <c r="T72" s="66">
+      <c r="X72" s="66">
         <v>0.6</v>
       </c>
-      <c r="U72" s="66">
+      <c r="Y72" s="66">
         <v>0.7</v>
       </c>
-      <c r="V72" s="66">
+      <c r="Z72" s="66">
         <v>3.7</v>
       </c>
-      <c r="W72" s="66"/>
-      <c r="X72" s="66"/>
-      <c r="Y72" s="66"/>
-      <c r="Z72" s="66"/>
       <c r="AA72" s="66"/>
       <c r="AB72" s="66"/>
       <c r="AC72" s="66"/>
@@ -7386,8 +7774,12 @@
       <c r="AM72" s="66"/>
       <c r="AN72" s="66"/>
       <c r="AO72" s="66"/>
-    </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP72" s="66"/>
+      <c r="AQ72" s="66"/>
+      <c r="AR72" s="66"/>
+      <c r="AS72" s="66"/>
+    </row>
+    <row r="73" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B73" s="65" t="s">
         <v>99</v>
       </c>
@@ -7404,31 +7796,31 @@
       <c r="M73" s="66"/>
       <c r="N73" s="66"/>
       <c r="O73" s="66"/>
-      <c r="P73" s="66">
+      <c r="P73" s="66"/>
+      <c r="Q73" s="66"/>
+      <c r="R73" s="66"/>
+      <c r="S73" s="66"/>
+      <c r="T73" s="66">
         <v>0.502</v>
       </c>
-      <c r="Q73" s="66">
+      <c r="U73" s="66">
         <v>0.60199999999999998</v>
       </c>
-      <c r="R73" s="66">
+      <c r="V73" s="66">
         <v>2.7770000000000001</v>
       </c>
-      <c r="S73" s="66">
+      <c r="W73" s="66">
         <v>-0.8</v>
       </c>
-      <c r="T73" s="66">
+      <c r="X73" s="66">
         <v>-4.5</v>
       </c>
-      <c r="U73" s="66">
+      <c r="Y73" s="66">
         <v>-7.2</v>
       </c>
-      <c r="V73" s="66">
+      <c r="Z73" s="66">
         <v>-8.5</v>
       </c>
-      <c r="W73" s="66"/>
-      <c r="X73" s="66"/>
-      <c r="Y73" s="66"/>
-      <c r="Z73" s="66"/>
       <c r="AA73" s="66"/>
       <c r="AB73" s="66"/>
       <c r="AC73" s="66"/>
@@ -7444,8 +7836,12 @@
       <c r="AM73" s="66"/>
       <c r="AN73" s="66"/>
       <c r="AO73" s="66"/>
-    </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP73" s="66"/>
+      <c r="AQ73" s="66"/>
+      <c r="AR73" s="66"/>
+      <c r="AS73" s="66"/>
+    </row>
+    <row r="74" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B74" s="65" t="s">
         <v>100</v>
       </c>
@@ -7462,31 +7858,31 @@
       <c r="M74" s="66"/>
       <c r="N74" s="66"/>
       <c r="O74" s="66"/>
-      <c r="P74" s="66">
+      <c r="P74" s="66"/>
+      <c r="Q74" s="66"/>
+      <c r="R74" s="66"/>
+      <c r="S74" s="66"/>
+      <c r="T74" s="66">
         <v>1.518</v>
       </c>
-      <c r="Q74" s="66">
+      <c r="U74" s="66">
         <v>6.6660000000000004</v>
       </c>
-      <c r="R74" s="66">
+      <c r="V74" s="66">
         <v>15.183</v>
       </c>
-      <c r="S74" s="66">
+      <c r="W74" s="66">
         <v>-8.3000000000000007</v>
       </c>
-      <c r="T74" s="66">
+      <c r="X74" s="66">
         <v>102.9</v>
       </c>
-      <c r="U74" s="66">
+      <c r="Y74" s="66">
         <v>-70.900000000000006</v>
       </c>
-      <c r="V74" s="66">
+      <c r="Z74" s="66">
         <v>165.6</v>
       </c>
-      <c r="W74" s="66"/>
-      <c r="X74" s="66"/>
-      <c r="Y74" s="66"/>
-      <c r="Z74" s="66"/>
       <c r="AA74" s="66"/>
       <c r="AB74" s="66"/>
       <c r="AC74" s="66"/>
@@ -7502,8 +7898,12 @@
       <c r="AM74" s="66"/>
       <c r="AN74" s="66"/>
       <c r="AO74" s="66"/>
-    </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP74" s="66"/>
+      <c r="AQ74" s="66"/>
+      <c r="AR74" s="66"/>
+      <c r="AS74" s="66"/>
+    </row>
+    <row r="75" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B75" s="65" t="s">
         <v>101</v>
       </c>
@@ -7520,31 +7920,31 @@
       <c r="M75" s="66"/>
       <c r="N75" s="66"/>
       <c r="O75" s="66"/>
-      <c r="P75" s="66">
+      <c r="P75" s="66"/>
+      <c r="Q75" s="66"/>
+      <c r="R75" s="66"/>
+      <c r="S75" s="66"/>
+      <c r="T75" s="66">
         <v>4.62</v>
       </c>
-      <c r="Q75" s="66">
+      <c r="U75" s="66">
         <v>3.0830000000000002</v>
       </c>
-      <c r="R75" s="66">
+      <c r="V75" s="66">
         <v>10.625</v>
       </c>
-      <c r="S75" s="66">
+      <c r="W75" s="66">
         <v>20.2</v>
       </c>
-      <c r="T75" s="66">
+      <c r="X75" s="66">
         <v>-10.5</v>
       </c>
-      <c r="U75" s="66">
+      <c r="Y75" s="66">
         <v>37.4</v>
       </c>
-      <c r="V75" s="66">
+      <c r="Z75" s="66">
         <v>1.5</v>
       </c>
-      <c r="W75" s="66"/>
-      <c r="X75" s="66"/>
-      <c r="Y75" s="66"/>
-      <c r="Z75" s="66"/>
       <c r="AA75" s="66"/>
       <c r="AB75" s="66"/>
       <c r="AC75" s="66"/>
@@ -7560,8 +7960,12 @@
       <c r="AM75" s="66"/>
       <c r="AN75" s="66"/>
       <c r="AO75" s="66"/>
-    </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP75" s="66"/>
+      <c r="AQ75" s="66"/>
+      <c r="AR75" s="66"/>
+      <c r="AS75" s="66"/>
+    </row>
+    <row r="76" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B76" s="65" t="s">
         <v>102</v>
       </c>
@@ -7578,31 +7982,31 @@
       <c r="M76" s="66"/>
       <c r="N76" s="66"/>
       <c r="O76" s="66"/>
-      <c r="P76" s="66">
+      <c r="P76" s="66"/>
+      <c r="Q76" s="66"/>
+      <c r="R76" s="66"/>
+      <c r="S76" s="66"/>
+      <c r="T76" s="66">
         <v>-21.481000000000002</v>
       </c>
-      <c r="Q76" s="66">
+      <c r="U76" s="66">
         <v>-13.481999999999999</v>
       </c>
-      <c r="R76" s="66">
+      <c r="V76" s="66">
         <v>-46.993000000000002</v>
       </c>
-      <c r="S76" s="66">
+      <c r="W76" s="66">
         <v>-78.599999999999994</v>
       </c>
-      <c r="T76" s="66">
+      <c r="X76" s="66">
         <v>-46.9</v>
       </c>
-      <c r="U76" s="66">
+      <c r="Y76" s="66">
         <v>-30.1</v>
       </c>
-      <c r="V76" s="66">
+      <c r="Z76" s="66">
         <v>-96.1</v>
       </c>
-      <c r="W76" s="66"/>
-      <c r="X76" s="66"/>
-      <c r="Y76" s="66"/>
-      <c r="Z76" s="66"/>
       <c r="AA76" s="66"/>
       <c r="AB76" s="66"/>
       <c r="AC76" s="66"/>
@@ -7618,8 +8022,12 @@
       <c r="AM76" s="66"/>
       <c r="AN76" s="66"/>
       <c r="AO76" s="66"/>
-    </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP76" s="66"/>
+      <c r="AQ76" s="66"/>
+      <c r="AR76" s="66"/>
+      <c r="AS76" s="66"/>
+    </row>
+    <row r="77" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B77" s="65" t="s">
         <v>103</v>
       </c>
@@ -7636,31 +8044,31 @@
       <c r="M77" s="66"/>
       <c r="N77" s="66"/>
       <c r="O77" s="66"/>
-      <c r="P77" s="66">
+      <c r="P77" s="66"/>
+      <c r="Q77" s="66"/>
+      <c r="R77" s="66"/>
+      <c r="S77" s="66"/>
+      <c r="T77" s="66">
         <v>-12.353</v>
       </c>
-      <c r="Q77" s="66">
+      <c r="U77" s="66">
         <v>-61.305</v>
       </c>
-      <c r="R77" s="66">
+      <c r="V77" s="66">
         <v>-31.771000000000001</v>
       </c>
-      <c r="S77" s="66">
+      <c r="W77" s="66">
         <v>-273</v>
       </c>
-      <c r="T77" s="66">
+      <c r="X77" s="66">
         <v>-10</v>
       </c>
-      <c r="U77" s="66">
+      <c r="Y77" s="66">
         <v>-27.8</v>
       </c>
-      <c r="V77" s="97">
+      <c r="Z77" s="91">
         <v>-82.4</v>
       </c>
-      <c r="W77" s="66"/>
-      <c r="X77" s="66"/>
-      <c r="Y77" s="66"/>
-      <c r="Z77" s="66"/>
       <c r="AA77" s="66"/>
       <c r="AB77" s="66"/>
       <c r="AC77" s="66"/>
@@ -7676,8 +8084,12 @@
       <c r="AM77" s="66"/>
       <c r="AN77" s="66"/>
       <c r="AO77" s="66"/>
-    </row>
-    <row r="78" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP77" s="66"/>
+      <c r="AQ77" s="66"/>
+      <c r="AR77" s="66"/>
+      <c r="AS77" s="66"/>
+    </row>
+    <row r="78" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B78" s="65" t="s">
         <v>104</v>
       </c>
@@ -7694,31 +8106,31 @@
       <c r="M78" s="66"/>
       <c r="N78" s="66"/>
       <c r="O78" s="66"/>
-      <c r="P78" s="66">
+      <c r="P78" s="66"/>
+      <c r="Q78" s="66"/>
+      <c r="R78" s="66"/>
+      <c r="S78" s="66"/>
+      <c r="T78" s="66">
         <v>3.1539999999999999</v>
       </c>
-      <c r="Q78" s="66">
+      <c r="U78" s="66">
         <v>25.564</v>
       </c>
-      <c r="R78" s="66">
+      <c r="V78" s="66">
         <v>4.327</v>
       </c>
-      <c r="S78" s="66">
+      <c r="W78" s="66">
         <v>65.8</v>
       </c>
-      <c r="T78" s="66">
+      <c r="X78" s="66">
         <v>-44.3</v>
       </c>
-      <c r="U78" s="66">
+      <c r="Y78" s="66">
         <v>104</v>
       </c>
-      <c r="V78" s="66">
+      <c r="Z78" s="66">
         <v>-9.1999999999999993</v>
       </c>
-      <c r="W78" s="66"/>
-      <c r="X78" s="66"/>
-      <c r="Y78" s="66"/>
-      <c r="Z78" s="66"/>
       <c r="AA78" s="66"/>
       <c r="AB78" s="66"/>
       <c r="AC78" s="66"/>
@@ -7734,8 +8146,12 @@
       <c r="AM78" s="66"/>
       <c r="AN78" s="66"/>
       <c r="AO78" s="66"/>
-    </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP78" s="66"/>
+      <c r="AQ78" s="66"/>
+      <c r="AR78" s="66"/>
+      <c r="AS78" s="66"/>
+    </row>
+    <row r="79" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B79" s="65" t="s">
         <v>105</v>
       </c>
@@ -7752,38 +8168,38 @@
       <c r="M79" s="66"/>
       <c r="N79" s="66"/>
       <c r="O79" s="66"/>
-      <c r="P79" s="66">
-        <f t="shared" ref="P79" si="48">+SUM(P76:P78)</f>
+      <c r="P79" s="66"/>
+      <c r="Q79" s="66"/>
+      <c r="R79" s="66"/>
+      <c r="S79" s="66"/>
+      <c r="T79" s="66">
+        <f t="shared" ref="T79" si="54">+SUM(T76:T78)</f>
         <v>-30.680000000000003</v>
       </c>
-      <c r="Q79" s="66">
-        <f t="shared" ref="Q79" si="49">+SUM(Q76:Q78)</f>
+      <c r="U79" s="66">
+        <f t="shared" ref="U79" si="55">+SUM(U76:U78)</f>
         <v>-49.223000000000006</v>
       </c>
-      <c r="R79" s="66">
-        <f t="shared" ref="R79:T79" si="50">+SUM(R76:R78)</f>
+      <c r="V79" s="66">
+        <f t="shared" ref="V79:X79" si="56">+SUM(V76:V78)</f>
         <v>-74.437000000000012</v>
       </c>
-      <c r="S79" s="66">
-        <f t="shared" si="50"/>
+      <c r="W79" s="66">
+        <f t="shared" si="56"/>
         <v>-285.8</v>
       </c>
-      <c r="T79" s="66">
-        <f t="shared" si="50"/>
+      <c r="X79" s="66">
+        <f t="shared" si="56"/>
         <v>-101.19999999999999</v>
       </c>
-      <c r="U79" s="66">
-        <f>+SUM(U76:U78)</f>
+      <c r="Y79" s="66">
+        <f>+SUM(Y76:Y78)</f>
         <v>46.099999999999994</v>
       </c>
-      <c r="V79" s="66">
-        <f>+SUM(V76:V78)</f>
+      <c r="Z79" s="66">
+        <f>+SUM(Z76:Z78)</f>
         <v>-187.7</v>
       </c>
-      <c r="W79" s="66"/>
-      <c r="X79" s="66"/>
-      <c r="Y79" s="66"/>
-      <c r="Z79" s="66"/>
       <c r="AA79" s="66"/>
       <c r="AB79" s="66"/>
       <c r="AC79" s="66"/>
@@ -7799,8 +8215,12 @@
       <c r="AM79" s="66"/>
       <c r="AN79" s="66"/>
       <c r="AO79" s="66"/>
-    </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP79" s="66"/>
+      <c r="AQ79" s="66"/>
+      <c r="AR79" s="66"/>
+      <c r="AS79" s="66"/>
+    </row>
+    <row r="80" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B80" s="65" t="s">
         <v>106</v>
       </c>
@@ -7817,31 +8237,31 @@
       <c r="M80" s="66"/>
       <c r="N80" s="66"/>
       <c r="O80" s="66"/>
-      <c r="P80" s="66">
+      <c r="P80" s="66"/>
+      <c r="Q80" s="66"/>
+      <c r="R80" s="66"/>
+      <c r="S80" s="66"/>
+      <c r="T80" s="66">
         <v>-2.677</v>
       </c>
-      <c r="Q80" s="66">
+      <c r="U80" s="66">
         <v>-6.5110000000000001</v>
       </c>
-      <c r="R80" s="66">
+      <c r="V80" s="66">
         <v>8.0950000000000006</v>
       </c>
-      <c r="S80" s="66">
+      <c r="W80" s="66">
         <v>-67.599999999999994</v>
       </c>
-      <c r="T80" s="66">
+      <c r="X80" s="66">
         <v>93.4</v>
       </c>
-      <c r="U80" s="66">
+      <c r="Y80" s="66">
         <v>95.7</v>
       </c>
-      <c r="V80" s="66">
+      <c r="Z80" s="66">
         <v>25</v>
       </c>
-      <c r="W80" s="66"/>
-      <c r="X80" s="66"/>
-      <c r="Y80" s="66"/>
-      <c r="Z80" s="66"/>
       <c r="AA80" s="66"/>
       <c r="AB80" s="66"/>
       <c r="AC80" s="66"/>
@@ -7857,8 +8277,12 @@
       <c r="AM80" s="66"/>
       <c r="AN80" s="66"/>
       <c r="AO80" s="66"/>
-    </row>
-    <row r="81" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP80" s="66"/>
+      <c r="AQ80" s="66"/>
+      <c r="AR80" s="66"/>
+      <c r="AS80" s="66"/>
+    </row>
+    <row r="81" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B81" s="65" t="s">
         <v>107</v>
       </c>
@@ -7875,31 +8299,31 @@
       <c r="M81" s="66"/>
       <c r="N81" s="66"/>
       <c r="O81" s="66"/>
-      <c r="P81" s="66">
+      <c r="P81" s="66"/>
+      <c r="Q81" s="66"/>
+      <c r="R81" s="66"/>
+      <c r="S81" s="66"/>
+      <c r="T81" s="66">
         <v>1.099</v>
       </c>
-      <c r="Q81" s="66">
+      <c r="U81" s="66">
         <v>1.6739999999999999</v>
       </c>
-      <c r="R81" s="66">
+      <c r="V81" s="66">
         <v>4.3680000000000003</v>
       </c>
-      <c r="S81" s="66">
+      <c r="W81" s="66">
         <v>-7.4</v>
       </c>
-      <c r="T81" s="66">
+      <c r="X81" s="66">
         <v>4.8</v>
       </c>
-      <c r="U81" s="66">
+      <c r="Y81" s="66">
         <v>18</v>
       </c>
-      <c r="V81" s="66">
+      <c r="Z81" s="66">
         <v>-7.8</v>
       </c>
-      <c r="W81" s="66"/>
-      <c r="X81" s="66"/>
-      <c r="Y81" s="66"/>
-      <c r="Z81" s="66"/>
       <c r="AA81" s="66"/>
       <c r="AB81" s="66"/>
       <c r="AC81" s="66"/>
@@ -7915,8 +8339,12 @@
       <c r="AM81" s="66"/>
       <c r="AN81" s="66"/>
       <c r="AO81" s="66"/>
-    </row>
-    <row r="82" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP81" s="66"/>
+      <c r="AQ81" s="66"/>
+      <c r="AR81" s="66"/>
+      <c r="AS81" s="66"/>
+    </row>
+    <row r="82" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B82" s="65" t="s">
         <v>108</v>
       </c>
@@ -7933,31 +8361,31 @@
       <c r="M82" s="66"/>
       <c r="N82" s="66"/>
       <c r="O82" s="66"/>
-      <c r="P82" s="66">
+      <c r="P82" s="66"/>
+      <c r="Q82" s="66"/>
+      <c r="R82" s="66"/>
+      <c r="S82" s="66"/>
+      <c r="T82" s="66">
         <v>0</v>
       </c>
-      <c r="Q82" s="66">
+      <c r="U82" s="66">
         <v>0</v>
       </c>
-      <c r="R82" s="66">
+      <c r="V82" s="66">
         <v>0</v>
       </c>
-      <c r="S82" s="66">
+      <c r="W82" s="66">
         <v>5.6</v>
       </c>
-      <c r="T82" s="66">
+      <c r="X82" s="66">
         <v>11</v>
       </c>
-      <c r="U82" s="66">
+      <c r="Y82" s="66">
         <v>22.5</v>
       </c>
-      <c r="V82" s="66">
+      <c r="Z82" s="66">
         <v>30.1</v>
       </c>
-      <c r="W82" s="66"/>
-      <c r="X82" s="66"/>
-      <c r="Y82" s="66"/>
-      <c r="Z82" s="66"/>
       <c r="AA82" s="66"/>
       <c r="AB82" s="66"/>
       <c r="AC82" s="66"/>
@@ -7973,8 +8401,12 @@
       <c r="AM82" s="66"/>
       <c r="AN82" s="66"/>
       <c r="AO82" s="66"/>
-    </row>
-    <row r="83" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP82" s="66"/>
+      <c r="AQ82" s="66"/>
+      <c r="AR82" s="66"/>
+      <c r="AS82" s="66"/>
+    </row>
+    <row r="83" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B83" s="65" t="s">
         <v>109</v>
       </c>
@@ -7991,31 +8423,31 @@
       <c r="M83" s="66"/>
       <c r="N83" s="66"/>
       <c r="O83" s="66"/>
-      <c r="P83" s="66">
+      <c r="P83" s="66"/>
+      <c r="Q83" s="66"/>
+      <c r="R83" s="66"/>
+      <c r="S83" s="66"/>
+      <c r="T83" s="66">
         <v>-2.1629999999999998</v>
       </c>
-      <c r="Q83" s="66">
+      <c r="U83" s="66">
         <v>-5.1740000000000004</v>
       </c>
-      <c r="R83" s="66">
+      <c r="V83" s="66">
         <v>-4.407</v>
       </c>
-      <c r="S83" s="66">
+      <c r="W83" s="66">
         <v>-31</v>
       </c>
-      <c r="T83" s="66">
+      <c r="X83" s="66">
         <v>-28.6</v>
       </c>
-      <c r="U83" s="66">
+      <c r="Y83" s="66">
         <v>-41.2</v>
       </c>
-      <c r="V83" s="66">
+      <c r="Z83" s="66">
         <v>-64</v>
       </c>
-      <c r="W83" s="66"/>
-      <c r="X83" s="66"/>
-      <c r="Y83" s="66"/>
-      <c r="Z83" s="66"/>
       <c r="AA83" s="66"/>
       <c r="AB83" s="66"/>
       <c r="AC83" s="66"/>
@@ -8031,8 +8463,12 @@
       <c r="AM83" s="66"/>
       <c r="AN83" s="66"/>
       <c r="AO83" s="66"/>
-    </row>
-    <row r="84" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP83" s="66"/>
+      <c r="AQ83" s="66"/>
+      <c r="AR83" s="66"/>
+      <c r="AS83" s="66"/>
+    </row>
+    <row r="84" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B84" s="64" t="s">
         <v>97</v>
       </c>
@@ -8049,38 +8485,38 @@
       <c r="M84" s="66"/>
       <c r="N84" s="66"/>
       <c r="O84" s="66"/>
-      <c r="P84" s="81">
-        <f t="shared" ref="P84" si="51">+SUM(P68:P75)+P79+SUM(P80:P83)</f>
+      <c r="P84" s="66"/>
+      <c r="Q84" s="66"/>
+      <c r="R84" s="66"/>
+      <c r="S84" s="66"/>
+      <c r="T84" s="81">
+        <f t="shared" ref="T84" si="57">+SUM(T68:T75)+T79+SUM(T80:T83)</f>
         <v>-5.2170000000000023</v>
       </c>
-      <c r="Q84" s="81">
-        <f t="shared" ref="Q84" si="52">+SUM(Q68:Q75)+Q79+SUM(Q80:Q83)</f>
+      <c r="U84" s="81">
+        <f t="shared" ref="U84" si="58">+SUM(U68:U75)+U79+SUM(U80:U83)</f>
         <v>-14.728000000000005</v>
       </c>
-      <c r="R84" s="81">
-        <f t="shared" ref="R84:S84" si="53">+SUM(R68:R75)+R79+SUM(R80:R83)</f>
+      <c r="V84" s="81">
+        <f t="shared" ref="V84:W84" si="59">+SUM(V68:V75)+V79+SUM(V80:V83)</f>
         <v>16.945999999999987</v>
       </c>
-      <c r="S84" s="81">
-        <f t="shared" si="53"/>
+      <c r="W84" s="81">
+        <f t="shared" si="59"/>
         <v>-227.00000000000006</v>
       </c>
-      <c r="T84" s="81">
-        <f>+SUM(T68:T75)+T79+SUM(T80:T83)</f>
+      <c r="X84" s="81">
+        <f>+SUM(X68:X75)+X79+SUM(X80:X83)</f>
         <v>232.20000000000002</v>
       </c>
-      <c r="U84" s="81">
-        <f>+SUM(U68:U75)+U79+SUM(U80:U83)</f>
+      <c r="Y84" s="81">
+        <f>+SUM(Y68:Y75)+Y79+SUM(Y80:Y83)</f>
         <v>510.70000000000005</v>
       </c>
-      <c r="V84" s="81">
-        <f>+SUM(V68:V75)+V79+SUM(V80:V83)</f>
+      <c r="Z84" s="81">
+        <f>+SUM(Z68:Z75)+Z79+SUM(Z80:Z83)</f>
         <v>359.59999999999991</v>
       </c>
-      <c r="W84" s="66"/>
-      <c r="X84" s="66"/>
-      <c r="Y84" s="66"/>
-      <c r="Z84" s="66"/>
       <c r="AA84" s="66"/>
       <c r="AB84" s="66"/>
       <c r="AC84" s="66"/>
@@ -8096,8 +8532,12 @@
       <c r="AM84" s="66"/>
       <c r="AN84" s="66"/>
       <c r="AO84" s="66"/>
-    </row>
-    <row r="85" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP84" s="66"/>
+      <c r="AQ84" s="66"/>
+      <c r="AR84" s="66"/>
+      <c r="AS84" s="66"/>
+    </row>
+    <row r="85" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B85" s="65" t="s">
         <v>110</v>
       </c>
@@ -8114,31 +8554,31 @@
       <c r="M85" s="66"/>
       <c r="N85" s="66"/>
       <c r="O85" s="66"/>
-      <c r="P85" s="66">
+      <c r="P85" s="66"/>
+      <c r="Q85" s="66"/>
+      <c r="R85" s="66"/>
+      <c r="S85" s="66"/>
+      <c r="T85" s="66">
         <v>-7.4320000000000004</v>
       </c>
-      <c r="Q85" s="66">
+      <c r="U85" s="66">
         <v>-10.986000000000001</v>
       </c>
-      <c r="R85" s="66">
+      <c r="V85" s="66">
         <v>-24.638999999999999</v>
       </c>
-      <c r="S85" s="66">
+      <c r="W85" s="66">
         <v>-60.3</v>
       </c>
-      <c r="T85" s="66">
+      <c r="X85" s="66">
         <v>-42.8</v>
       </c>
-      <c r="U85" s="66">
+      <c r="Y85" s="66">
         <v>-60.5</v>
       </c>
-      <c r="V85" s="66">
+      <c r="Z85" s="66">
         <v>-72.900000000000006</v>
       </c>
-      <c r="W85" s="66"/>
-      <c r="X85" s="66"/>
-      <c r="Y85" s="66"/>
-      <c r="Z85" s="66"/>
       <c r="AA85" s="66"/>
       <c r="AB85" s="66"/>
       <c r="AC85" s="66"/>
@@ -8154,8 +8594,12 @@
       <c r="AM85" s="66"/>
       <c r="AN85" s="66"/>
       <c r="AO85" s="66"/>
-    </row>
-    <row r="86" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP85" s="66"/>
+      <c r="AQ85" s="66"/>
+      <c r="AR85" s="66"/>
+      <c r="AS85" s="66"/>
+    </row>
+    <row r="86" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B86" s="65" t="s">
         <v>111</v>
       </c>
@@ -8172,31 +8616,31 @@
       <c r="M86" s="66"/>
       <c r="N86" s="66"/>
       <c r="O86" s="66"/>
-      <c r="P86" s="66">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="66">
-        <v>0</v>
-      </c>
-      <c r="R86" s="66">
-        <v>0</v>
-      </c>
-      <c r="S86" s="66">
-        <v>0</v>
-      </c>
+      <c r="P86" s="66"/>
+      <c r="Q86" s="66"/>
+      <c r="R86" s="66"/>
+      <c r="S86" s="66"/>
       <c r="T86" s="66">
         <v>0</v>
       </c>
       <c r="U86" s="66">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="V86" s="66">
         <v>0</v>
       </c>
-      <c r="W86" s="66"/>
-      <c r="X86" s="66"/>
-      <c r="Y86" s="66"/>
-      <c r="Z86" s="66"/>
+      <c r="W86" s="66">
+        <v>0</v>
+      </c>
+      <c r="X86" s="66">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="66">
+        <v>0.1</v>
+      </c>
+      <c r="Z86" s="66">
+        <v>0</v>
+      </c>
       <c r="AA86" s="66"/>
       <c r="AB86" s="66"/>
       <c r="AC86" s="66"/>
@@ -8212,8 +8656,12 @@
       <c r="AM86" s="66"/>
       <c r="AN86" s="66"/>
       <c r="AO86" s="66"/>
-    </row>
-    <row r="87" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP86" s="66"/>
+      <c r="AQ86" s="66"/>
+      <c r="AR86" s="66"/>
+      <c r="AS86" s="66"/>
+    </row>
+    <row r="87" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B87" s="65" t="s">
         <v>112</v>
       </c>
@@ -8230,34 +8678,34 @@
       <c r="M87" s="66"/>
       <c r="N87" s="66"/>
       <c r="O87" s="66"/>
-      <c r="P87" s="66">
+      <c r="P87" s="66"/>
+      <c r="Q87" s="66"/>
+      <c r="R87" s="66"/>
+      <c r="S87" s="66"/>
+      <c r="T87" s="66">
         <f>-1.785-0.321</f>
         <v>-2.1059999999999999</v>
       </c>
-      <c r="Q87" s="66">
+      <c r="U87" s="66">
         <f>-7.612-0.026</f>
         <v>-7.6379999999999999</v>
       </c>
-      <c r="R87" s="66">
+      <c r="V87" s="66">
         <f>-11.6-0.2</f>
         <v>-11.799999999999999</v>
       </c>
-      <c r="S87" s="66">
+      <c r="W87" s="66">
         <v>-22.7</v>
       </c>
-      <c r="T87" s="66">
+      <c r="X87" s="66">
         <v>-4.4000000000000004</v>
       </c>
-      <c r="U87" s="66">
+      <c r="Y87" s="66">
         <v>-4.5</v>
       </c>
-      <c r="V87" s="66">
+      <c r="Z87" s="66">
         <v>-5.7</v>
       </c>
-      <c r="W87" s="66"/>
-      <c r="X87" s="66"/>
-      <c r="Y87" s="66"/>
-      <c r="Z87" s="66"/>
       <c r="AA87" s="66"/>
       <c r="AB87" s="66"/>
       <c r="AC87" s="66"/>
@@ -8273,8 +8721,12 @@
       <c r="AM87" s="66"/>
       <c r="AN87" s="66"/>
       <c r="AO87" s="66"/>
-    </row>
-    <row r="88" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP87" s="66"/>
+      <c r="AQ87" s="66"/>
+      <c r="AR87" s="66"/>
+      <c r="AS87" s="66"/>
+    </row>
+    <row r="88" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B88" s="64" t="s">
         <v>113</v>
       </c>
@@ -8291,38 +8743,38 @@
       <c r="M88" s="66"/>
       <c r="N88" s="66"/>
       <c r="O88" s="66"/>
-      <c r="P88" s="81">
-        <f t="shared" ref="P88" si="54">+SUM(P85:P87)</f>
+      <c r="P88" s="66"/>
+      <c r="Q88" s="66"/>
+      <c r="R88" s="66"/>
+      <c r="S88" s="66"/>
+      <c r="T88" s="81">
+        <f t="shared" ref="T88" si="60">+SUM(T85:T87)</f>
         <v>-9.5380000000000003</v>
       </c>
-      <c r="Q88" s="81">
-        <f t="shared" ref="Q88" si="55">+SUM(Q85:Q87)</f>
+      <c r="U88" s="81">
+        <f t="shared" ref="U88" si="61">+SUM(U85:U87)</f>
         <v>-18.624000000000002</v>
       </c>
-      <c r="R88" s="81">
-        <f t="shared" ref="R88:T88" si="56">+SUM(R85:R87)</f>
+      <c r="V88" s="81">
+        <f t="shared" ref="V88:X88" si="62">+SUM(V85:V87)</f>
         <v>-36.439</v>
       </c>
-      <c r="S88" s="81">
-        <f t="shared" si="56"/>
+      <c r="W88" s="81">
+        <f t="shared" si="62"/>
         <v>-83</v>
       </c>
-      <c r="T88" s="81">
-        <f t="shared" si="56"/>
+      <c r="X88" s="81">
+        <f t="shared" si="62"/>
         <v>-47.199999999999996</v>
       </c>
-      <c r="U88" s="81">
-        <f>+SUM(U85:U87)</f>
+      <c r="Y88" s="81">
+        <f>+SUM(Y85:Y87)</f>
         <v>-64.900000000000006</v>
       </c>
-      <c r="V88" s="81">
-        <f>+SUM(V85:V87)</f>
+      <c r="Z88" s="81">
+        <f>+SUM(Z85:Z87)</f>
         <v>-78.600000000000009</v>
       </c>
-      <c r="W88" s="66"/>
-      <c r="X88" s="66"/>
-      <c r="Y88" s="66"/>
-      <c r="Z88" s="66"/>
       <c r="AA88" s="66"/>
       <c r="AB88" s="66"/>
       <c r="AC88" s="66"/>
@@ -8338,8 +8790,12 @@
       <c r="AM88" s="66"/>
       <c r="AN88" s="66"/>
       <c r="AO88" s="66"/>
-    </row>
-    <row r="89" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP88" s="66"/>
+      <c r="AQ88" s="66"/>
+      <c r="AR88" s="66"/>
+      <c r="AS88" s="66"/>
+    </row>
+    <row r="89" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B89" s="65" t="s">
         <v>116</v>
       </c>
@@ -8356,33 +8812,33 @@
       <c r="M89" s="66"/>
       <c r="N89" s="66"/>
       <c r="O89" s="66"/>
-      <c r="P89" s="66">
+      <c r="P89" s="66"/>
+      <c r="Q89" s="66"/>
+      <c r="R89" s="66"/>
+      <c r="S89" s="66"/>
+      <c r="T89" s="66">
         <f>3-1.2-2</f>
         <v>-0.19999999999999996</v>
       </c>
-      <c r="Q89" s="66">
+      <c r="U89" s="66">
         <f>-(3+3.399)</f>
         <v>-6.399</v>
       </c>
-      <c r="R89" s="66">
+      <c r="V89" s="66">
         <v>-13.311</v>
       </c>
-      <c r="S89" s="66">
+      <c r="W89" s="66">
         <v>-15.4</v>
       </c>
-      <c r="T89" s="66">
+      <c r="X89" s="66">
         <v>-25.5</v>
       </c>
-      <c r="U89" s="66">
+      <c r="Y89" s="66">
         <v>-51.3</v>
       </c>
-      <c r="V89" s="66">
+      <c r="Z89" s="66">
         <v>-69.900000000000006</v>
       </c>
-      <c r="W89" s="66"/>
-      <c r="X89" s="66"/>
-      <c r="Y89" s="66"/>
-      <c r="Z89" s="66"/>
       <c r="AA89" s="66"/>
       <c r="AB89" s="66"/>
       <c r="AC89" s="66"/>
@@ -8398,8 +8854,12 @@
       <c r="AM89" s="66"/>
       <c r="AN89" s="66"/>
       <c r="AO89" s="66"/>
-    </row>
-    <row r="90" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP89" s="66"/>
+      <c r="AQ89" s="66"/>
+      <c r="AR89" s="66"/>
+      <c r="AS89" s="66"/>
+    </row>
+    <row r="90" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B90" s="65" t="s">
         <v>117</v>
       </c>
@@ -8416,33 +8876,33 @@
       <c r="M90" s="66"/>
       <c r="N90" s="66"/>
       <c r="O90" s="66"/>
-      <c r="P90" s="66">
+      <c r="P90" s="66"/>
+      <c r="Q90" s="66"/>
+      <c r="R90" s="66"/>
+      <c r="S90" s="66"/>
+      <c r="T90" s="66">
         <v>0</v>
       </c>
-      <c r="Q90" s="66">
+      <c r="U90" s="66">
         <f>133.266-1.476</f>
         <v>131.79</v>
       </c>
-      <c r="R90" s="66">
+      <c r="V90" s="66">
         <f>0.071+618.191-6.836</f>
         <v>611.42600000000004</v>
       </c>
-      <c r="S90" s="66">
+      <c r="W90" s="66">
         <v>0</v>
       </c>
-      <c r="T90" s="66">
+      <c r="X90" s="66">
         <v>0</v>
       </c>
-      <c r="U90" s="66">
+      <c r="Y90" s="66">
         <v>0.2</v>
       </c>
-      <c r="V90" s="66">
+      <c r="Z90" s="66">
         <v>4.3</v>
       </c>
-      <c r="W90" s="66"/>
-      <c r="X90" s="66"/>
-      <c r="Y90" s="66"/>
-      <c r="Z90" s="66"/>
       <c r="AA90" s="66"/>
       <c r="AB90" s="66"/>
       <c r="AC90" s="66"/>
@@ -8458,8 +8918,12 @@
       <c r="AM90" s="66"/>
       <c r="AN90" s="66"/>
       <c r="AO90" s="66"/>
-    </row>
-    <row r="91" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP90" s="66"/>
+      <c r="AQ90" s="66"/>
+      <c r="AR90" s="66"/>
+      <c r="AS90" s="66"/>
+    </row>
+    <row r="91" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B91" s="65" t="s">
         <v>118</v>
       </c>
@@ -8476,32 +8940,32 @@
       <c r="M91" s="66"/>
       <c r="N91" s="66"/>
       <c r="O91" s="66"/>
-      <c r="P91" s="66">
+      <c r="P91" s="66"/>
+      <c r="Q91" s="66"/>
+      <c r="R91" s="66"/>
+      <c r="S91" s="66"/>
+      <c r="T91" s="66">
         <v>-0.49099999999999999</v>
       </c>
-      <c r="Q91" s="66">
+      <c r="U91" s="66">
         <v>-0.59499999999999997</v>
       </c>
-      <c r="R91" s="66">
+      <c r="V91" s="66">
         <f>0.5-2.764</f>
         <v>-2.2639999999999998</v>
       </c>
-      <c r="S91" s="66">
+      <c r="W91" s="66">
         <v>26.4</v>
       </c>
-      <c r="T91" s="66">
+      <c r="X91" s="66">
         <v>10.1</v>
       </c>
-      <c r="U91" s="66">
+      <c r="Y91" s="66">
         <v>10.9</v>
       </c>
-      <c r="V91" s="66">
+      <c r="Z91" s="66">
         <v>8.6</v>
       </c>
-      <c r="W91" s="66"/>
-      <c r="X91" s="66"/>
-      <c r="Y91" s="66"/>
-      <c r="Z91" s="66"/>
       <c r="AA91" s="66"/>
       <c r="AB91" s="66"/>
       <c r="AC91" s="66"/>
@@ -8517,8 +8981,12 @@
       <c r="AM91" s="66"/>
       <c r="AN91" s="66"/>
       <c r="AO91" s="66"/>
-    </row>
-    <row r="92" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP91" s="66"/>
+      <c r="AQ91" s="66"/>
+      <c r="AR91" s="66"/>
+      <c r="AS91" s="66"/>
+    </row>
+    <row r="92" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B92" s="65" t="s">
         <v>119</v>
       </c>
@@ -8535,31 +9003,31 @@
       <c r="M92" s="66"/>
       <c r="N92" s="66"/>
       <c r="O92" s="66"/>
-      <c r="P92" s="66">
+      <c r="P92" s="66"/>
+      <c r="Q92" s="66"/>
+      <c r="R92" s="66"/>
+      <c r="S92" s="66"/>
+      <c r="T92" s="66">
         <v>0</v>
       </c>
-      <c r="Q92" s="66">
+      <c r="U92" s="66">
         <v>0</v>
       </c>
-      <c r="R92" s="66">
+      <c r="V92" s="66">
         <v>0</v>
       </c>
-      <c r="S92" s="66">
+      <c r="W92" s="66">
         <v>-4.7</v>
       </c>
-      <c r="T92" s="66">
+      <c r="X92" s="66">
         <v>-6.5</v>
       </c>
-      <c r="U92" s="66">
+      <c r="Y92" s="66">
         <v>-15.3</v>
       </c>
-      <c r="V92" s="66">
+      <c r="Z92" s="66">
         <v>-21.5</v>
       </c>
-      <c r="W92" s="66"/>
-      <c r="X92" s="66"/>
-      <c r="Y92" s="66"/>
-      <c r="Z92" s="66"/>
       <c r="AA92" s="66"/>
       <c r="AB92" s="66"/>
       <c r="AC92" s="66"/>
@@ -8575,8 +9043,12 @@
       <c r="AM92" s="66"/>
       <c r="AN92" s="66"/>
       <c r="AO92" s="66"/>
-    </row>
-    <row r="93" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP92" s="66"/>
+      <c r="AQ92" s="66"/>
+      <c r="AR92" s="66"/>
+      <c r="AS92" s="66"/>
+    </row>
+    <row r="93" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B93" s="64" t="s">
         <v>120</v>
       </c>
@@ -8593,38 +9065,38 @@
       <c r="M93" s="66"/>
       <c r="N93" s="66"/>
       <c r="O93" s="66"/>
-      <c r="P93" s="81">
-        <f t="shared" ref="P93" si="57">+SUM(P89:P92)</f>
+      <c r="P93" s="66"/>
+      <c r="Q93" s="66"/>
+      <c r="R93" s="66"/>
+      <c r="S93" s="66"/>
+      <c r="T93" s="81">
+        <f t="shared" ref="T93" si="63">+SUM(T89:T92)</f>
         <v>-0.69099999999999995</v>
-      </c>
-      <c r="Q93" s="81">
-        <f>+SUM(Q89:Q92)</f>
-        <v>124.79599999999999</v>
-      </c>
-      <c r="R93" s="81">
-        <f>+SUM(R89:R92)</f>
-        <v>595.851</v>
-      </c>
-      <c r="S93" s="81">
-        <f t="shared" ref="S93:T93" si="58">+SUM(S89:S92)</f>
-        <v>6.299999999999998</v>
-      </c>
-      <c r="T93" s="81">
-        <f t="shared" si="58"/>
-        <v>-21.9</v>
       </c>
       <c r="U93" s="81">
         <f>+SUM(U89:U92)</f>
-        <v>-55.5</v>
+        <v>124.79599999999999</v>
       </c>
       <c r="V93" s="81">
         <f>+SUM(V89:V92)</f>
+        <v>595.851</v>
+      </c>
+      <c r="W93" s="81">
+        <f t="shared" ref="W93:X93" si="64">+SUM(W89:W92)</f>
+        <v>6.299999999999998</v>
+      </c>
+      <c r="X93" s="81">
+        <f t="shared" si="64"/>
+        <v>-21.9</v>
+      </c>
+      <c r="Y93" s="81">
+        <f>+SUM(Y89:Y92)</f>
+        <v>-55.5</v>
+      </c>
+      <c r="Z93" s="81">
+        <f>+SUM(Z89:Z92)</f>
         <v>-78.5</v>
       </c>
-      <c r="W93" s="66"/>
-      <c r="X93" s="66"/>
-      <c r="Y93" s="66"/>
-      <c r="Z93" s="66"/>
       <c r="AA93" s="66"/>
       <c r="AB93" s="66"/>
       <c r="AC93" s="66"/>
@@ -8640,8 +9112,12 @@
       <c r="AM93" s="66"/>
       <c r="AN93" s="66"/>
       <c r="AO93" s="66"/>
-    </row>
-    <row r="94" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP93" s="66"/>
+      <c r="AQ93" s="66"/>
+      <c r="AR93" s="66"/>
+      <c r="AS93" s="66"/>
+    </row>
+    <row r="94" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B94" s="65" t="s">
         <v>114</v>
       </c>
@@ -8658,31 +9134,31 @@
       <c r="M94" s="66"/>
       <c r="N94" s="66"/>
       <c r="O94" s="66"/>
-      <c r="P94" s="66">
+      <c r="P94" s="66"/>
+      <c r="Q94" s="66"/>
+      <c r="R94" s="66"/>
+      <c r="S94" s="66"/>
+      <c r="T94" s="66">
         <v>-0.19500000000000001</v>
       </c>
-      <c r="Q94" s="66">
+      <c r="U94" s="66">
         <v>-0.96899999999999997</v>
       </c>
-      <c r="R94" s="66">
+      <c r="V94" s="66">
         <v>-13.868</v>
       </c>
-      <c r="S94" s="66">
+      <c r="W94" s="66">
         <v>21.5</v>
       </c>
-      <c r="T94" s="66">
+      <c r="X94" s="66">
         <v>-39.6</v>
       </c>
-      <c r="U94" s="66">
+      <c r="Y94" s="66">
         <v>39.4</v>
       </c>
-      <c r="V94" s="66">
+      <c r="Z94" s="66">
         <v>-106.7</v>
       </c>
-      <c r="W94" s="66"/>
-      <c r="X94" s="66"/>
-      <c r="Y94" s="66"/>
-      <c r="Z94" s="66"/>
       <c r="AA94" s="66"/>
       <c r="AB94" s="66"/>
       <c r="AC94" s="66"/>
@@ -8698,8 +9174,12 @@
       <c r="AM94" s="66"/>
       <c r="AN94" s="66"/>
       <c r="AO94" s="66"/>
-    </row>
-    <row r="95" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP94" s="66"/>
+      <c r="AQ94" s="66"/>
+      <c r="AR94" s="66"/>
+      <c r="AS94" s="66"/>
+    </row>
+    <row r="95" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B95" s="64" t="s">
         <v>115</v>
       </c>
@@ -8716,38 +9196,38 @@
       <c r="M95" s="66"/>
       <c r="N95" s="66"/>
       <c r="O95" s="66"/>
-      <c r="P95" s="81">
-        <f t="shared" ref="P95" si="59">+SUM(P94,P93,P88,P84)</f>
+      <c r="P95" s="66"/>
+      <c r="Q95" s="66"/>
+      <c r="R95" s="66"/>
+      <c r="S95" s="66"/>
+      <c r="T95" s="81">
+        <f t="shared" ref="T95" si="65">+SUM(T94,T93,T88,T84)</f>
         <v>-15.641000000000002</v>
       </c>
-      <c r="Q95" s="81">
-        <f t="shared" ref="Q95" si="60">+SUM(Q94,Q93,Q88,Q84)</f>
+      <c r="U95" s="81">
+        <f t="shared" ref="U95" si="66">+SUM(U94,U93,U88,U84)</f>
         <v>90.474999999999994</v>
       </c>
-      <c r="R95" s="81">
-        <f t="shared" ref="R95:T95" si="61">+SUM(R94,R93,R88,R84)</f>
+      <c r="V95" s="81">
+        <f t="shared" ref="V95:X95" si="67">+SUM(V94,V93,V88,V84)</f>
         <v>562.49</v>
       </c>
-      <c r="S95" s="81">
-        <f t="shared" si="61"/>
+      <c r="W95" s="81">
+        <f t="shared" si="67"/>
         <v>-282.20000000000005</v>
       </c>
-      <c r="T95" s="81">
-        <f t="shared" si="61"/>
+      <c r="X95" s="81">
+        <f t="shared" si="67"/>
         <v>123.50000000000003</v>
       </c>
-      <c r="U95" s="81">
-        <f>+SUM(U94,U93,U88,U84)</f>
+      <c r="Y95" s="81">
+        <f>+SUM(Y94,Y93,Y88,Y84)</f>
         <v>429.70000000000005</v>
       </c>
-      <c r="V95" s="81">
-        <f>+SUM(V94,V93,V88,V84)</f>
+      <c r="Z95" s="81">
+        <f>+SUM(Z94,Z93,Z88,Z84)</f>
         <v>95.799999999999898</v>
       </c>
-      <c r="W95" s="66"/>
-      <c r="X95" s="66"/>
-      <c r="Y95" s="66"/>
-      <c r="Z95" s="66"/>
       <c r="AA95" s="66"/>
       <c r="AB95" s="66"/>
       <c r="AC95" s="66"/>
@@ -8763,8 +9243,12 @@
       <c r="AM95" s="66"/>
       <c r="AN95" s="66"/>
       <c r="AO95" s="66"/>
-    </row>
-    <row r="96" spans="2:41" x14ac:dyDescent="0.2">
+      <c r="AP95" s="66"/>
+      <c r="AQ95" s="66"/>
+      <c r="AR95" s="66"/>
+      <c r="AS95" s="66"/>
+    </row>
+    <row r="96" spans="2:45" x14ac:dyDescent="0.2">
       <c r="B96" s="65" t="s">
         <v>121</v>
       </c>
@@ -8781,60 +9265,64 @@
       <c r="M96" s="66"/>
       <c r="N96" s="66"/>
       <c r="O96" s="66"/>
-      <c r="P96" s="66">
-        <f>+P97-P95</f>
+      <c r="P96" s="66"/>
+      <c r="Q96" s="66"/>
+      <c r="R96" s="66"/>
+      <c r="S96" s="66"/>
+      <c r="T96" s="66">
+        <f>+T97-T95</f>
         <v>15.776000000000021</v>
       </c>
-      <c r="Q96" s="66">
-        <f>+Q97-Q95</f>
+      <c r="U96" s="66">
+        <f>+U97-U95</f>
         <v>0.13500000000001933</v>
       </c>
-      <c r="R96" s="88">
-        <f>+R97-R95</f>
+      <c r="V96" s="88">
+        <f>+V97-V95</f>
         <v>90.610000000000014</v>
       </c>
-      <c r="S96" s="88">
+      <c r="W96" s="88">
         <v>653.1</v>
       </c>
-      <c r="T96" s="88">
+      <c r="X96" s="88">
         <v>371</v>
       </c>
-      <c r="U96" s="66">
+      <c r="Y96" s="66">
         <v>494.6</v>
       </c>
-      <c r="V96" s="65">
+      <c r="Z96" s="65">
         <v>924.3</v>
       </c>
     </row>
-    <row r="97" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B97" s="65" t="s">
         <v>122</v>
       </c>
-      <c r="P97" s="66">
-        <f>+Q96</f>
-        <v>0.13500000000001933</v>
-      </c>
-      <c r="Q97" s="88">
-        <f>+R96</f>
-        <v>90.610000000000014</v>
-      </c>
-      <c r="R97" s="88">
-        <f>+S96</f>
-        <v>653.1</v>
-      </c>
-      <c r="S97" s="88">
-        <f>+T96</f>
-        <v>371</v>
-      </c>
       <c r="T97" s="66">
         <f>+U96</f>
+        <v>0.13500000000001933</v>
+      </c>
+      <c r="U97" s="88">
+        <f>+V96</f>
+        <v>90.610000000000014</v>
+      </c>
+      <c r="V97" s="88">
+        <f>+W96</f>
+        <v>653.1</v>
+      </c>
+      <c r="W97" s="88">
+        <f>+X96</f>
+        <v>371</v>
+      </c>
+      <c r="X97" s="66">
+        <f>+Y96</f>
         <v>494.6</v>
       </c>
-      <c r="U97" s="88">
-        <f>+U95+U96</f>
+      <c r="Y97" s="88">
+        <f>+Y95+Y96</f>
         <v>924.30000000000007</v>
       </c>
-      <c r="V97" s="65">
+      <c r="Z97" s="65">
         <v>1019.9</v>
       </c>
     </row>
@@ -8852,9 +9340,9 @@
   <dimension ref="A1:J60"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" style="95" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" style="95" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="95"/>
+    <col min="1" max="1" width="5.42578125" style="89" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" style="89" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="89"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
@@ -8863,482 +9351,482 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="92" t="s">
         <v>217</v>
       </c>
-      <c r="C2" s="99">
+      <c r="C2" s="93">
         <v>20</v>
       </c>
-      <c r="D2" s="99">
+      <c r="D2" s="93">
         <v>21</v>
       </c>
-      <c r="E2" s="99">
+      <c r="E2" s="93">
         <v>22</v>
       </c>
-      <c r="F2" s="99">
+      <c r="F2" s="93">
         <v>23</v>
       </c>
-      <c r="G2" s="99">
+      <c r="G2" s="93">
         <v>24</v>
       </c>
-      <c r="H2" s="99">
+      <c r="H2" s="93">
         <v>25</v>
       </c>
-      <c r="I2" s="100"/>
+      <c r="I2" s="94"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B3" s="95" t="s">
+      <c r="B3" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="102">
+      <c r="D3" s="96">
         <v>38.68</v>
       </c>
-      <c r="E3" s="102">
+      <c r="E3" s="96">
         <v>17.07</v>
       </c>
-      <c r="F3" s="102">
+      <c r="F3" s="96">
         <v>26.76</v>
       </c>
-      <c r="G3" s="102">
+      <c r="G3" s="96">
         <v>55.37</v>
       </c>
-      <c r="H3" s="103">
+      <c r="H3" s="97">
         <v>41.05</v>
       </c>
-      <c r="I3" s="103"/>
-    </row>
-    <row r="4" spans="1:10" s="104" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="104" t="s">
+      <c r="I3" s="97"/>
+    </row>
+    <row r="4" spans="1:10" s="98" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="101" t="s">
+      <c r="C4" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="102">
+      <c r="D4" s="96">
         <f>+D3*Main!$H$10</f>
         <v>32.878</v>
       </c>
-      <c r="E4" s="102">
+      <c r="E4" s="96">
         <f>+E3*Main!$H$10</f>
         <v>14.509499999999999</v>
       </c>
-      <c r="F4" s="102">
+      <c r="F4" s="96">
         <f>+F3*Main!$H$10</f>
         <v>22.746000000000002</v>
       </c>
-      <c r="G4" s="102">
+      <c r="G4" s="96">
         <f>+G3*Main!$H$10</f>
         <v>47.064499999999995</v>
       </c>
-      <c r="H4" s="102">
+      <c r="H4" s="96">
         <f>+H3*Main!$H$10</f>
         <v>34.892499999999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="95" t="s">
+      <c r="B5" s="89" t="s">
         <v>218</v>
       </c>
-      <c r="C5" s="101" t="s">
+      <c r="C5" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="102">
-        <f>+Model!R24</f>
+      <c r="D5" s="96">
+        <f>+Model!V24</f>
         <v>264.17120799999998</v>
       </c>
-      <c r="E5" s="102">
-        <f>+Model!S24</f>
+      <c r="E5" s="96">
+        <f>+Model!W24</f>
         <v>282.19649500000003</v>
       </c>
-      <c r="F5" s="102">
-        <f>+Model!T24</f>
+      <c r="F5" s="96">
+        <f>+Model!X24</f>
         <v>284.78245600000002</v>
       </c>
-      <c r="G5" s="102">
-        <f>+Model!U24</f>
+      <c r="G5" s="96">
+        <f>+Model!Y24</f>
         <v>289.63972999999999</v>
       </c>
-      <c r="H5" s="102">
-        <f>+Model!V24</f>
+      <c r="H5" s="96">
+        <f>+Model!Z24</f>
         <v>296.87335300000001</v>
       </c>
-      <c r="I5" s="103"/>
+      <c r="I5" s="97"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B6" s="95" t="s">
+      <c r="B6" s="89" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="101" t="s">
+      <c r="C6" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="103">
+      <c r="D6" s="97">
         <f t="shared" ref="D6:F6" si="0">+D4*D5</f>
         <v>8685.4209766240001</v>
       </c>
-      <c r="E6" s="103">
+      <c r="E6" s="97">
         <f t="shared" si="0"/>
         <v>4094.5300442025</v>
       </c>
-      <c r="F6" s="103">
+      <c r="F6" s="97">
         <f t="shared" si="0"/>
         <v>6477.6617441760009</v>
       </c>
-      <c r="G6" s="103">
+      <c r="G6" s="97">
         <f>+G4*G5</f>
         <v>13631.749072584998</v>
       </c>
-      <c r="H6" s="103">
+      <c r="H6" s="97">
         <f>+H4*H5</f>
         <v>10358.653469552501</v>
       </c>
-      <c r="I6" s="103"/>
+      <c r="I6" s="97"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="89" t="s">
         <v>220</v>
       </c>
-      <c r="C7" s="103">
-        <f>+Model!Q53-Model!Q39+Model!Q42</f>
+      <c r="C7" s="97">
+        <f>+Model!U53-Model!U39+Model!U42</f>
         <v>-66.230999999999995</v>
       </c>
-      <c r="D7" s="103">
-        <f>+Model!R53-Model!R39+Model!R42</f>
+      <c r="D7" s="97">
+        <f>+Model!V53-Model!V39+Model!V42</f>
         <v>-602.93000000000006</v>
       </c>
-      <c r="E7" s="103">
-        <f>+Model!S53-Model!S39+Model!S42</f>
+      <c r="E7" s="97">
+        <f>+Model!W53-Model!W39+Model!W42</f>
         <v>-306.8</v>
       </c>
-      <c r="F7" s="103">
-        <f>+Model!T53-Model!T39+Model!T42</f>
+      <c r="F7" s="97">
+        <f>+Model!X53-Model!X39+Model!X42</f>
         <v>-445.6</v>
       </c>
-      <c r="G7" s="103">
-        <f>+Model!U53-Model!U39+Model!U42</f>
+      <c r="G7" s="97">
+        <f>+Model!Y53-Model!Y39+Model!Y42</f>
         <v>-816.6</v>
       </c>
-      <c r="H7" s="103">
-        <f>+Model!V53-Model!V39+Model!V42</f>
+      <c r="H7" s="97">
+        <f>+Model!Z53-Model!Z39+Model!Z42</f>
         <v>-903.99999999999989</v>
       </c>
-      <c r="I7" s="103"/>
+      <c r="I7" s="97"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B8" s="95" t="s">
+      <c r="B8" s="89" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="101" t="s">
+      <c r="C8" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="103">
+      <c r="D8" s="97">
         <f t="shared" ref="D8:F8" si="1">+D6+D7</f>
         <v>8082.4909766239998</v>
       </c>
-      <c r="E8" s="103">
+      <c r="E8" s="97">
         <f t="shared" si="1"/>
         <v>3787.7300442024998</v>
       </c>
-      <c r="F8" s="103">
+      <c r="F8" s="97">
         <f t="shared" si="1"/>
         <v>6032.0617441760005</v>
       </c>
-      <c r="G8" s="103">
+      <c r="G8" s="97">
         <f>+G6+G7</f>
         <v>12815.149072584998</v>
       </c>
-      <c r="H8" s="103">
+      <c r="H8" s="97">
         <f>+H6+H7</f>
         <v>9454.6534695525006</v>
       </c>
-      <c r="I8" s="103"/>
+      <c r="I8" s="97"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="C9" s="103"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="103"/>
+      <c r="C9" s="97"/>
+      <c r="D9" s="97"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="97"/>
+      <c r="H9" s="97"/>
+      <c r="I9" s="97"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="105" t="s">
+      <c r="A10" s="99" t="s">
         <v>138</v>
       </c>
       <c r="B10" s="68" t="s">
         <v>221</v>
       </c>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="103"/>
-      <c r="H10" s="103"/>
-      <c r="I10" s="103"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="97"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="97"/>
+      <c r="H10" s="97"/>
+      <c r="I10" s="97"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B11" s="95" t="s">
+      <c r="B11" s="89" t="s">
         <v>222</v>
       </c>
-      <c r="C11" s="101" t="s">
+      <c r="C11" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="103">
-        <f>+Model!R49+SUM(Model!R40,Model!R41,Model!R43)-Model!R51</f>
+      <c r="D11" s="97">
+        <f>+Model!V49+SUM(Model!V40,Model!V41,Model!V43)-Model!V51</f>
         <v>507.45099999999996</v>
       </c>
-      <c r="E11" s="103">
-        <f>+Model!S49+SUM(Model!S40,Model!S41,Model!S43)-Model!S51</f>
+      <c r="E11" s="97">
+        <f>+Model!W49+SUM(Model!W40,Model!W41,Model!W43)-Model!W51</f>
         <v>867</v>
       </c>
-      <c r="F11" s="103">
-        <f>+Model!T49+SUM(Model!T40,Model!T41,Model!T43)-Model!T51</f>
+      <c r="F11" s="97">
+        <f>+Model!X49+SUM(Model!X40,Model!X41,Model!X43)-Model!X51</f>
         <v>999.1</v>
       </c>
-      <c r="G11" s="103">
-        <f>+Model!U49+SUM(Model!U40,Model!U41,Model!U43)-Model!U51</f>
+      <c r="G11" s="97">
+        <f>+Model!Y49+SUM(Model!Y40,Model!Y41,Model!Y43)-Model!Y51</f>
         <v>1229.4000000000001</v>
       </c>
-      <c r="H11" s="103">
-        <f>+Model!V49+SUM(Model!V40,Model!V41,Model!V43)-Model!V51</f>
+      <c r="H11" s="97">
+        <f>+Model!Z49+SUM(Model!Z40,Model!Z41,Model!Z43)-Model!Z51</f>
         <v>1601.6000000000001</v>
       </c>
-      <c r="J11" s="106" t="s">
+      <c r="J11" s="100" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B12" s="95" t="s">
+      <c r="B12" s="89" t="s">
         <v>224</v>
       </c>
-      <c r="C12" s="101" t="s">
+      <c r="C12" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="103">
-        <f>+Model!R45+SUM(Model!R40:R41,Model!R43)-SUM(Model!R51:R54)+Model!R42+Model!R47</f>
+      <c r="D12" s="97">
+        <f>+Model!V45+SUM(Model!V40:V41,Model!V43)-SUM(Model!V51:V54)+Model!V42+Model!V47</f>
         <v>215.67400000000001</v>
       </c>
-      <c r="E12" s="103">
-        <f>+Model!S45+SUM(Model!S40:S41,Model!S43)-SUM(Model!S51:S54)+Model!S42+Model!S47</f>
+      <c r="E12" s="97">
+        <f>+Model!W45+SUM(Model!W40:W41,Model!W43)-SUM(Model!W51:W54)+Model!W42+Model!W47</f>
         <v>604.20000000000005</v>
       </c>
-      <c r="F12" s="103">
-        <f>+Model!T45+SUM(Model!T40:T41,Model!T43)-SUM(Model!T51:T54)+Model!T42+Model!T47</f>
+      <c r="F12" s="97">
+        <f>+Model!X45+SUM(Model!X40:X41,Model!X43)-SUM(Model!X51:X54)+Model!X42+Model!X47</f>
         <v>539.9</v>
       </c>
-      <c r="G12" s="103">
-        <f>+Model!U45+SUM(Model!U40:U41,Model!U43)-SUM(Model!U51:U54)+Model!U42+Model!U47</f>
+      <c r="G12" s="97">
+        <f>+Model!Y45+SUM(Model!Y40:Y41,Model!Y43)-SUM(Model!Y51:Y54)+Model!Y42+Model!Y47</f>
         <v>444.7</v>
       </c>
-      <c r="H12" s="103">
-        <f>+Model!V45+SUM(Model!V40:V41,Model!V43)-SUM(Model!V51:V54)+Model!V42+Model!V47</f>
+      <c r="H12" s="97">
+        <f>+Model!Z45+SUM(Model!Z40:Z41,Model!Z43)-SUM(Model!Z51:Z54)+Model!Z42+Model!Z47</f>
         <v>497.50000000000011</v>
       </c>
-      <c r="J12" s="106" t="s">
+      <c r="J12" s="100" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B13" s="95" t="s">
+      <c r="B13" s="89" t="s">
         <v>226</v>
       </c>
-      <c r="C13" s="101" t="s">
+      <c r="C13" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="103">
-        <f>+D12-Model!R47</f>
+      <c r="D13" s="97">
+        <f>+D12-Model!V47</f>
         <v>158.21</v>
       </c>
-      <c r="E13" s="103">
-        <f>+E12-Model!S47</f>
+      <c r="E13" s="97">
+        <f>+E12-Model!W47</f>
         <v>533.90000000000009</v>
       </c>
-      <c r="F13" s="103">
-        <f>+F12-Model!T47</f>
+      <c r="F13" s="97">
+        <f>+F12-Model!X47</f>
         <v>475.29999999999995</v>
       </c>
-      <c r="G13" s="103">
-        <f>+G12-Model!U47</f>
+      <c r="G13" s="97">
+        <f>+G12-Model!Y47</f>
         <v>386.4</v>
       </c>
-      <c r="H13" s="103">
-        <f>+H12-Model!V47</f>
+      <c r="H13" s="97">
+        <f>+H12-Model!Z47</f>
         <v>443.30000000000013</v>
       </c>
-      <c r="J13" s="106"/>
+      <c r="J13" s="100"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B14" s="95" t="s">
+      <c r="B14" s="89" t="s">
         <v>227</v>
       </c>
-      <c r="C14" s="101" t="s">
+      <c r="C14" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="103">
-        <f>+D12+Model!R39+Model!R46</f>
+      <c r="D14" s="97">
+        <f>+D12+Model!V39+Model!V46</f>
         <v>1046.645</v>
       </c>
-      <c r="E14" s="103">
-        <f>+E12+Model!S39+Model!S46</f>
+      <c r="E14" s="97">
+        <f>+E12+Model!W39+Model!W46</f>
         <v>1126.8</v>
       </c>
-      <c r="F14" s="103">
-        <f>+F12+Model!T39+Model!T46</f>
+      <c r="F14" s="97">
+        <f>+F12+Model!X39+Model!X46</f>
         <v>1248.5</v>
       </c>
-      <c r="G14" s="103">
-        <f>+G12+Model!U39+Model!U46</f>
+      <c r="G14" s="97">
+        <f>+G12+Model!Y39+Model!Y46</f>
         <v>1692.6</v>
       </c>
-      <c r="H14" s="103">
-        <f>+H12+Model!V39+Model!V46</f>
+      <c r="H14" s="97">
+        <f>+H12+Model!Z39+Model!Z46</f>
         <v>2011.5</v>
       </c>
-      <c r="J14" s="106" t="s">
+      <c r="J14" s="100" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B15" s="95" t="s">
+      <c r="B15" s="89" t="s">
         <v>229</v>
       </c>
-      <c r="C15" s="101" t="s">
+      <c r="C15" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="103">
-        <f>+Model!R15*(1-Model!R37)</f>
+      <c r="D15" s="97">
+        <f>+Model!V15*(1-Model!V37)</f>
         <v>-150.47130325814533</v>
       </c>
-      <c r="E15" s="103">
-        <f>+Model!S15*(1-Model!S37)</f>
+      <c r="E15" s="97">
+        <f>+Model!W15*(1-Model!W37)</f>
         <v>63.032991014120576</v>
       </c>
-      <c r="F15" s="103">
-        <f>+Model!T15*(1-Model!T37)</f>
+      <c r="F15" s="97">
+        <f>+Model!X15*(1-Model!X37)</f>
         <v>207.69725036179449</v>
       </c>
-      <c r="G15" s="103">
-        <f>+Model!U15*(1-Model!U37)</f>
+      <c r="G15" s="97">
+        <f>+Model!Y15*(1-Model!Y37)</f>
         <v>183.20922746781139</v>
       </c>
-      <c r="H15" s="103">
-        <f>+Model!V15*(1-Model!V37)</f>
+      <c r="H15" s="97">
+        <f>+Model!Z15*(1-Model!Z37)</f>
         <v>374.3434210526317</v>
       </c>
-      <c r="J15" s="95" t="s">
+      <c r="J15" s="89" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B16" s="95" t="s">
+      <c r="B16" s="89" t="s">
         <v>231</v>
       </c>
-      <c r="C16" s="101" t="s">
+      <c r="C16" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="101" t="s">
+      <c r="D16" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="103">
+      <c r="E16" s="97">
         <f t="shared" ref="E16" si="2">+E14-D14</f>
         <v>80.154999999999973</v>
       </c>
-      <c r="F16" s="103">
+      <c r="F16" s="97">
         <f>+F14-E14</f>
         <v>121.70000000000005</v>
       </c>
-      <c r="G16" s="103">
+      <c r="G16" s="97">
         <f>+G14-F14</f>
         <v>444.09999999999991</v>
       </c>
-      <c r="H16" s="103">
+      <c r="H16" s="97">
         <f>+H14-G14</f>
         <v>318.90000000000009</v>
       </c>
-      <c r="J16" s="106" t="s">
+      <c r="J16" s="100" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B17" s="95" t="s">
+      <c r="B17" s="89" t="s">
         <v>233</v>
       </c>
-      <c r="C17" s="101" t="s">
+      <c r="C17" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="101" t="s">
+      <c r="D17" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="103">
-        <f>+E15-E16+SUM(Model!S69:S71)</f>
+      <c r="E17" s="97">
+        <f>+E15-E16+SUM(Model!W69:W71)</f>
         <v>72.377991014120596</v>
       </c>
-      <c r="F17" s="103">
-        <f>+F15-F16+SUM(Model!T69:T71)</f>
+      <c r="F17" s="97">
+        <f>+F15-F16+SUM(Model!X69:X71)</f>
         <v>170.69725036179443</v>
       </c>
-      <c r="G17" s="103">
-        <f>+G15-G16+SUM(Model!U69:U71)</f>
+      <c r="G17" s="97">
+        <f>+G15-G16+SUM(Model!Y69:Y71)</f>
         <v>-93.59077253218851</v>
       </c>
-      <c r="H17" s="103">
-        <f>+H15-H16+SUM(Model!V69:V71)</f>
+      <c r="H17" s="97">
+        <f>+H15-H16+SUM(Model!Z69:Z71)</f>
         <v>253.44342105263161</v>
       </c>
-      <c r="J17" s="106" t="s">
+      <c r="J17" s="100" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B18" s="95" t="s">
+      <c r="B18" s="89" t="s">
         <v>235</v>
       </c>
-      <c r="C18" s="101" t="s">
+      <c r="C18" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="101" t="s">
+      <c r="D18" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="107">
+      <c r="E18" s="101">
         <f t="shared" ref="E18:F18" si="3">+E16/E15</f>
         <v>1.2716356738020531</v>
       </c>
-      <c r="F18" s="107">
+      <c r="F18" s="101">
         <f t="shared" si="3"/>
         <v>0.58594901852579617</v>
       </c>
-      <c r="G18" s="107">
+      <c r="G18" s="101">
         <f>+G16/G15</f>
         <v>2.4240045446293106</v>
       </c>
-      <c r="H18" s="107">
+      <c r="H18" s="101">
         <f>+H16/H15</f>
         <v>0.85189155749891909</v>
       </c>
-      <c r="J18" s="106" t="s">
+      <c r="J18" s="100" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B19" s="95" t="s">
+      <c r="B19" s="89" t="s">
         <v>237</v>
       </c>
-      <c r="C19" s="101" t="s">
+      <c r="C19" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="103"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="103"/>
-      <c r="G19" s="103"/>
-      <c r="J19" s="106" t="s">
+      <c r="D19" s="97"/>
+      <c r="E19" s="97"/>
+      <c r="F19" s="97"/>
+      <c r="G19" s="97"/>
+      <c r="J19" s="100" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" s="105" t="s">
+      <c r="A21" s="99" t="s">
         <v>138</v>
       </c>
       <c r="B21" s="68" t="s">
@@ -9346,297 +9834,297 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B22" s="95" t="s">
+      <c r="B22" s="89" t="s">
         <v>240</v>
       </c>
-      <c r="C22" s="101" t="s">
+      <c r="C22" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="108">
-        <f>+Model!R11/Model!R65</f>
+      <c r="D22" s="102">
+        <f>+Model!V11/Model!V65</f>
         <v>0.86428691558352488</v>
       </c>
-      <c r="E22" s="108">
-        <f>+Model!S11/Model!S65</f>
+      <c r="E22" s="102">
+        <f>+Model!W11/Model!W65</f>
         <v>1.2605466735430633</v>
       </c>
-      <c r="F22" s="108">
-        <f>+Model!T11/Model!T65</f>
+      <c r="F22" s="102">
+        <f>+Model!X11/Model!X65</f>
         <v>1.6678455095393205</v>
       </c>
-      <c r="G22" s="108">
-        <f>+Model!U11/Model!U65</f>
+      <c r="G22" s="102">
+        <f>+Model!Y11/Model!Y65</f>
         <v>1.6656847248167843</v>
       </c>
-      <c r="H22" s="108">
-        <f>+Model!V11/Model!V65</f>
+      <c r="H22" s="102">
+        <f>+Model!Z11/Model!Z65</f>
         <v>1.8463611859838274</v>
       </c>
-      <c r="J22" s="106" t="s">
+      <c r="J22" s="100" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B23" s="95" t="s">
+      <c r="B23" s="89" t="s">
         <v>242</v>
       </c>
-      <c r="C23" s="101" t="s">
+      <c r="C23" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="109">
-        <f>+Model!R21/Model!R65</f>
+      <c r="D23" s="103">
+        <f>+Model!V21/Model!V65</f>
         <v>-0.20301081014672356</v>
       </c>
-      <c r="E23" s="109">
-        <f>+Model!S21/Model!S65</f>
+      <c r="E23" s="103">
+        <f>+Model!W21/Model!W65</f>
         <v>5.951521402784931E-2</v>
       </c>
-      <c r="F23" s="109">
-        <f>+Model!T21/Model!T65</f>
+      <c r="F23" s="103">
+        <f>+Model!X21/Model!X65</f>
         <v>7.4080967892042757E-2</v>
       </c>
-      <c r="G23" s="109">
-        <f>+Model!U21/Model!U65</f>
+      <c r="G23" s="103">
+        <f>+Model!Y21/Model!Y65</f>
         <v>0.17401925564017837</v>
       </c>
-      <c r="H23" s="109">
-        <f>+Model!V21/Model!V65</f>
+      <c r="H23" s="103">
+        <f>+Model!Z21/Model!Z65</f>
         <v>0.12478559176672389</v>
       </c>
-      <c r="J23" s="106" t="s">
+      <c r="J23" s="100" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B24" s="95" t="s">
+      <c r="B24" s="89" t="s">
         <v>244</v>
       </c>
-      <c r="C24" s="101" t="s">
+      <c r="C24" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="109">
-        <f>+Model!R15/KPIs!D11</f>
+      <c r="D24" s="103">
+        <f>+Model!V15/KPIs!D11</f>
         <v>-0.27805640347540939</v>
       </c>
-      <c r="E24" s="109">
-        <f>+Model!S15/KPIs!E11</f>
+      <c r="E24" s="103">
+        <f>+Model!W15/KPIs!E11</f>
         <v>9.8154555940022967E-2</v>
       </c>
-      <c r="F24" s="109">
-        <f>+Model!T15/KPIs!F11</f>
+      <c r="F24" s="103">
+        <f>+Model!X15/KPIs!F11</f>
         <v>0.18046241617455705</v>
       </c>
-      <c r="G24" s="109">
-        <f>+Model!U15/KPIs!G11</f>
+      <c r="G24" s="103">
+        <f>+Model!Y15/KPIs!G11</f>
         <v>0.1720351390922403</v>
       </c>
-      <c r="H24" s="109">
-        <f>+Model!V15/KPIs!H11</f>
+      <c r="H24" s="103">
+        <f>+Model!Z15/KPIs!H11</f>
         <v>0.23545204795204802</v>
       </c>
-      <c r="J24" s="106" t="s">
+      <c r="J24" s="100" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B25" s="95" t="s">
+      <c r="B25" s="89" t="s">
         <v>246</v>
       </c>
-      <c r="C25" s="101" t="s">
+      <c r="C25" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="109">
+      <c r="D25" s="103">
         <f t="shared" ref="D25:F25" si="4">+D15/D12</f>
         <v>-0.69767938304174504</v>
       </c>
-      <c r="E25" s="109">
+      <c r="E25" s="103">
         <f t="shared" si="4"/>
         <v>0.10432471203925947</v>
       </c>
-      <c r="F25" s="109">
+      <c r="F25" s="103">
         <f t="shared" si="4"/>
         <v>0.38469577766585383</v>
       </c>
-      <c r="G25" s="109">
+      <c r="G25" s="103">
         <f>+G15/G12</f>
         <v>0.41198387107670653</v>
       </c>
-      <c r="H25" s="109">
+      <c r="H25" s="103">
         <f>+H15/H12</f>
         <v>0.75244908754297812</v>
       </c>
-      <c r="J25" s="106" t="s">
+      <c r="J25" s="100" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B26" s="95" t="s">
+      <c r="B26" s="89" t="s">
         <v>248</v>
       </c>
-      <c r="C26" s="101" t="s">
+      <c r="C26" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="109">
+      <c r="D26" s="103">
         <f t="shared" ref="D26:F26" si="5">+D15/D13</f>
         <v>-0.95108591908315099</v>
       </c>
-      <c r="E26" s="109">
+      <c r="E26" s="103">
         <f t="shared" si="5"/>
         <v>0.11806141789496266</v>
       </c>
-      <c r="F26" s="109">
+      <c r="F26" s="103">
         <f t="shared" si="5"/>
         <v>0.43698138094213024</v>
       </c>
-      <c r="G26" s="109">
+      <c r="G26" s="103">
         <f>+G15/G13</f>
         <v>0.47414396342601295</v>
       </c>
-      <c r="H26" s="109">
+      <c r="H26" s="103">
         <f>+H15/H13</f>
         <v>0.84444714877652061</v>
       </c>
-      <c r="J26" s="106" t="s">
+      <c r="J26" s="100" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B27" s="95" t="s">
+      <c r="B27" s="89" t="s">
         <v>250</v>
       </c>
-      <c r="C27" s="101" t="s">
+      <c r="C27" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="J27" s="106" t="s">
+      <c r="J27" s="100" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B29" s="95" t="s">
+      <c r="B29" s="89" t="s">
         <v>252</v>
       </c>
-      <c r="C29" s="101" t="s">
+      <c r="C29" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="110">
-        <f>1-(0/Model!R21)%</f>
-        <v>1</v>
-      </c>
-      <c r="E29" s="110">
-        <f>1-(0/Model!S21)%</f>
-        <v>1</v>
-      </c>
-      <c r="F29" s="110">
-        <f>1-(0/Model!T21)%</f>
-        <v>1</v>
-      </c>
-      <c r="G29" s="110">
-        <f>1-(0/Model!U21)%</f>
-        <v>1</v>
-      </c>
-      <c r="H29" s="110">
+      <c r="D29" s="104">
         <f>1-(0/Model!V21)%</f>
         <v>1</v>
       </c>
-      <c r="J29" s="106" t="s">
+      <c r="E29" s="104">
+        <f>1-(0/Model!W21)%</f>
+        <v>1</v>
+      </c>
+      <c r="F29" s="104">
+        <f>1-(0/Model!X21)%</f>
+        <v>1</v>
+      </c>
+      <c r="G29" s="104">
+        <f>1-(0/Model!Y21)%</f>
+        <v>1</v>
+      </c>
+      <c r="H29" s="104">
+        <f>1-(0/Model!Z21)%</f>
+        <v>1</v>
+      </c>
+      <c r="J29" s="100" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B30" s="95" t="s">
+      <c r="B30" s="89" t="s">
         <v>254</v>
       </c>
-      <c r="C30" s="101" t="s">
+      <c r="C30" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D30" s="110">
-        <f>-(Model!R85+Model!R79)/KPIs!D15</f>
+      <c r="D30" s="104">
+        <f>-(Model!V85+Model!V79)/KPIs!D15</f>
         <v>-0.65843784066937572</v>
       </c>
-      <c r="E30" s="110">
-        <f>-(Model!S85+Model!S79)/KPIs!E15</f>
+      <c r="E30" s="104">
+        <f>-(Model!W85+Model!W79)/KPIs!E15</f>
         <v>5.4907754563394766</v>
       </c>
-      <c r="F30" s="110">
-        <f>-(Model!T85+Model!T79)/KPIs!F15</f>
+      <c r="F30" s="104">
+        <f>-(Model!X85+Model!X79)/KPIs!F15</f>
         <v>0.69331683375279063</v>
       </c>
-      <c r="G30" s="110">
-        <f>-(Model!U85+Model!U79)/KPIs!G15</f>
+      <c r="G30" s="104">
+        <f>-(Model!Y85+Model!Y79)/KPIs!G15</f>
         <v>7.8598661208426235E-2</v>
       </c>
-      <c r="H30" s="110">
-        <f>-(Model!V85+Model!V79)/KPIs!H15</f>
+      <c r="H30" s="104">
+        <f>-(Model!Z85+Model!Z79)/KPIs!H15</f>
         <v>0.69615221036129915</v>
       </c>
-      <c r="J30" s="106" t="s">
+      <c r="J30" s="100" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B31" s="95" t="s">
+      <c r="B31" s="89" t="s">
         <v>256</v>
       </c>
-      <c r="C31" s="101" t="s">
+      <c r="C31" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="109">
+      <c r="D31" s="103">
         <f t="shared" ref="D31:F31" si="6">+D29*D23</f>
         <v>-0.20301081014672356</v>
       </c>
-      <c r="E31" s="109">
+      <c r="E31" s="103">
         <f t="shared" si="6"/>
         <v>5.951521402784931E-2</v>
       </c>
-      <c r="F31" s="109">
+      <c r="F31" s="103">
         <f t="shared" si="6"/>
         <v>7.4080967892042757E-2</v>
       </c>
-      <c r="G31" s="109">
+      <c r="G31" s="103">
         <f>+G29*G23</f>
         <v>0.17401925564017837</v>
       </c>
-      <c r="H31" s="109">
+      <c r="H31" s="103">
         <f>+H29*H23</f>
         <v>0.12478559176672389</v>
       </c>
-      <c r="J31" s="106" t="s">
+      <c r="J31" s="100" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B32" s="95" t="s">
+      <c r="B32" s="89" t="s">
         <v>258</v>
       </c>
-      <c r="C32" s="101" t="s">
+      <c r="C32" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D32" s="109">
+      <c r="D32" s="103">
         <f t="shared" ref="D32:F32" si="7">+D30*D26</f>
         <v>0.62623095885215851</v>
       </c>
-      <c r="E32" s="109">
+      <c r="E32" s="103">
         <f t="shared" si="7"/>
         <v>0.64824873571829922</v>
       </c>
-      <c r="F32" s="109">
+      <c r="F32" s="103">
         <f t="shared" si="7"/>
         <v>0.30296654744371976</v>
       </c>
-      <c r="G32" s="109">
+      <c r="G32" s="103">
         <f>+G30*G26</f>
         <v>3.726708074534163E-2</v>
       </c>
-      <c r="H32" s="109">
+      <c r="H32" s="103">
         <f>+H30*H26</f>
         <v>0.58786374915407169</v>
       </c>
-      <c r="J32" s="106" t="s">
+      <c r="J32" s="100" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A34" s="105" t="s">
+      <c r="A34" s="99" t="s">
         <v>138</v>
       </c>
       <c r="B34" s="68" t="s">
@@ -9644,70 +10132,70 @@
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B35" s="95" t="s">
+      <c r="B35" s="89" t="s">
         <v>261</v>
       </c>
-      <c r="C35" s="101" t="s">
+      <c r="C35" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="J35" s="106" t="s">
+      <c r="J35" s="100" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B36" s="95" t="s">
+      <c r="B36" s="89" t="s">
         <v>263</v>
       </c>
-      <c r="C36" s="101" t="s">
+      <c r="C36" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="J36" s="106" t="s">
+      <c r="J36" s="100" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B37" s="95" t="s">
+      <c r="B37" s="89" t="s">
         <v>265</v>
       </c>
-      <c r="C37" s="101" t="s">
+      <c r="C37" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="J37" s="106" t="s">
+      <c r="J37" s="100" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B38" s="95" t="s">
+      <c r="B38" s="89" t="s">
         <v>267</v>
       </c>
-      <c r="C38" s="101" t="s">
+      <c r="C38" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D38" s="107"/>
-      <c r="E38" s="107"/>
-      <c r="G38" s="110"/>
-      <c r="H38" s="110"/>
-      <c r="J38" s="106" t="s">
+      <c r="D38" s="101"/>
+      <c r="E38" s="101"/>
+      <c r="G38" s="104"/>
+      <c r="H38" s="104"/>
+      <c r="J38" s="100" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B39" s="95" t="s">
+      <c r="B39" s="89" t="s">
         <v>269</v>
       </c>
-      <c r="C39" s="101" t="s">
+      <c r="C39" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D39" s="96"/>
-      <c r="E39" s="96"/>
-      <c r="G39" s="110"/>
-      <c r="H39" s="110"/>
-      <c r="J39" s="106" t="s">
+      <c r="D39" s="90"/>
+      <c r="E39" s="90"/>
+      <c r="G39" s="104"/>
+      <c r="H39" s="104"/>
+      <c r="J39" s="100" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A41" s="105" t="s">
+      <c r="A41" s="99" t="s">
         <v>138</v>
       </c>
       <c r="B41" s="68" t="s">
@@ -9715,193 +10203,193 @@
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B42" s="95" t="s">
+      <c r="B42" s="89" t="s">
         <v>272</v>
       </c>
-      <c r="C42" s="101" t="s">
+      <c r="C42" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D42" s="111">
-        <f>+Model!R40/Model!R11*360</f>
+      <c r="D42" s="105">
+        <f>+Model!V40/Model!V11*360</f>
         <v>49.316919679823343</v>
       </c>
-      <c r="E42" s="111">
-        <f>+Model!S40/Model!S11*360</f>
+      <c r="E42" s="105">
+        <f>+Model!W40/Model!W11*360</f>
         <v>51.432779641600533</v>
       </c>
-      <c r="F42" s="111">
-        <f>+Model!T40/Model!T11*360</f>
+      <c r="F42" s="105">
+        <f>+Model!X40/Model!X11*360</f>
         <v>41.140561352603093</v>
       </c>
-      <c r="G42" s="111">
-        <f>+Model!U40/Model!U11*360</f>
+      <c r="G42" s="105">
+        <f>+Model!Y40/Model!Y11*360</f>
         <v>38.215934089634644</v>
       </c>
-      <c r="H42" s="111">
-        <f>+Model!V40/Model!V11*360</f>
+      <c r="H42" s="105">
+        <f>+Model!Z40/Model!Z11*360</f>
         <v>36.477770404777701</v>
       </c>
-      <c r="J42" s="106" t="s">
+      <c r="J42" s="100" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B43" s="95" t="s">
+      <c r="B43" s="89" t="s">
         <v>274</v>
       </c>
-      <c r="C43" s="101" t="s">
+      <c r="C43" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D43" s="111">
-        <f>+Model!R51/Model!R11*360</f>
+      <c r="D43" s="105">
+        <f>+Model!V51/Model!V11*360</f>
         <v>22.823682031465637</v>
       </c>
-      <c r="E43" s="111">
-        <f>+Model!S51/Model!S11*360</f>
+      <c r="E43" s="105">
+        <f>+Model!W51/Model!W11*360</f>
         <v>32.697815236069061</v>
       </c>
-      <c r="F43" s="111">
-        <f>+Model!T51/Model!T11*360</f>
+      <c r="F43" s="105">
+        <f>+Model!X51/Model!X11*360</f>
         <v>13.077395234640925</v>
       </c>
-      <c r="G43" s="111">
-        <f>+Model!U51/Model!U11*360</f>
+      <c r="G43" s="105">
+        <f>+Model!Y51/Model!Y11*360</f>
         <v>25.855152482422461</v>
       </c>
-      <c r="H43" s="111">
-        <f>+Model!V51/Model!V11*360</f>
+      <c r="H43" s="105">
+        <f>+Model!Z51/Model!Z11*360</f>
         <v>18.48971466489715</v>
       </c>
-      <c r="J43" s="106" t="s">
+      <c r="J43" s="100" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B44" s="95" t="s">
+      <c r="B44" s="89" t="s">
         <v>276</v>
       </c>
-      <c r="C44" s="101" t="s">
+      <c r="C44" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D44" s="109">
-        <f>+Model!R41/Model!R50</f>
+      <c r="D44" s="103">
+        <f>+Model!V41/Model!V50</f>
         <v>0.10851216109662157</v>
       </c>
-      <c r="E44" s="109">
-        <f>+Model!S41/Model!S50</f>
+      <c r="E44" s="103">
+        <f>+Model!W41/Model!W50</f>
         <v>0.28621038923455361</v>
       </c>
-      <c r="F44" s="109">
-        <f>+Model!T41/Model!T50</f>
+      <c r="F44" s="103">
+        <f>+Model!X41/Model!X50</f>
         <v>0.22379158819836784</v>
       </c>
-      <c r="G44" s="109">
-        <f>+Model!U41/Model!U50</f>
+      <c r="G44" s="103">
+        <f>+Model!Y41/Model!Y50</f>
         <v>0.17638643440208701</v>
       </c>
-      <c r="H44" s="109">
-        <f>+Model!V41/Model!V50</f>
+      <c r="H44" s="103">
+        <f>+Model!Z41/Model!Z50</f>
         <v>0.1480514900370305</v>
       </c>
-      <c r="J44" s="106" t="s">
+      <c r="J44" s="100" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B45" s="95" t="s">
+      <c r="B45" s="89" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="101" t="s">
+      <c r="C45" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="111">
-        <f>+Model!R12/Model!R41</f>
+      <c r="D45" s="105">
+        <f>+Model!V12/Model!V41</f>
         <v>2.1933550954701966</v>
       </c>
-      <c r="E45" s="111">
-        <f>+Model!S12/Model!S41</f>
+      <c r="E45" s="105">
+        <f>+Model!W12/Model!W41</f>
         <v>1.3579373104145602</v>
       </c>
-      <c r="F45" s="111">
-        <f>+Model!T12/Model!T41</f>
+      <c r="F45" s="105">
+        <f>+Model!X12/Model!X41</f>
         <v>2.0330995792426365</v>
       </c>
-      <c r="G45" s="111">
-        <f>+Model!U12/Model!U41</f>
+      <c r="G45" s="105">
+        <f>+Model!Y12/Model!Y41</f>
         <v>2.1770038167938934</v>
       </c>
-      <c r="H45" s="111">
-        <f>+Model!V12/Model!V41</f>
+      <c r="H45" s="105">
+        <f>+Model!Z12/Model!Z41</f>
         <v>2.6686517389232964</v>
       </c>
-      <c r="J45" s="106" t="s">
+      <c r="J45" s="100" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B46" s="95" t="s">
+      <c r="B46" s="89" t="s">
         <v>280</v>
       </c>
-      <c r="C46" s="101" t="s">
+      <c r="C46" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D46" s="111">
+      <c r="D46" s="105">
         <f t="shared" ref="D46:F46" si="8">360/D45</f>
         <v>164.1321100917431</v>
       </c>
-      <c r="E46" s="111">
+      <c r="E46" s="105">
         <f t="shared" si="8"/>
         <v>265.10796723752793</v>
       </c>
-      <c r="F46" s="111">
+      <c r="F46" s="105">
         <f t="shared" si="8"/>
         <v>177.06953642384107</v>
       </c>
-      <c r="G46" s="111">
+      <c r="G46" s="105">
         <f>360/G45</f>
         <v>165.36489151873764</v>
       </c>
-      <c r="H46" s="111">
+      <c r="H46" s="105">
         <f>360/H45</f>
         <v>134.8995804695171</v>
       </c>
-      <c r="J46" s="106" t="s">
+      <c r="J46" s="100" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B47" s="95" t="s">
+      <c r="B47" s="89" t="s">
         <v>282</v>
       </c>
-      <c r="C47" s="101" t="s">
+      <c r="C47" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="111">
+      <c r="D47" s="105">
         <f t="shared" ref="D47:F47" si="9">+D42+D46-D43</f>
         <v>190.62534774010081</v>
       </c>
-      <c r="E47" s="111">
+      <c r="E47" s="105">
         <f t="shared" si="9"/>
         <v>283.84293164305939</v>
       </c>
-      <c r="F47" s="111">
+      <c r="F47" s="105">
         <f t="shared" si="9"/>
         <v>205.13270254180324</v>
       </c>
-      <c r="G47" s="111">
+      <c r="G47" s="105">
         <f>+G42+G46-G43</f>
         <v>177.72567312594981</v>
       </c>
-      <c r="H47" s="111">
+      <c r="H47" s="105">
         <f>+H42+H46-H43</f>
         <v>152.88763620939764</v>
       </c>
-      <c r="J47" s="106" t="s">
+      <c r="J47" s="100" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A49" s="105" t="s">
+      <c r="A49" s="99" t="s">
         <v>138</v>
       </c>
       <c r="B49" s="68" t="s">
@@ -9912,161 +10400,161 @@
       <c r="B50" s="68" t="s">
         <v>285</v>
       </c>
-      <c r="C50" s="112"/>
-      <c r="D50" s="112"/>
-      <c r="E50" s="112"/>
+      <c r="C50" s="106"/>
+      <c r="D50" s="106"/>
+      <c r="E50" s="106"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B51" s="95" t="s">
+      <c r="B51" s="89" t="s">
         <v>286</v>
       </c>
-      <c r="C51" s="101" t="s">
+      <c r="C51" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D51" s="111">
-        <f>+D6/Model!R21</f>
+      <c r="D51" s="105">
+        <f>+D6/Model!V21</f>
         <v>-51.030675538331387</v>
       </c>
-      <c r="E51" s="111">
-        <f>+E6/Model!S21</f>
+      <c r="E51" s="105">
+        <f>+E6/Model!W21</f>
         <v>70.962392447183831</v>
       </c>
-      <c r="F51" s="111">
-        <f>+F6/Model!T21</f>
+      <c r="F51" s="105">
+        <f>+F6/Model!X21</f>
         <v>81.377660102713648</v>
       </c>
-      <c r="G51" s="111">
-        <f>+G6/Model!U21</f>
+      <c r="G51" s="105">
+        <f>+G6/Model!Y21</f>
         <v>56.283026724132881</v>
       </c>
-      <c r="H51" s="111">
-        <f>+H6/Model!V21</f>
+      <c r="H51" s="105">
+        <f>+H6/Model!Z21</f>
         <v>50.852496168642588</v>
       </c>
-      <c r="J51" s="106" t="s">
+      <c r="J51" s="100" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B52" s="95" t="s">
+      <c r="B52" s="89" t="s">
         <v>288</v>
       </c>
-      <c r="C52" s="101" t="s">
+      <c r="C52" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="101" t="s">
+      <c r="D52" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="E52" s="111">
-        <f>+E51/((Model!S21/Model!R21-1)*100)</f>
+      <c r="E52" s="105">
+        <f>+E51/((Model!W21/Model!V21-1)*100)</f>
         <v>-0.52996047365119314</v>
       </c>
-      <c r="F52" s="111">
-        <f>+F51/((Model!T21/Model!S21-1)*100)</f>
+      <c r="F52" s="105">
+        <f>+F51/((Model!X21/Model!W21-1)*100)</f>
         <v>2.1440598118386132</v>
       </c>
-      <c r="G52" s="111">
-        <f>+G51/((Model!U21/Model!T21-1)*100)</f>
+      <c r="G52" s="105">
+        <f>+G51/((Model!Y21/Model!X21-1)*100)</f>
         <v>0.27553068433216271</v>
       </c>
-      <c r="H52" s="111">
-        <f>+H51/((Model!V21/Model!U21-1)*100)</f>
+      <c r="H52" s="105">
+        <f>+H51/((Model!Z21/Model!Y21-1)*100)</f>
         <v>-3.1990843044273247</v>
       </c>
-      <c r="J52" s="106" t="s">
+      <c r="J52" s="100" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B53" s="95" t="s">
+      <c r="B53" s="89" t="s">
         <v>290</v>
       </c>
-      <c r="C53" s="101" t="s">
+      <c r="C53" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D53" s="111">
-        <f>+KPIs!D6/Model!R50</f>
+      <c r="D53" s="105">
+        <f>+KPIs!D6/Model!V50</f>
         <v>7.0240561061232079</v>
       </c>
-      <c r="E53" s="111">
-        <f>+KPIs!E6/Model!S50</f>
+      <c r="E53" s="105">
+        <f>+KPIs!E6/Model!W50</f>
         <v>2.9623282044584718</v>
       </c>
-      <c r="F53" s="111">
-        <f>+KPIs!F6/Model!T50</f>
+      <c r="F53" s="105">
+        <f>+KPIs!F6/Model!X50</f>
         <v>4.0663287785160076</v>
       </c>
-      <c r="G53" s="111">
-        <f>+KPIs!G6/Model!U50</f>
+      <c r="G53" s="105">
+        <f>+KPIs!G6/Model!Y50</f>
         <v>5.7358196888769664</v>
       </c>
-      <c r="H53" s="111">
-        <f>+KPIs!H6/Model!V50</f>
+      <c r="H53" s="105">
+        <f>+KPIs!H6/Model!Z50</f>
         <v>3.653201717352319</v>
       </c>
-      <c r="J53" s="106" t="s">
+      <c r="J53" s="100" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B54" s="95" t="s">
+      <c r="B54" s="89" t="s">
         <v>292</v>
       </c>
-      <c r="C54" s="101" t="s">
+      <c r="C54" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D54" s="111">
-        <f>+D6/Model!R84</f>
+      <c r="D54" s="105">
+        <f>+D6/Model!V84</f>
         <v>512.53516916228057</v>
       </c>
-      <c r="E54" s="111">
-        <f>+E6/Model!S84</f>
+      <c r="E54" s="105">
+        <f>+E6/Model!W84</f>
         <v>-18.037577287235678</v>
       </c>
-      <c r="F54" s="111">
-        <f>+F6/Model!T84</f>
+      <c r="F54" s="105">
+        <f>+F6/Model!X84</f>
         <v>27.896906736330752</v>
       </c>
-      <c r="G54" s="111">
-        <f>+G6/Model!U84</f>
+      <c r="G54" s="105">
+        <f>+G6/Model!Y84</f>
         <v>26.6922832829156</v>
       </c>
-      <c r="H54" s="111">
-        <f>+H6/Model!V84</f>
+      <c r="H54" s="105">
+        <f>+H6/Model!Z84</f>
         <v>28.806044131124871</v>
       </c>
-      <c r="J54" s="106" t="s">
+      <c r="J54" s="100" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B55" s="95" t="s">
+      <c r="B55" s="89" t="s">
         <v>294</v>
       </c>
-      <c r="C55" s="101" t="s">
+      <c r="C55" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D55" s="111">
-        <f>+D6/Model!R11</f>
+      <c r="D55" s="105">
+        <f>+D6/Model!V11</f>
         <v>11.98650424596191</v>
       </c>
-      <c r="E55" s="111">
-        <f>+E6/Model!S11</f>
+      <c r="E55" s="105">
+        <f>+E6/Model!W11</f>
         <v>3.3504050766733493</v>
       </c>
-      <c r="F55" s="111">
-        <f>+F6/Model!T11</f>
+      <c r="F55" s="105">
+        <f>+F6/Model!X11</f>
         <v>3.6145648926823286</v>
       </c>
-      <c r="G55" s="111">
-        <f>+G6/Model!U11</f>
+      <c r="G55" s="105">
+        <f>+G6/Model!Y11</f>
         <v>5.8800625771405759</v>
       </c>
-      <c r="H55" s="111">
-        <f>+H6/Model!V11</f>
+      <c r="H55" s="105">
+        <f>+H6/Model!Z11</f>
         <v>3.4368458757639351</v>
       </c>
-      <c r="J55" s="106" t="s">
+      <c r="J55" s="100" t="s">
         <v>295</v>
       </c>
     </row>
@@ -10074,129 +10562,129 @@
       <c r="B56" s="68" t="s">
         <v>296</v>
       </c>
-      <c r="G56" s="111"/>
-      <c r="H56" s="111"/>
+      <c r="G56" s="105"/>
+      <c r="H56" s="105"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B57" s="95" t="s">
+      <c r="B57" s="89" t="s">
         <v>297</v>
       </c>
-      <c r="C57" s="101" t="s">
+      <c r="C57" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D57" s="111">
-        <f>+D8/(Model!R15+Model!R71)</f>
+      <c r="D57" s="105">
+        <f>+D8/(Model!V15+Model!V71)</f>
         <v>-73.686863316746766</v>
       </c>
-      <c r="E57" s="111">
-        <f>+E8/(Model!S15+Model!S71)</f>
+      <c r="E57" s="105">
+        <f>+E8/(Model!W15+Model!W71)</f>
         <v>28.804030754391651</v>
       </c>
-      <c r="F57" s="111">
-        <f>+F8/(Model!T15+Model!T71)</f>
+      <c r="F57" s="105">
+        <f>+F8/(Model!X15+Model!X71)</f>
         <v>24.60057807575857</v>
       </c>
-      <c r="G57" s="111">
-        <f>+G8/(Model!U15+Model!U71)</f>
+      <c r="G57" s="105">
+        <f>+G8/(Model!Y15+Model!Y71)</f>
         <v>40.541439647532385</v>
       </c>
-      <c r="H57" s="111">
-        <f>+H8/(Model!V15+Model!V71)</f>
+      <c r="H57" s="105">
+        <f>+H8/(Model!Z15+Model!Z71)</f>
         <v>18.740641168587707</v>
       </c>
-      <c r="J57" s="106" t="s">
+      <c r="J57" s="100" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B58" s="95" t="s">
+      <c r="B58" s="89" t="s">
         <v>299</v>
       </c>
-      <c r="C58" s="101" t="s">
+      <c r="C58" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D58" s="111">
-        <f>+D8/Model!R15</f>
+      <c r="D58" s="105">
+        <f>+D8/Model!V15</f>
         <v>-57.282005504068053</v>
       </c>
-      <c r="E58" s="111">
-        <f>+E8/Model!S15</f>
+      <c r="E58" s="105">
+        <f>+E8/Model!W15</f>
         <v>44.509166206844931</v>
       </c>
-      <c r="F58" s="111">
-        <f>+F8/Model!T15</f>
+      <c r="F58" s="105">
+        <f>+F8/Model!X15</f>
         <v>33.455694643239056</v>
       </c>
-      <c r="G58" s="111">
-        <f>+G8/Model!U15</f>
+      <c r="G58" s="105">
+        <f>+G8/Model!Y15</f>
         <v>60.591721383380538</v>
       </c>
-      <c r="H58" s="111">
-        <f>+H8/Model!V15</f>
+      <c r="H58" s="105">
+        <f>+H8/Model!Z15</f>
         <v>25.072006018436745</v>
       </c>
-      <c r="J58" s="106" t="s">
+      <c r="J58" s="100" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B59" s="95" t="s">
+      <c r="B59" s="89" t="s">
         <v>301</v>
       </c>
-      <c r="C59" s="101" t="s">
+      <c r="C59" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D59" s="101" t="s">
+      <c r="D59" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="E59" s="113">
+      <c r="E59" s="107">
         <f t="shared" ref="E59:F59" si="10">+E8/E17</f>
         <v>52.332621990896818</v>
       </c>
-      <c r="F59" s="113">
+      <c r="F59" s="107">
         <f t="shared" si="10"/>
         <v>35.337779204943189</v>
       </c>
-      <c r="G59" s="113">
+      <c r="G59" s="107">
         <f>+G8/G17</f>
         <v>-136.92748468528248</v>
       </c>
-      <c r="H59" s="113">
+      <c r="H59" s="107">
         <f>+H8/H17</f>
         <v>37.304789488258564</v>
       </c>
-      <c r="J59" s="106" t="s">
+      <c r="J59" s="100" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B60" s="95" t="s">
+      <c r="B60" s="89" t="s">
         <v>303</v>
       </c>
-      <c r="C60" s="101" t="s">
+      <c r="C60" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="D60" s="111">
-        <f>+D8/Model!R11</f>
+      <c r="D60" s="105">
+        <f>+D8/Model!V11</f>
         <v>11.154417577455147</v>
       </c>
-      <c r="E60" s="111">
-        <f>+E8/Model!S11</f>
+      <c r="E60" s="105">
+        <f>+E8/Model!W11</f>
         <v>3.0993617905265527</v>
       </c>
-      <c r="F60" s="111">
-        <f>+F8/Model!T11</f>
+      <c r="F60" s="105">
+        <f>+F8/Model!X11</f>
         <v>3.3659180537782496</v>
       </c>
-      <c r="G60" s="111">
-        <f>+G8/Model!U11</f>
+      <c r="G60" s="105">
+        <f>+G8/Model!Y11</f>
         <v>5.527821710988654</v>
       </c>
-      <c r="H60" s="111">
-        <f>+H8/Model!V11</f>
+      <c r="H60" s="105">
+        <f>+H8/Model!Z11</f>
         <v>3.1369122327645989</v>
       </c>
-      <c r="J60" s="106" t="s">
+      <c r="J60" s="100" t="s">
         <v>304</v>
       </c>
     </row>
@@ -10546,14 +11034,14 @@
       </c>
       <c r="J3" s="10">
         <f>+Main!H3</f>
-        <v>34.884</v>
+        <v>30.957000000000001</v>
       </c>
       <c r="L3" t="s">
         <v>132</v>
       </c>
       <c r="O3" s="10">
         <f>+J3</f>
-        <v>34.884</v>
+        <v>30.957000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -10562,14 +11050,14 @@
       </c>
       <c r="E4" s="11">
         <f ca="1">+TODAY()</f>
-        <v>46084</v>
+        <v>46156</v>
       </c>
       <c r="G4" t="s">
         <v>134</v>
       </c>
       <c r="J4" s="12">
         <f ca="1">V62</f>
-        <v>104.6096984767934</v>
+        <v>102.80593028423641</v>
       </c>
       <c r="L4" t="s">
         <v>135</v>
@@ -10591,7 +11079,7 @@
       </c>
       <c r="J5" s="15">
         <f ca="1">J4/J3-1</f>
-        <v>1.9987873660358155</v>
+        <v>2.3209267785714509</v>
       </c>
       <c r="L5" t="s">
         <v>137</v>
@@ -10951,23 +11439,23 @@
         <v>62</v>
       </c>
       <c r="H25" s="23">
-        <f>+Model!Q11</f>
+        <f>+Model!U11</f>
         <v>425.29</v>
       </c>
       <c r="I25" s="23">
-        <f>+Model!R11</f>
+        <f>+Model!V11</f>
         <v>724.6</v>
       </c>
       <c r="J25" s="23">
-        <f>+Model!S11</f>
+        <f>+Model!W11</f>
         <v>1222.0999999999999</v>
       </c>
       <c r="K25" s="23">
-        <f>+Model!T11</f>
+        <f>+Model!X11</f>
         <v>1792.1</v>
       </c>
       <c r="L25" s="23">
-        <f>+Model!U11</f>
+        <f>+Model!Y11</f>
         <v>2318.3000000000002</v>
       </c>
       <c r="M25" s="23">
@@ -11171,23 +11659,23 @@
         <v>62</v>
       </c>
       <c r="H31" s="23">
-        <f>+Model!Q15</f>
+        <f>+Model!U15</f>
         <v>-17.09899999999999</v>
       </c>
       <c r="I31" s="23">
-        <f>+Model!R15</f>
+        <f>+Model!V15</f>
         <v>-141.09999999999997</v>
       </c>
       <c r="J31" s="23">
-        <f>+Model!S15</f>
+        <f>+Model!W15</f>
         <v>85.099999999999909</v>
       </c>
       <c r="K31" s="23">
-        <f>+Model!T15</f>
+        <f>+Model!X15</f>
         <v>180.29999999999995</v>
       </c>
       <c r="L31" s="23">
-        <f>+Model!U15</f>
+        <f>+Model!Y15</f>
         <v>211.50000000000023</v>
       </c>
       <c r="M31" s="23">
@@ -11372,23 +11860,23 @@
         <v>62</v>
       </c>
       <c r="H37" s="23">
-        <f>+Model!Q20</f>
+        <f>+Model!U20</f>
         <v>3.0830000000000002</v>
       </c>
       <c r="I37" s="23">
-        <f>+Model!R20</f>
+        <f>+Model!V20</f>
         <v>10.6</v>
       </c>
       <c r="J37" s="23">
-        <f>+Model!S20</f>
+        <f>+Model!W20</f>
         <v>20.2</v>
       </c>
       <c r="K37" s="23">
-        <f>+Model!T20</f>
+        <f>+Model!X20</f>
         <v>-10.5</v>
       </c>
       <c r="L37" s="23">
-        <f>+Model!U20</f>
+        <f>+Model!Y20</f>
         <v>37.4</v>
       </c>
       <c r="M37" s="23">
@@ -11573,23 +12061,23 @@
         <v>62</v>
       </c>
       <c r="H42" s="23">
-        <f>+Model!Q71</f>
+        <f>+Model!U71</f>
         <v>12.090999999999999</v>
       </c>
       <c r="I42" s="23">
-        <f>+Model!R71</f>
+        <f>+Model!V71</f>
         <v>31.413</v>
       </c>
       <c r="J42" s="23">
-        <f>+Model!S71</f>
+        <f>+Model!W71</f>
         <v>46.4</v>
       </c>
       <c r="K42" s="23">
-        <f>+Model!T71</f>
+        <f>+Model!X71</f>
         <v>64.900000000000006</v>
       </c>
       <c r="L42" s="23">
-        <f>+Model!U71</f>
+        <f>+Model!Y71</f>
         <v>104.6</v>
       </c>
       <c r="M42" s="23">
@@ -11703,23 +12191,23 @@
         <v>62</v>
       </c>
       <c r="H45" s="23">
-        <f>+SUM(Model!Q85:Q86)</f>
+        <f>+SUM(Model!U85:U86)</f>
         <v>-10.986000000000001</v>
       </c>
       <c r="I45" s="23">
-        <f>+SUM(Model!R85:R86)</f>
+        <f>+SUM(Model!V85:V86)</f>
         <v>-24.638999999999999</v>
       </c>
       <c r="J45" s="23">
-        <f>+SUM(Model!S85:S86)</f>
+        <f>+SUM(Model!W85:W86)</f>
         <v>-60.3</v>
       </c>
       <c r="K45" s="23">
-        <f>+SUM(Model!T85:T86)</f>
+        <f>+SUM(Model!X85:X86)</f>
         <v>-42.8</v>
       </c>
       <c r="L45" s="23">
-        <f>+SUM(Model!U85:U86)</f>
+        <f>+SUM(Model!Y85:Y86)</f>
         <v>-60.4</v>
       </c>
       <c r="M45" s="23">
@@ -11832,23 +12320,23 @@
         <v>62</v>
       </c>
       <c r="H48" s="23">
-        <f>+Model!Q79</f>
+        <f>+Model!U79</f>
         <v>-49.223000000000006</v>
       </c>
       <c r="I48" s="23">
-        <f>+Model!R79</f>
+        <f>+Model!V79</f>
         <v>-74.437000000000012</v>
       </c>
       <c r="J48" s="23">
-        <f>+Model!S79</f>
+        <f>+Model!W79</f>
         <v>-285.8</v>
       </c>
       <c r="K48" s="23">
-        <f>+Model!T79</f>
+        <f>+Model!X79</f>
         <v>-101.19999999999999</v>
       </c>
       <c r="L48" s="23">
-        <f>+Model!U79</f>
+        <f>+Model!Y79</f>
         <v>46.099999999999994</v>
       </c>
       <c r="M48" s="23">
@@ -12041,43 +12529,43 @@
       <c r="L52" s="41"/>
       <c r="M52" s="41">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>20.739593465686514</v>
+        <v>43.29133022654247</v>
       </c>
       <c r="N52" s="41">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>267.88153615334789</v>
+        <v>262.89312165622772</v>
       </c>
       <c r="O52" s="41">
         <f t="shared" ref="O52:U52" ca="1" si="16">O51/(1+$E$18)^O53</f>
-        <v>303.19319319174377</v>
+        <v>297.54721496545773</v>
       </c>
       <c r="P52" s="41">
         <f t="shared" ca="1" si="16"/>
-        <v>511.7795668769017</v>
+        <v>502.24935196400389</v>
       </c>
       <c r="Q52" s="41">
         <f t="shared" ca="1" si="16"/>
-        <v>765.60418222436806</v>
+        <v>751.34731683340055</v>
       </c>
       <c r="R52" s="41">
         <f t="shared" ca="1" si="16"/>
-        <v>1070.0342816209804</v>
+        <v>1050.1084046848482</v>
       </c>
       <c r="S52" s="41">
         <f t="shared" ca="1" si="16"/>
-        <v>1341.9159985121164</v>
+        <v>1316.9272168401187</v>
       </c>
       <c r="T52" s="41">
         <f t="shared" ca="1" si="16"/>
-        <v>1636.3034204891806</v>
+        <v>1605.8326391816443</v>
       </c>
       <c r="U52" s="41">
         <f t="shared" ca="1" si="16"/>
-        <v>1636.3034204891803</v>
+        <v>1605.832639181644</v>
       </c>
       <c r="V52" s="42">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>1561.9259922851263</v>
+        <v>1532.8402464915691</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.25">
@@ -12086,43 +12574,43 @@
       </c>
       <c r="M53" s="4">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.17499999999999999</v>
+        <v>0.37222222222222223</v>
       </c>
       <c r="N53" s="4">
         <f ca="1">M53+1</f>
-        <v>1.175</v>
+        <v>1.3722222222222222</v>
       </c>
       <c r="O53" s="4">
         <f ca="1">N53+1</f>
-        <v>2.1749999999999998</v>
+        <v>2.3722222222222222</v>
       </c>
       <c r="P53" s="4">
         <f t="shared" ref="P53:V53" ca="1" si="17">O53+1</f>
-        <v>3.1749999999999998</v>
+        <v>3.3722222222222222</v>
       </c>
       <c r="Q53" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>4.1749999999999998</v>
+        <v>4.3722222222222218</v>
       </c>
       <c r="R53" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>5.1749999999999998</v>
+        <v>5.3722222222222218</v>
       </c>
       <c r="S53" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>6.1749999999999998</v>
+        <v>6.3722222222222218</v>
       </c>
       <c r="T53" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>7.1749999999999998</v>
+        <v>7.3722222222222218</v>
       </c>
       <c r="U53" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>8.1750000000000007</v>
+        <v>8.3722222222222218</v>
       </c>
       <c r="V53" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9.1750000000000007</v>
+        <v>9.3722222222222218</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.25">
@@ -12135,7 +12623,7 @@
       <c r="Q54" s="43"/>
       <c r="V54" s="23">
         <f ca="1">SUM(M52:V52)</f>
-        <v>9115.681185308631</v>
+        <v>8968.8694820254568</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.25">
@@ -12179,7 +12667,7 @@
       <c r="U56" s="45"/>
       <c r="V56" s="46">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>20979.750757816015</v>
+        <v>20589.071749740047</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.25">
@@ -12207,7 +12695,7 @@
       <c r="U57" s="48"/>
       <c r="V57" s="49">
         <f ca="1">V54+V56</f>
-        <v>30095.431943124648</v>
+        <v>29557.941231765504</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.25">
@@ -12220,7 +12708,7 @@
       <c r="Q58" s="43"/>
       <c r="V58" s="50">
         <f>+Main!H6</f>
-        <v>1019.9</v>
+        <v>1020.4</v>
       </c>
     </row>
     <row r="59" spans="2:24" x14ac:dyDescent="0.25">
@@ -12248,7 +12736,7 @@
       <c r="U59" s="45"/>
       <c r="V59" s="46">
         <f>+Main!H7</f>
-        <v>59.5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="2:24" x14ac:dyDescent="0.25">
@@ -12261,7 +12749,7 @@
       <c r="Q60" s="43"/>
       <c r="V60" s="50">
         <f ca="1">V57+V58-V59</f>
-        <v>31055.831943124649</v>
+        <v>30520.341231765506</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.25">
@@ -12298,7 +12786,7 @@
       </c>
       <c r="V62" s="50">
         <f ca="1">V60/V61</f>
-        <v>104.6096984767934</v>
+        <v>102.80593028423641</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.25">
@@ -12331,35 +12819,35 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B68" s="51"/>
-      <c r="C68" s="89" t="s">
+      <c r="C68" s="108" t="s">
         <v>151</v>
       </c>
-      <c r="D68" s="89"/>
-      <c r="E68" s="89"/>
-      <c r="F68" s="89"/>
-      <c r="G68" s="89"/>
-      <c r="H68" s="89"/>
-      <c r="I68" s="89"/>
-      <c r="J68" s="90"/>
+      <c r="D68" s="108"/>
+      <c r="E68" s="108"/>
+      <c r="F68" s="108"/>
+      <c r="G68" s="108"/>
+      <c r="H68" s="108"/>
+      <c r="I68" s="108"/>
+      <c r="J68" s="109"/>
       <c r="M68" s="51"/>
-      <c r="N68" s="91" t="s">
+      <c r="N68" s="110" t="s">
         <v>179</v>
       </c>
-      <c r="O68" s="91"/>
-      <c r="P68" s="91"/>
-      <c r="Q68" s="91"/>
-      <c r="R68" s="91"/>
-      <c r="S68" s="91"/>
-      <c r="T68" s="91"/>
-      <c r="U68" s="92"/>
+      <c r="O68" s="110"/>
+      <c r="P68" s="110"/>
+      <c r="Q68" s="110"/>
+      <c r="R68" s="110"/>
+      <c r="S68" s="110"/>
+      <c r="T68" s="110"/>
+      <c r="U68" s="111"/>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="93" t="s">
+      <c r="B69" s="112" t="s">
         <v>149</v>
       </c>
       <c r="C69" s="52">
         <f ca="1">+J4</f>
-        <v>104.6096984767934</v>
+        <v>102.80593028423641</v>
       </c>
       <c r="D69" s="53"/>
       <c r="E69" s="53"/>
@@ -12368,12 +12856,12 @@
       <c r="H69" s="53"/>
       <c r="I69" s="53"/>
       <c r="J69" s="53"/>
-      <c r="M69" s="93" t="s">
+      <c r="M69" s="112" t="s">
         <v>149</v>
       </c>
       <c r="N69" s="52">
         <f ca="1">+J4</f>
-        <v>104.6096984767934</v>
+        <v>102.80593028423641</v>
       </c>
       <c r="O69" s="53"/>
       <c r="P69" s="53"/>
@@ -12384,7 +12872,7 @@
       <c r="U69" s="53"/>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="93"/>
+      <c r="B70" s="112"/>
       <c r="C70" s="54"/>
       <c r="D70" s="55"/>
       <c r="E70" s="55"/>
@@ -12393,7 +12881,7 @@
       <c r="H70" s="55"/>
       <c r="I70" s="55"/>
       <c r="J70" s="55"/>
-      <c r="M70" s="93"/>
+      <c r="M70" s="112"/>
       <c r="N70" s="54"/>
       <c r="O70" s="55"/>
       <c r="P70" s="55"/>
@@ -12404,7 +12892,7 @@
       <c r="U70" s="55"/>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="93"/>
+      <c r="B71" s="112"/>
       <c r="C71" s="54"/>
       <c r="D71" s="55"/>
       <c r="E71" s="55"/>
@@ -12413,7 +12901,7 @@
       <c r="H71" s="55"/>
       <c r="I71" s="55"/>
       <c r="J71" s="55"/>
-      <c r="M71" s="93"/>
+      <c r="M71" s="112"/>
       <c r="N71" s="54"/>
       <c r="O71" s="55"/>
       <c r="P71" s="55"/>
@@ -12424,7 +12912,7 @@
       <c r="U71" s="55"/>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="93"/>
+      <c r="B72" s="112"/>
       <c r="C72" s="54"/>
       <c r="D72" s="56"/>
       <c r="E72" s="56"/>
@@ -12433,7 +12921,7 @@
       <c r="H72" s="56"/>
       <c r="I72" s="56"/>
       <c r="J72" s="56"/>
-      <c r="M72" s="93"/>
+      <c r="M72" s="112"/>
       <c r="N72" s="54"/>
       <c r="O72" s="56"/>
       <c r="P72" s="56"/>
@@ -12444,7 +12932,7 @@
       <c r="U72" s="56"/>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="93"/>
+      <c r="B73" s="112"/>
       <c r="C73" s="54"/>
       <c r="D73" s="55"/>
       <c r="E73" s="55"/>
@@ -12453,7 +12941,7 @@
       <c r="H73" s="55"/>
       <c r="I73" s="55"/>
       <c r="J73" s="55"/>
-      <c r="M73" s="93"/>
+      <c r="M73" s="112"/>
       <c r="N73" s="54"/>
       <c r="O73" s="55"/>
       <c r="P73" s="55"/>
@@ -12464,7 +12952,7 @@
       <c r="U73" s="55"/>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="93"/>
+      <c r="B74" s="112"/>
       <c r="C74" s="54"/>
       <c r="D74" s="55"/>
       <c r="E74" s="55"/>
@@ -12473,7 +12961,7 @@
       <c r="H74" s="55"/>
       <c r="I74" s="55"/>
       <c r="J74" s="55"/>
-      <c r="M74" s="93"/>
+      <c r="M74" s="112"/>
       <c r="N74" s="54"/>
       <c r="O74" s="55"/>
       <c r="P74" s="55"/>
@@ -12484,7 +12972,7 @@
       <c r="U74" s="55"/>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="93"/>
+      <c r="B75" s="112"/>
       <c r="C75" s="54"/>
       <c r="D75" s="55"/>
       <c r="E75" s="55"/>
@@ -12493,7 +12981,7 @@
       <c r="H75" s="55"/>
       <c r="I75" s="55"/>
       <c r="J75" s="55"/>
-      <c r="M75" s="93"/>
+      <c r="M75" s="112"/>
       <c r="N75" s="54"/>
       <c r="O75" s="55"/>
       <c r="P75" s="55"/>
@@ -12504,7 +12992,7 @@
       <c r="U75" s="55"/>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="94"/>
+      <c r="B76" s="113"/>
       <c r="C76" s="54"/>
       <c r="D76" s="55"/>
       <c r="E76" s="55"/>
@@ -12513,7 +13001,7 @@
       <c r="H76" s="55"/>
       <c r="I76" s="55"/>
       <c r="J76" s="55"/>
-      <c r="M76" s="94"/>
+      <c r="M76" s="113"/>
       <c r="N76" s="54"/>
       <c r="O76" s="55"/>
       <c r="P76" s="55"/>

--- a/ONON.xlsx
+++ b/ONON.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F02E5AE-7E7C-4B42-B511-C4954981D781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C089CC-B821-40F3-9D0A-FCB9D90BFEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{3D17FBD5-4686-4900-BBF2-80842DD395C0}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{3D17FBD5-4686-4900-BBF2-80842DD395C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1068,13 +1068,19 @@
     <numFmt numFmtId="173" formatCode="\F\Y#,##0"/>
     <numFmt numFmtId="174" formatCode="#,##0.0;\(#,##0.0\)"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1443,19 +1449,19 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1475,43 +1481,43 @@
     <xf numFmtId="9" fontId="0" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="168" fontId="0" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="6" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="6" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="7" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="7" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1527,106 +1533,110 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="13" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="9" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="7" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="7" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="173" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="173" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="174" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2101,7 +2111,7 @@
         <v>19</v>
       </c>
       <c r="H2" s="89">
-        <v>36.42</v>
+        <v>30.85</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -2110,7 +2120,7 @@
       </c>
       <c r="H3" s="66">
         <f>+H2*H10</f>
-        <v>30.957000000000001</v>
+        <v>26.2225</v>
       </c>
       <c r="K3" s="68"/>
     </row>
@@ -2124,8 +2134,8 @@
       <c r="H4" s="66">
         <v>296.87335300000001</v>
       </c>
-      <c r="I4" s="114" t="s">
-        <v>313</v>
+      <c r="I4" s="117" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -2137,7 +2147,7 @@
       </c>
       <c r="H5" s="66">
         <f>+H3*H4</f>
-        <v>9190.3083888210003</v>
+        <v>7784.7614990425</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -2147,8 +2157,8 @@
       <c r="H6" s="66">
         <v>1020.4</v>
       </c>
-      <c r="I6" s="114" t="s">
-        <v>313</v>
+      <c r="I6" s="117" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -2165,8 +2175,8 @@
         <f>52.2+5.8</f>
         <v>58</v>
       </c>
-      <c r="I7" s="114" t="s">
-        <v>313</v>
+      <c r="I7" s="117" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -2181,7 +2191,7 @@
       </c>
       <c r="H8" s="66">
         <f>+H5-H6+H7</f>
-        <v>8227.9083888210007</v>
+        <v>6822.3614990425003</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -2323,16 +2333,16 @@
       <c r="N2" s="67" t="s">
         <v>308</v>
       </c>
-      <c r="O2" s="114" t="s">
+      <c r="O2" s="108" t="s">
         <v>313</v>
       </c>
-      <c r="P2" s="114" t="s">
+      <c r="P2" s="108" t="s">
         <v>314</v>
       </c>
-      <c r="Q2" s="114" t="s">
+      <c r="Q2" s="108" t="s">
         <v>315</v>
       </c>
-      <c r="R2" s="114" t="s">
+      <c r="R2" s="108" t="s">
         <v>316</v>
       </c>
       <c r="T2" s="67" t="s">
@@ -2403,7 +2413,9 @@
       <c r="O3" s="66">
         <v>207.1</v>
       </c>
-      <c r="P3" s="66"/>
+      <c r="P3" s="66">
+        <v>228.2</v>
+      </c>
       <c r="Q3" s="66"/>
       <c r="R3" s="66"/>
       <c r="S3" s="66"/>
@@ -2501,7 +2513,9 @@
       <c r="O4" s="66">
         <v>450.7</v>
       </c>
-      <c r="P4" s="66"/>
+      <c r="P4" s="66">
+        <v>451.6</v>
+      </c>
       <c r="Q4" s="66"/>
       <c r="R4" s="66"/>
       <c r="S4" s="66"/>
@@ -2596,7 +2610,9 @@
       <c r="O5" s="66">
         <v>174</v>
       </c>
-      <c r="P5" s="66"/>
+      <c r="P5" s="66">
+        <v>170.5</v>
+      </c>
       <c r="Q5" s="66"/>
       <c r="R5" s="66"/>
       <c r="S5" s="66"/>
@@ -2692,7 +2708,9 @@
       <c r="O6" s="66">
         <v>763.7</v>
       </c>
-      <c r="P6" s="66"/>
+      <c r="P6" s="66">
+        <v>781.6</v>
+      </c>
       <c r="Q6" s="66"/>
       <c r="R6" s="66"/>
       <c r="S6" s="66"/>
@@ -2787,7 +2805,9 @@
       <c r="O7" s="66">
         <v>55.3</v>
       </c>
-      <c r="P7" s="66"/>
+      <c r="P7" s="66">
+        <v>54.2</v>
+      </c>
       <c r="Q7" s="66"/>
       <c r="R7" s="66"/>
       <c r="S7" s="66"/>
@@ -2882,7 +2902,9 @@
       <c r="O8" s="66">
         <v>12.9</v>
       </c>
-      <c r="P8" s="66"/>
+      <c r="P8" s="66">
+        <v>14.5</v>
+      </c>
       <c r="Q8" s="66"/>
       <c r="R8" s="66"/>
       <c r="S8" s="66"/>
@@ -2977,7 +2999,9 @@
       <c r="O9" s="66">
         <v>509.6</v>
       </c>
-      <c r="P9" s="66"/>
+      <c r="P9" s="66">
+        <v>461.9</v>
+      </c>
       <c r="Q9" s="66"/>
       <c r="R9" s="66"/>
       <c r="S9" s="66"/>
@@ -3072,7 +3096,9 @@
       <c r="O10" s="66">
         <v>322.3</v>
       </c>
-      <c r="P10" s="66"/>
+      <c r="P10" s="66">
+        <v>388.4</v>
+      </c>
       <c r="Q10" s="66"/>
       <c r="R10" s="66"/>
       <c r="S10" s="66"/>
@@ -3163,7 +3189,9 @@
       <c r="O11" s="81">
         <v>831.9</v>
       </c>
-      <c r="P11" s="66"/>
+      <c r="P11" s="81">
+        <v>850.3</v>
+      </c>
       <c r="Q11" s="66"/>
       <c r="R11" s="66"/>
       <c r="S11" s="66"/>
@@ -3254,7 +3282,9 @@
       <c r="O12" s="66">
         <v>297.60000000000002</v>
       </c>
-      <c r="P12" s="66"/>
+      <c r="P12" s="116">
+        <v>294.60000000000002</v>
+      </c>
       <c r="Q12" s="66"/>
       <c r="R12" s="66"/>
       <c r="S12" s="66"/>
@@ -3332,7 +3362,7 @@
         <v>385.29999999999995</v>
       </c>
       <c r="J13" s="66">
-        <f t="shared" ref="J13:O13" si="4">+J11-J12</f>
+        <f t="shared" ref="J13:P13" si="4">+J11-J12</f>
         <v>376.80000000000007</v>
       </c>
       <c r="K13" s="66">
@@ -3355,7 +3385,10 @@
         <f t="shared" si="4"/>
         <v>534.29999999999995</v>
       </c>
-      <c r="P13" s="66"/>
+      <c r="P13" s="66">
+        <f t="shared" si="4"/>
+        <v>555.69999999999993</v>
+      </c>
       <c r="Q13" s="66"/>
       <c r="R13" s="66"/>
       <c r="S13" s="66"/>
@@ -3453,7 +3486,9 @@
       <c r="O14" s="66">
         <v>416.9</v>
       </c>
-      <c r="P14" s="66"/>
+      <c r="P14" s="66">
+        <v>436.3</v>
+      </c>
       <c r="Q14" s="66"/>
       <c r="R14" s="66"/>
       <c r="S14" s="66"/>
@@ -3531,7 +3566,7 @@
         <v>72.599999999999966</v>
       </c>
       <c r="J15" s="66">
-        <f t="shared" ref="J15:O15" si="7">+J13-J14</f>
+        <f t="shared" ref="J15:P15" si="7">+J13-J14</f>
         <v>53.000000000000114</v>
       </c>
       <c r="K15" s="66">
@@ -3554,7 +3589,10 @@
         <f t="shared" si="7"/>
         <v>117.39999999999998</v>
       </c>
-      <c r="P15" s="66"/>
+      <c r="P15" s="66">
+        <f t="shared" si="7"/>
+        <v>119.39999999999992</v>
+      </c>
       <c r="Q15" s="66"/>
       <c r="R15" s="66"/>
       <c r="S15" s="66"/>
@@ -3652,7 +3690,9 @@
       <c r="O16" s="66">
         <v>7</v>
       </c>
-      <c r="P16" s="66"/>
+      <c r="P16" s="66">
+        <v>11.3</v>
+      </c>
       <c r="Q16" s="66"/>
       <c r="R16" s="66"/>
       <c r="S16" s="66"/>
@@ -3743,7 +3783,9 @@
       <c r="O17" s="66">
         <v>8</v>
       </c>
-      <c r="P17" s="66"/>
+      <c r="P17" s="66">
+        <v>8.3000000000000007</v>
+      </c>
       <c r="Q17" s="66"/>
       <c r="R17" s="66"/>
       <c r="S17" s="66"/>
@@ -3831,10 +3873,12 @@
         <f>+Z18-SUM(K18:M18)</f>
         <v>-333.7</v>
       </c>
-      <c r="O18" s="115">
+      <c r="O18" s="109">
         <v>0.3</v>
       </c>
-      <c r="P18" s="66"/>
+      <c r="P18" s="66">
+        <v>3.3</v>
+      </c>
       <c r="Q18" s="66"/>
       <c r="R18" s="66"/>
       <c r="S18" s="66"/>
@@ -3912,7 +3956,7 @@
         <v>29.499999999999964</v>
       </c>
       <c r="J19" s="66">
-        <f t="shared" ref="J19:O19" si="10">+J15+J16-J17-J18</f>
+        <f t="shared" ref="J19:P19" si="10">+J15+J16-J17-J18</f>
         <v>-43.899999999999892</v>
       </c>
       <c r="K19" s="66">
@@ -3935,7 +3979,10 @@
         <f t="shared" si="10"/>
         <v>116.09999999999998</v>
       </c>
-      <c r="P19" s="66"/>
+      <c r="P19" s="66">
+        <f t="shared" si="10"/>
+        <v>119.09999999999994</v>
+      </c>
       <c r="Q19" s="66"/>
       <c r="R19" s="66"/>
       <c r="S19" s="66"/>
@@ -4033,7 +4080,9 @@
       <c r="O20" s="66">
         <v>12.8</v>
       </c>
-      <c r="P20" s="66"/>
+      <c r="P20" s="66">
+        <v>20.7</v>
+      </c>
       <c r="Q20" s="66"/>
       <c r="R20" s="66"/>
       <c r="S20" s="66"/>
@@ -4134,7 +4183,10 @@
         <f>+O19-O20</f>
         <v>103.29999999999998</v>
       </c>
-      <c r="P21" s="66"/>
+      <c r="P21" s="66">
+        <f>+P19-P20</f>
+        <v>98.399999999999935</v>
+      </c>
       <c r="Q21" s="66"/>
       <c r="R21" s="66"/>
       <c r="S21" s="66"/>
@@ -4248,7 +4300,7 @@
         <v>0.10547035930930765</v>
       </c>
       <c r="J23" s="82">
-        <f t="shared" ref="J23:O23" si="15">+J21/J24</f>
+        <f t="shared" ref="J23:P23" si="15">+J21/J24</f>
         <v>0.30865931272619346</v>
       </c>
       <c r="K23" s="82">
@@ -4271,7 +4323,10 @@
         <f t="shared" si="15"/>
         <v>0.34795982514469725</v>
       </c>
-      <c r="P23" s="82"/>
+      <c r="P23" s="82">
+        <f t="shared" si="15"/>
+        <v>0.33145447041856912</v>
+      </c>
       <c r="Q23" s="82"/>
       <c r="R23" s="82"/>
       <c r="S23" s="66"/>
@@ -4366,7 +4421,9 @@
       <c r="O24" s="66">
         <v>296.87335300000001</v>
       </c>
-      <c r="P24" s="66"/>
+      <c r="P24" s="66">
+        <v>296.87335300000001</v>
+      </c>
       <c r="Q24" s="66"/>
       <c r="R24" s="66"/>
       <c r="S24" s="66"/>
@@ -4476,7 +4533,7 @@
         <v>0.15138888888888902</v>
       </c>
       <c r="J26" s="85">
-        <f t="shared" ref="J26:O34" si="19">+J3/F3-1</f>
+        <f t="shared" ref="J26:P34" si="19">+J3/F3-1</f>
         <v>0.31372549019607776</v>
       </c>
       <c r="K26" s="85">
@@ -4499,7 +4556,10 @@
         <f t="shared" si="19"/>
         <v>0.22835112692763948</v>
       </c>
-      <c r="P26" s="85"/>
+      <c r="P26" s="85">
+        <f t="shared" si="19"/>
+        <v>0.15369059656218398</v>
+      </c>
       <c r="Q26" s="85"/>
       <c r="R26" s="85"/>
       <c r="S26" s="66"/>
@@ -4594,7 +4654,10 @@
         <f t="shared" si="19"/>
         <v>3.0406950160036583E-2</v>
       </c>
-      <c r="P27" s="85"/>
+      <c r="P27" s="85">
+        <f t="shared" si="19"/>
+        <v>4.4644922507518059E-2</v>
+      </c>
       <c r="Q27" s="85"/>
       <c r="R27" s="85"/>
       <c r="S27" s="66"/>
@@ -4689,7 +4752,10 @@
         <f t="shared" si="19"/>
         <v>0.44278606965174139</v>
       </c>
-      <c r="P28" s="85"/>
+      <c r="P28" s="85">
+        <f t="shared" si="19"/>
+        <v>0.43036912751677847</v>
+      </c>
       <c r="Q28" s="85"/>
       <c r="R28" s="85"/>
       <c r="S28" s="66"/>
@@ -4784,7 +4850,10 @@
         <f t="shared" si="19"/>
         <v>0.12160375972976945</v>
       </c>
-      <c r="P29" s="85"/>
+      <c r="P29" s="85">
+        <f t="shared" si="19"/>
+        <v>0.10880976024968092</v>
+      </c>
       <c r="Q29" s="85"/>
       <c r="R29" s="85"/>
       <c r="S29" s="66"/>
@@ -4879,7 +4948,10 @@
         <f t="shared" si="19"/>
         <v>0.45144356955380571</v>
       </c>
-      <c r="P30" s="85"/>
+      <c r="P30" s="85">
+        <f t="shared" si="19"/>
+        <v>0.47683923705722076</v>
+      </c>
       <c r="Q30" s="85"/>
       <c r="R30" s="85"/>
       <c r="S30" s="66"/>
@@ -4974,7 +5046,10 @@
         <f t="shared" si="19"/>
         <v>0.69736842105263164</v>
       </c>
-      <c r="P31" s="85"/>
+      <c r="P31" s="85">
+        <f t="shared" si="19"/>
+        <v>0.88311688311688297</v>
+      </c>
       <c r="Q31" s="85"/>
       <c r="R31" s="85"/>
       <c r="S31" s="66"/>
@@ -5069,7 +5144,10 @@
         <f t="shared" si="19"/>
         <v>0.1331999110518125</v>
       </c>
-      <c r="P32" s="85"/>
+      <c r="P32" s="85">
+        <f t="shared" si="19"/>
+        <v>4.7392290249433033E-2</v>
+      </c>
       <c r="Q32" s="85"/>
       <c r="R32" s="85"/>
       <c r="S32" s="66"/>
@@ -5164,7 +5242,10 @@
         <f t="shared" si="19"/>
         <v>0.16395810762007956</v>
       </c>
-      <c r="P33" s="85"/>
+      <c r="P33" s="85">
+        <f t="shared" si="19"/>
+        <v>0.25981187155368146</v>
+      </c>
       <c r="Q33" s="85"/>
       <c r="R33" s="85"/>
       <c r="S33" s="66"/>
@@ -5259,7 +5340,10 @@
         <f t="shared" si="19"/>
         <v>0.14492155243600324</v>
       </c>
-      <c r="P34" s="86"/>
+      <c r="P34" s="86">
+        <f t="shared" si="19"/>
+        <v>0.13494394020288292</v>
+      </c>
       <c r="Q34" s="86"/>
       <c r="R34" s="86"/>
       <c r="S34" s="81"/>
@@ -5363,10 +5447,13 @@
         <v>0.63901586447969883</v>
       </c>
       <c r="O35" s="85">
-        <f t="shared" ref="O35" si="34">+O13/O11</f>
+        <f t="shared" ref="O35:P35" si="34">+O13/O11</f>
         <v>0.64226469527587449</v>
       </c>
-      <c r="P35" s="85"/>
+      <c r="P35" s="85">
+        <f t="shared" si="34"/>
+        <v>0.65353404680700922</v>
+      </c>
       <c r="Q35" s="85"/>
       <c r="R35" s="85"/>
       <c r="S35" s="66"/>
@@ -5471,10 +5558,13 @@
         <v>0.11078246840548535</v>
       </c>
       <c r="O36" s="85">
-        <f t="shared" ref="O36" si="39">+O15/O11</f>
+        <f t="shared" ref="O36:P36" si="39">+O15/O11</f>
         <v>0.14112273109748766</v>
       </c>
-      <c r="P36" s="85"/>
+      <c r="P36" s="85">
+        <f t="shared" si="39"/>
+        <v>0.14042102787251551</v>
+      </c>
       <c r="Q36" s="85"/>
       <c r="R36" s="85"/>
       <c r="S36" s="66"/>
@@ -5579,10 +5669,13 @@
         <v>2.4026910139356089E-3</v>
       </c>
       <c r="O37" s="85">
-        <f t="shared" ref="O37" si="44">+O20/O19</f>
+        <f t="shared" ref="O37:P37" si="44">+O20/O19</f>
         <v>0.11024978466838935</v>
       </c>
-      <c r="P37" s="85"/>
+      <c r="P37" s="85">
+        <f t="shared" si="44"/>
+        <v>0.17380352644836281</v>
+      </c>
       <c r="Q37" s="85"/>
       <c r="R37" s="85"/>
       <c r="S37" s="66"/>
@@ -11034,14 +11127,14 @@
       </c>
       <c r="J3" s="10">
         <f>+Main!H3</f>
-        <v>30.957000000000001</v>
+        <v>26.2225</v>
       </c>
       <c r="L3" t="s">
         <v>132</v>
       </c>
       <c r="O3" s="10">
         <f>+J3</f>
-        <v>30.957000000000001</v>
+        <v>26.2225</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -11050,14 +11143,14 @@
       </c>
       <c r="E4" s="11">
         <f ca="1">+TODAY()</f>
-        <v>46156</v>
+        <v>46245</v>
       </c>
       <c r="G4" t="s">
         <v>134</v>
       </c>
       <c r="J4" s="12">
         <f ca="1">V62</f>
-        <v>102.80593028423641</v>
+        <v>100.63137066955122</v>
       </c>
       <c r="L4" t="s">
         <v>135</v>
@@ -11079,7 +11172,7 @@
       </c>
       <c r="J5" s="15">
         <f ca="1">J4/J3-1</f>
-        <v>2.3209267785714509</v>
+        <v>2.8375963645552948</v>
       </c>
       <c r="L5" t="s">
         <v>137</v>
@@ -12529,43 +12622,43 @@
       <c r="L52" s="41"/>
       <c r="M52" s="41">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>43.29133022654247</v>
+        <v>69.772642896395425</v>
       </c>
       <c r="N52" s="41">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>262.89312165622772</v>
+        <v>256.90703157218201</v>
       </c>
       <c r="O52" s="41">
         <f t="shared" ref="O52:U52" ca="1" si="16">O51/(1+$E$18)^O53</f>
-        <v>297.54721496545773</v>
+        <v>290.77204937033326</v>
       </c>
       <c r="P52" s="41">
         <f t="shared" ca="1" si="16"/>
-        <v>502.24935196400389</v>
+        <v>490.81310803883355</v>
       </c>
       <c r="Q52" s="41">
         <f t="shared" ca="1" si="16"/>
-        <v>751.34731683340055</v>
+        <v>734.23909926332612</v>
       </c>
       <c r="R52" s="41">
         <f t="shared" ca="1" si="16"/>
-        <v>1050.1084046848482</v>
+        <v>1026.1973815707595</v>
       </c>
       <c r="S52" s="41">
         <f t="shared" ca="1" si="16"/>
-        <v>1316.9272168401187</v>
+        <v>1286.9407154646849</v>
       </c>
       <c r="T52" s="41">
         <f t="shared" ca="1" si="16"/>
-        <v>1605.8326391816443</v>
+        <v>1569.2677462796071</v>
       </c>
       <c r="U52" s="41">
         <f t="shared" ca="1" si="16"/>
-        <v>1605.832639181644</v>
+        <v>1569.2677462796071</v>
       </c>
       <c r="V52" s="42">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>1532.8402464915691</v>
+        <v>1497.9373941759882</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.25">
@@ -12574,43 +12667,43 @@
       </c>
       <c r="M53" s="4">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.37222222222222223</v>
+        <v>0.61388888888888893</v>
       </c>
       <c r="N53" s="4">
         <f ca="1">M53+1</f>
-        <v>1.3722222222222222</v>
+        <v>1.6138888888888889</v>
       </c>
       <c r="O53" s="4">
         <f ca="1">N53+1</f>
-        <v>2.3722222222222222</v>
+        <v>2.6138888888888889</v>
       </c>
       <c r="P53" s="4">
         <f t="shared" ref="P53:V53" ca="1" si="17">O53+1</f>
-        <v>3.3722222222222222</v>
+        <v>3.6138888888888889</v>
       </c>
       <c r="Q53" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>4.3722222222222218</v>
+        <v>4.6138888888888889</v>
       </c>
       <c r="R53" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>5.3722222222222218</v>
+        <v>5.6138888888888889</v>
       </c>
       <c r="S53" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>6.3722222222222218</v>
+        <v>6.6138888888888889</v>
       </c>
       <c r="T53" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>7.3722222222222218</v>
+        <v>7.6138888888888889</v>
       </c>
       <c r="U53" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>8.3722222222222218</v>
+        <v>8.6138888888888889</v>
       </c>
       <c r="V53" s="4">
         <f t="shared" ca="1" si="17"/>
-        <v>9.3722222222222218</v>
+        <v>9.6138888888888889</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.25">
@@ -12623,7 +12716,7 @@
       <c r="Q54" s="43"/>
       <c r="V54" s="23">
         <f ca="1">SUM(M52:V52)</f>
-        <v>8968.8694820254568</v>
+        <v>8792.1149149117173</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.25">
@@ -12667,7 +12760,7 @@
       <c r="U56" s="45"/>
       <c r="V56" s="46">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>20589.071749740047</v>
+        <v>20120.257512743803</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.25">
@@ -12695,7 +12788,7 @@
       <c r="U57" s="48"/>
       <c r="V57" s="49">
         <f ca="1">V54+V56</f>
-        <v>29557.941231765504</v>
+        <v>28912.372427655522</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.25">
@@ -12749,7 +12842,7 @@
       <c r="Q60" s="43"/>
       <c r="V60" s="50">
         <f ca="1">V57+V58-V59</f>
-        <v>30520.341231765506</v>
+        <v>29874.772427655524</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.25">
@@ -12786,7 +12879,7 @@
       </c>
       <c r="V62" s="50">
         <f ca="1">V60/V61</f>
-        <v>102.80593028423641</v>
+        <v>100.63137066955122</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.25">
@@ -12819,35 +12912,35 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B68" s="51"/>
-      <c r="C68" s="108" t="s">
+      <c r="C68" s="110" t="s">
         <v>151</v>
       </c>
-      <c r="D68" s="108"/>
-      <c r="E68" s="108"/>
-      <c r="F68" s="108"/>
-      <c r="G68" s="108"/>
-      <c r="H68" s="108"/>
-      <c r="I68" s="108"/>
-      <c r="J68" s="109"/>
+      <c r="D68" s="110"/>
+      <c r="E68" s="110"/>
+      <c r="F68" s="110"/>
+      <c r="G68" s="110"/>
+      <c r="H68" s="110"/>
+      <c r="I68" s="110"/>
+      <c r="J68" s="111"/>
       <c r="M68" s="51"/>
-      <c r="N68" s="110" t="s">
+      <c r="N68" s="112" t="s">
         <v>179</v>
       </c>
-      <c r="O68" s="110"/>
-      <c r="P68" s="110"/>
-      <c r="Q68" s="110"/>
-      <c r="R68" s="110"/>
-      <c r="S68" s="110"/>
-      <c r="T68" s="110"/>
-      <c r="U68" s="111"/>
+      <c r="O68" s="112"/>
+      <c r="P68" s="112"/>
+      <c r="Q68" s="112"/>
+      <c r="R68" s="112"/>
+      <c r="S68" s="112"/>
+      <c r="T68" s="112"/>
+      <c r="U68" s="113"/>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B69" s="112" t="s">
+      <c r="B69" s="114" t="s">
         <v>149</v>
       </c>
       <c r="C69" s="52">
         <f ca="1">+J4</f>
-        <v>102.80593028423641</v>
+        <v>100.63137066955122</v>
       </c>
       <c r="D69" s="53"/>
       <c r="E69" s="53"/>
@@ -12856,12 +12949,12 @@
       <c r="H69" s="53"/>
       <c r="I69" s="53"/>
       <c r="J69" s="53"/>
-      <c r="M69" s="112" t="s">
+      <c r="M69" s="114" t="s">
         <v>149</v>
       </c>
       <c r="N69" s="52">
         <f ca="1">+J4</f>
-        <v>102.80593028423641</v>
+        <v>100.63137066955122</v>
       </c>
       <c r="O69" s="53"/>
       <c r="P69" s="53"/>
@@ -12872,7 +12965,7 @@
       <c r="U69" s="53"/>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B70" s="112"/>
+      <c r="B70" s="114"/>
       <c r="C70" s="54"/>
       <c r="D70" s="55"/>
       <c r="E70" s="55"/>
@@ -12881,7 +12974,7 @@
       <c r="H70" s="55"/>
       <c r="I70" s="55"/>
       <c r="J70" s="55"/>
-      <c r="M70" s="112"/>
+      <c r="M70" s="114"/>
       <c r="N70" s="54"/>
       <c r="O70" s="55"/>
       <c r="P70" s="55"/>
@@ -12892,7 +12985,7 @@
       <c r="U70" s="55"/>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B71" s="112"/>
+      <c r="B71" s="114"/>
       <c r="C71" s="54"/>
       <c r="D71" s="55"/>
       <c r="E71" s="55"/>
@@ -12901,7 +12994,7 @@
       <c r="H71" s="55"/>
       <c r="I71" s="55"/>
       <c r="J71" s="55"/>
-      <c r="M71" s="112"/>
+      <c r="M71" s="114"/>
       <c r="N71" s="54"/>
       <c r="O71" s="55"/>
       <c r="P71" s="55"/>
@@ -12912,7 +13005,7 @@
       <c r="U71" s="55"/>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B72" s="112"/>
+      <c r="B72" s="114"/>
       <c r="C72" s="54"/>
       <c r="D72" s="56"/>
       <c r="E72" s="56"/>
@@ -12921,7 +13014,7 @@
       <c r="H72" s="56"/>
       <c r="I72" s="56"/>
       <c r="J72" s="56"/>
-      <c r="M72" s="112"/>
+      <c r="M72" s="114"/>
       <c r="N72" s="54"/>
       <c r="O72" s="56"/>
       <c r="P72" s="56"/>
@@ -12932,7 +13025,7 @@
       <c r="U72" s="56"/>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B73" s="112"/>
+      <c r="B73" s="114"/>
       <c r="C73" s="54"/>
       <c r="D73" s="55"/>
       <c r="E73" s="55"/>
@@ -12941,7 +13034,7 @@
       <c r="H73" s="55"/>
       <c r="I73" s="55"/>
       <c r="J73" s="55"/>
-      <c r="M73" s="112"/>
+      <c r="M73" s="114"/>
       <c r="N73" s="54"/>
       <c r="O73" s="55"/>
       <c r="P73" s="55"/>
@@ -12952,7 +13045,7 @@
       <c r="U73" s="55"/>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B74" s="112"/>
+      <c r="B74" s="114"/>
       <c r="C74" s="54"/>
       <c r="D74" s="55"/>
       <c r="E74" s="55"/>
@@ -12961,7 +13054,7 @@
       <c r="H74" s="55"/>
       <c r="I74" s="55"/>
       <c r="J74" s="55"/>
-      <c r="M74" s="112"/>
+      <c r="M74" s="114"/>
       <c r="N74" s="54"/>
       <c r="O74" s="55"/>
       <c r="P74" s="55"/>
@@ -12972,7 +13065,7 @@
       <c r="U74" s="55"/>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B75" s="112"/>
+      <c r="B75" s="114"/>
       <c r="C75" s="54"/>
       <c r="D75" s="55"/>
       <c r="E75" s="55"/>
@@ -12981,7 +13074,7 @@
       <c r="H75" s="55"/>
       <c r="I75" s="55"/>
       <c r="J75" s="55"/>
-      <c r="M75" s="112"/>
+      <c r="M75" s="114"/>
       <c r="N75" s="54"/>
       <c r="O75" s="55"/>
       <c r="P75" s="55"/>
@@ -12992,7 +13085,7 @@
       <c r="U75" s="55"/>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B76" s="113"/>
+      <c r="B76" s="115"/>
       <c r="C76" s="54"/>
       <c r="D76" s="55"/>
       <c r="E76" s="55"/>
@@ -13001,7 +13094,7 @@
       <c r="H76" s="55"/>
       <c r="I76" s="55"/>
       <c r="J76" s="55"/>
-      <c r="M76" s="113"/>
+      <c r="M76" s="115"/>
       <c r="N76" s="54"/>
       <c r="O76" s="55"/>
       <c r="P76" s="55"/>
